--- a/research/traditional_assets/database/data/belgium/belgium_transportation.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_transportation.xlsx
@@ -650,10 +650,10 @@
         <v>0.08557186374965384</v>
       </c>
       <c r="X2">
-        <v>0.3060504760511554</v>
+        <v>0.3059289365130447</v>
       </c>
       <c r="Y2">
-        <v>-0.2204786123015015</v>
+        <v>-0.2203570727633909</v>
       </c>
       <c r="Z2">
         <v>2.898019618730335</v>
@@ -662,10 +662,10 @@
         <v>0.06918219552027643</v>
       </c>
       <c r="AB2">
-        <v>0.07880147948437749</v>
+        <v>0.07878611947149011</v>
       </c>
       <c r="AC2">
-        <v>-0.009619283964101055</v>
+        <v>-0.009603923951213678</v>
       </c>
       <c r="AD2">
         <v>2819.7</v>
@@ -787,10 +787,10 @@
         <v>0.08557186374965384</v>
       </c>
       <c r="X3">
-        <v>0.3060504760511554</v>
+        <v>0.3059289365130447</v>
       </c>
       <c r="Y3">
-        <v>-0.2204786123015015</v>
+        <v>-0.2203570727633909</v>
       </c>
       <c r="Z3">
         <v>2.898019618730335</v>
@@ -799,10 +799,10 @@
         <v>0.06918219552027643</v>
       </c>
       <c r="AB3">
-        <v>0.07880147948437749</v>
+        <v>0.07878611947149011</v>
       </c>
       <c r="AC3">
-        <v>-0.009619283964101055</v>
+        <v>-0.009603923951213678</v>
       </c>
       <c r="AD3">
         <v>2819.7</v>
@@ -1139,49 +1139,49 @@
         <v>-0.580769230769231</v>
       </c>
       <c r="F2">
-        <v>5.27327187001986</v>
+        <v>4.58097150134437</v>
       </c>
       <c r="G2">
         <v>8.33984028393966</v>
       </c>
       <c r="H2">
-        <v>0.477314404022478</v>
+        <v>0.572777284826974</v>
       </c>
       <c r="I2">
         <v>0.873621266575784</v>
       </c>
       <c r="J2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K2">
         <v>407.9</v>
       </c>
       <c r="L2">
-        <v>2527.15507916892</v>
+        <v>2504.86642581341</v>
       </c>
       <c r="M2">
         <v>2594</v>
       </c>
       <c r="N2">
-        <v>2054.93507916892</v>
+        <v>2064.92242581341</v>
       </c>
       <c r="O2">
         <v>2819.7</v>
       </c>
       <c r="P2">
-        <v>161.38</v>
+        <v>193.656</v>
       </c>
       <c r="Q2">
-        <v>0.0788014794843775</v>
+        <v>0.0787861194714901</v>
       </c>
       <c r="R2">
-        <v>0.0874586580521545</v>
+        <v>0.0872378733260836</v>
       </c>
       <c r="S2">
         <v>0.0459274624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.306050476051155</v>
+        <v>0.305928936513045</v>
       </c>
       <c r="X2">
-        <v>0.0895418788708521</v>
+        <v>0.08987470805986129</v>
       </c>
       <c r="Y2">
         <v>5.07039715037416</v>
       </c>
       <c r="Z2">
-        <v>0.852212458336425</v>
+        <v>0.859098096297667</v>
       </c>
       <c r="AA2">
         <v>2819.7</v>
@@ -1236,7 +1236,7 @@
         <v>407.9</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08788079486309822</v>
+        <v>0.08786114271702496</v>
       </c>
       <c r="C2">
-        <v>2667.920835929487</v>
+        <v>2667.924043089088</v>
       </c>
       <c r="D2">
-        <v>2034.320835929487</v>
+        <v>2034.324043089088</v>
       </c>
       <c r="E2">
         <v>-2819.7</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08788079486309822</v>
+        <v>0.08786114271702496</v>
       </c>
       <c r="T2">
         <v>0.819849959918586</v>
       </c>
       <c r="U2">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08774986750090946</v>
+        <v>0.0877197644852014</v>
       </c>
       <c r="C3">
-        <v>2641.994039794984</v>
+        <v>2642.508986601059</v>
       </c>
       <c r="D3">
-        <v>2040.670039794984</v>
+        <v>2041.184986601059</v>
       </c>
       <c r="E3">
         <v>-2787.424</v>
@@ -1539,37 +1539,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M3">
-        <v>1.86027943939995</v>
+        <v>1.81509303939995</v>
       </c>
       <c r="N3">
-        <v>52.46472056060004</v>
+        <v>52.50990696060004</v>
       </c>
       <c r="O3">
-        <v>13.11618014015001</v>
+        <v>13.12747674015001</v>
       </c>
       <c r="P3">
-        <v>39.34854042045003</v>
+        <v>39.38243022045003</v>
       </c>
       <c r="Q3">
-        <v>407.64854042045</v>
+        <v>407.68243022045</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08819958876357623</v>
+        <v>0.08817978773760848</v>
       </c>
       <c r="T3">
         <v>0.8260609444634238</v>
       </c>
       <c r="U3">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>29.20260195829666</v>
+        <v>29.92959524430728</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08761894013872072</v>
+        <v>0.08757838625337784</v>
       </c>
       <c r="C4">
-        <v>2616.107000025006</v>
+        <v>2617.140365035455</v>
       </c>
       <c r="D4">
-        <v>2047.059000025006</v>
+        <v>2048.092365035455</v>
       </c>
       <c r="E4">
         <v>-2755.148</v>
@@ -1621,37 +1621,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M4">
-        <v>3.7205588787999</v>
+        <v>3.6301860787999</v>
       </c>
       <c r="N4">
-        <v>50.60444112120009</v>
+        <v>50.69481392120009</v>
       </c>
       <c r="O4">
-        <v>12.65111028030002</v>
+        <v>12.67370348030002</v>
       </c>
       <c r="P4">
-        <v>37.95333084090007</v>
+        <v>38.02111044090007</v>
       </c>
       <c r="Q4">
-        <v>406.2533308409</v>
+        <v>406.3211104409001</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08852488866202318</v>
+        <v>0.08850493571779575</v>
       </c>
       <c r="T4">
         <v>0.8323986837948909</v>
       </c>
       <c r="U4">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>14.60130097914833</v>
+        <v>14.96479762215364</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08756226277653199</v>
+        <v>0.0875090080215543</v>
       </c>
       <c r="C5">
-        <v>2586.609151797742</v>
+        <v>2588.271135746089</v>
       </c>
       <c r="D5">
-        <v>2049.837151797742</v>
+        <v>2051.499135746089</v>
       </c>
       <c r="E5">
         <v>-2722.872</v>
@@ -1703,37 +1703,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M5">
-        <v>5.90037071819985</v>
+        <v>5.75512871819985</v>
       </c>
       <c r="N5">
-        <v>48.42462928180014</v>
+        <v>48.56987128180014</v>
       </c>
       <c r="O5">
-        <v>12.10615732045003</v>
+        <v>12.14246782045003</v>
       </c>
       <c r="P5">
-        <v>36.3184719613501</v>
+        <v>36.4274034613501</v>
       </c>
       <c r="Q5">
-        <v>404.6184719613501</v>
+        <v>404.7274034613501</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.0888568957748711</v>
+        <v>0.08883678778004873</v>
       </c>
       <c r="T5">
         <v>0.8388670981641202</v>
       </c>
       <c r="U5">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04570246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>9.207048606697386</v>
+        <v>9.439406598883567</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08750108541434326</v>
+        <v>0.08741562978973072</v>
       </c>
       <c r="C6">
-        <v>2557.340354814581</v>
+        <v>2560.598342830819</v>
       </c>
       <c r="D6">
-        <v>2052.844354814581</v>
+        <v>2056.102342830819</v>
       </c>
       <c r="E6">
         <v>-2690.596</v>
@@ -1785,37 +1785,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M6">
-        <v>8.060816957599799</v>
+        <v>7.776788157599801</v>
       </c>
       <c r="N6">
-        <v>46.26418304240019</v>
+        <v>46.54821184240019</v>
       </c>
       <c r="O6">
-        <v>11.56604576060005</v>
+        <v>11.63705296060005</v>
       </c>
       <c r="P6">
-        <v>34.69813728180014</v>
+        <v>34.91115888180014</v>
       </c>
       <c r="Q6">
-        <v>402.9981372818002</v>
+        <v>403.2111588818001</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08919581970257004</v>
+        <v>0.08917555342693198</v>
       </c>
       <c r="T6">
         <v>0.8454702711660418</v>
       </c>
       <c r="U6">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>6.739391340325867</v>
+        <v>6.985531674398426</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08745865805215451</v>
+        <v>0.08734175155790717</v>
       </c>
       <c r="C7">
-        <v>2527.155079168922</v>
+        <v>2531.978934087565</v>
       </c>
       <c r="D7">
-        <v>2054.935079168923</v>
+        <v>2059.758934087566</v>
       </c>
       <c r="E7">
         <v>-2658.32</v>
@@ -1867,37 +1867,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M7">
-        <v>10.30195319699975</v>
+        <v>9.882365196999752</v>
       </c>
       <c r="N7">
-        <v>44.02304680300023</v>
+        <v>44.44263480300024</v>
       </c>
       <c r="O7">
-        <v>11.00576170075006</v>
+        <v>11.11065870075006</v>
       </c>
       <c r="P7">
-        <v>33.01728510225018</v>
+        <v>33.33197610225018</v>
       </c>
       <c r="Q7">
-        <v>401.3172851022502</v>
+        <v>401.6319761022502</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08954187887085209</v>
+        <v>0.08952145098217068</v>
       </c>
       <c r="T7">
         <v>0.8522124583364249</v>
       </c>
       <c r="U7">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>5.273271870019863</v>
+        <v>5.497165801613247</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08749123068996577</v>
+        <v>0.0872378733260836</v>
       </c>
       <c r="C8">
-        <v>2493.273593915749</v>
+        <v>2504.86642581341</v>
       </c>
       <c r="D8">
-        <v>2053.329593915749</v>
+        <v>2064.92242581341</v>
       </c>
       <c r="E8">
         <v>-2626.044</v>
@@ -1949,45 +1949,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M8">
-        <v>12.8658494363997</v>
+        <v>11.8588382363997</v>
       </c>
       <c r="N8">
-        <v>41.45915056360029</v>
+        <v>42.46616176360029</v>
       </c>
       <c r="O8">
-        <v>10.36478764090007</v>
+        <v>10.61654044090007</v>
       </c>
       <c r="P8">
-        <v>31.09436292270022</v>
+        <v>31.84962132270022</v>
       </c>
       <c r="Q8">
-        <v>399.3943629227002</v>
+        <v>400.1496213227002</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08989530100016142</v>
+        <v>0.08987470805986125</v>
       </c>
       <c r="T8">
         <v>0.8590980962976672</v>
       </c>
       <c r="U8">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.222418447265925</v>
+        <v>4.580971501344373</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08781480332777704</v>
+        <v>0.08744899509426005</v>
       </c>
       <c r="C9">
-        <v>2445.184089617847</v>
+        <v>2462.123184702351</v>
       </c>
       <c r="D9">
-        <v>2037.516089617848</v>
+        <v>2054.455184702351</v>
       </c>
       <c r="E9">
         <v>-2593.768</v>
@@ -2031,45 +2031,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M9">
-        <v>16.68205447579965</v>
+        <v>15.19090327579965</v>
       </c>
       <c r="N9">
-        <v>37.64294552420034</v>
+        <v>39.13409672420033</v>
       </c>
       <c r="O9">
-        <v>9.410736381050084</v>
+        <v>9.783524181050083</v>
       </c>
       <c r="P9">
-        <v>28.23220914315025</v>
+        <v>29.35057254315025</v>
       </c>
       <c r="Q9">
-        <v>396.5322091431503</v>
+        <v>397.6505725431502</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09025632360536989</v>
+        <v>0.09023556206395378</v>
       </c>
       <c r="T9">
         <v>0.8661318124946352</v>
       </c>
       <c r="U9">
-        <v>0.07383661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.05537746249690056</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>3.256493382083619</v>
+        <v>3.576153373745993</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08836337596558831</v>
+        <v>0.08755811686243652</v>
       </c>
       <c r="C10">
-        <v>2386.647823590824</v>
+        <v>2424.478509119288</v>
       </c>
       <c r="D10">
-        <v>2011.255823590824</v>
+        <v>2049.086509119289</v>
       </c>
       <c r="E10">
         <v>-2561.492</v>
@@ -2113,45 +2113,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M10">
-        <v>21.4665395151996</v>
+        <v>18.0840147151996</v>
       </c>
       <c r="N10">
-        <v>32.85846048480039</v>
+        <v>36.24098528480039</v>
       </c>
       <c r="O10">
-        <v>8.214615121200097</v>
+        <v>9.060246321200097</v>
       </c>
       <c r="P10">
-        <v>24.64384536360029</v>
+        <v>27.18073896360029</v>
       </c>
       <c r="Q10">
-        <v>392.9438453636003</v>
+        <v>395.4807389636003</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09062519452808289</v>
+        <v>0.09060426072030919</v>
       </c>
       <c r="T10">
         <v>0.8733184355654504</v>
       </c>
       <c r="U10">
-        <v>0.08313661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.06235246249690056</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.530682691615695</v>
+        <v>3.004034273116349</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08874094860339957</v>
+        <v>0.08830998863061296</v>
       </c>
       <c r="C11">
-        <v>2336.687184771124</v>
+        <v>2355.96043175377</v>
       </c>
       <c r="D11">
-        <v>1993.571184771124</v>
+        <v>2012.84443175377</v>
       </c>
       <c r="E11">
         <v>-2529.216</v>
@@ -2195,37 +2195,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M11">
-        <v>25.51513175459955</v>
+        <v>23.74317935459955</v>
       </c>
       <c r="N11">
-        <v>28.80986824540044</v>
+        <v>30.58182064540044</v>
       </c>
       <c r="O11">
-        <v>7.202467061350109</v>
+        <v>7.645455161350109</v>
       </c>
       <c r="P11">
-        <v>21.60740118405033</v>
+        <v>22.93636548405033</v>
       </c>
       <c r="Q11">
-        <v>389.9074011840503</v>
+        <v>391.2363654840503</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09100217250404231</v>
+        <v>0.09098106264383725</v>
       </c>
       <c r="T11">
         <v>0.8806630063960635</v>
       </c>
       <c r="U11">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>2.129128727317152</v>
+        <v>2.288025507817094</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09005902124121082</v>
+        <v>0.08835986039878939</v>
       </c>
       <c r="C12">
-        <v>2245.040878865464</v>
+        <v>2321.325774795429</v>
       </c>
       <c r="D12">
-        <v>1934.200878865464</v>
+        <v>2010.485774795428</v>
       </c>
       <c r="E12">
         <v>-2496.94</v>
@@ -2277,45 +2277,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M12">
-        <v>33.61113439399951</v>
+        <v>26.3813103939995</v>
       </c>
       <c r="N12">
-        <v>20.71386560600048</v>
+        <v>27.94368960600049</v>
       </c>
       <c r="O12">
-        <v>5.17846640150012</v>
+        <v>6.985922401500122</v>
       </c>
       <c r="P12">
-        <v>15.53539920450036</v>
+        <v>20.95776720450036</v>
       </c>
       <c r="Q12">
-        <v>383.8353992045004</v>
+        <v>389.2577672045004</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.0913875277683564</v>
+        <v>0.0913662379434437</v>
       </c>
       <c r="T12">
         <v>0.8881707899118014</v>
       </c>
       <c r="U12">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>1.616279872115785</v>
+        <v>2.059222957035385</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09623954206212385</v>
+        <v>0.08958123216696584</v>
       </c>
       <c r="C13">
-        <v>1975.760966559268</v>
+        <v>2232.962943883706</v>
       </c>
       <c r="D13">
-        <v>1697.196966559268</v>
+        <v>1954.398943883705</v>
       </c>
       <c r="E13">
         <v>-2464.664</v>
@@ -2359,45 +2359,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M13">
-        <v>60.19160223339945</v>
+        <v>34.06095263339945</v>
       </c>
       <c r="N13">
-        <v>-5.866602233399462</v>
+        <v>20.26404736660054</v>
       </c>
       <c r="O13">
-        <v>-1.466650558349865</v>
+        <v>5.066011841650134</v>
       </c>
       <c r="P13">
-        <v>-4.399951675049596</v>
+        <v>15.1980355249504</v>
       </c>
       <c r="Q13">
-        <v>363.9000483249504</v>
+        <v>383.4980355249504</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09190827209639593</v>
+        <v>0.09176006886776042</v>
       </c>
       <c r="T13">
-        <v>0.8983163258471368</v>
+        <v>0.8958472876638482</v>
       </c>
       <c r="U13">
-        <v>0.1695366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V13">
-        <v>0.2256336348605114</v>
+        <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.1312834536030134</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>0.9025345394420458</v>
+        <v>1.59493483886678</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09747690822874917</v>
+        <v>0.09532691692515077</v>
       </c>
       <c r="C14">
-        <v>1902.846813533092</v>
+        <v>1973.954473533167</v>
       </c>
       <c r="D14">
-        <v>1656.558813533092</v>
+        <v>1727.666473533167</v>
       </c>
       <c r="E14">
         <v>-2432.388</v>
@@ -2441,37 +2441,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M14">
-        <v>65.6635660727994</v>
+        <v>59.1567244727994</v>
       </c>
       <c r="N14">
-        <v>-11.33856607279941</v>
+        <v>-4.831724472799415</v>
       </c>
       <c r="O14">
-        <v>-2.834641518199852</v>
+        <v>-1.207931118199854</v>
       </c>
       <c r="P14">
-        <v>-8.503924554599557</v>
+        <v>-3.623793354599561</v>
       </c>
       <c r="Q14">
-        <v>359.7960754454004</v>
+        <v>364.6762066454004</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09243222973385497</v>
+        <v>0.09227996688885678</v>
       </c>
       <c r="T14">
-        <v>0.9085244659135815</v>
+        <v>0.9059810677806942</v>
       </c>
       <c r="U14">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V14">
-        <v>0.2068308319554688</v>
+        <v>0.229580831613568</v>
       </c>
       <c r="W14">
-        <v>0.1344712171913068</v>
+        <v>0.1176712171913068</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.8273233278218753</v>
+        <v>0.9183233264542721</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1057461489271499</v>
+        <v>0.09639628309177613</v>
       </c>
       <c r="C15">
-        <v>1642.057659555353</v>
+        <v>1905.163774011502</v>
       </c>
       <c r="D15">
-        <v>1428.045659555353</v>
+        <v>1691.151774011502</v>
       </c>
       <c r="E15">
         <v>-2400.112</v>
@@ -2523,45 +2523,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M15">
-        <v>93.03802351219937</v>
+        <v>64.08645151219936</v>
       </c>
       <c r="N15">
-        <v>-38.71302351219938</v>
+        <v>-9.761451512199372</v>
       </c>
       <c r="O15">
-        <v>-9.678255878049846</v>
+        <v>-2.440362878049843</v>
       </c>
       <c r="P15">
-        <v>-29.03476763414954</v>
+        <v>-7.321088634149529</v>
       </c>
       <c r="Q15">
-        <v>339.2652323658505</v>
+        <v>360.9789113658505</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09325084677881354</v>
+        <v>0.09281421938183215</v>
       </c>
       <c r="T15">
-        <v>0.9244733840288737</v>
+        <v>0.9163946432724264</v>
       </c>
       <c r="U15">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V15">
-        <v>0.1459752635245867</v>
+        <v>0.2119207676432935</v>
       </c>
       <c r="W15">
-        <v>0.1893685556121704</v>
+        <v>0.1203685556121704</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y15">
-        <v>0.5839010540983468</v>
+        <v>0.847683070573174</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1075055150937753</v>
+        <v>0.1053283226849624</v>
       </c>
       <c r="C16">
-        <v>1569.064793096988</v>
+        <v>1619.135712434033</v>
       </c>
       <c r="D16">
-        <v>1387.328793096988</v>
+        <v>1437.399712434033</v>
       </c>
       <c r="E16">
         <v>-2367.836</v>
@@ -2605,37 +2605,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M16">
-        <v>100.1947945515993</v>
+        <v>93.41683455159931</v>
       </c>
       <c r="N16">
-        <v>-45.86979455159933</v>
+        <v>-39.09183455159932</v>
       </c>
       <c r="O16">
-        <v>-11.46744863789983</v>
+        <v>-9.77295863789983</v>
       </c>
       <c r="P16">
-        <v>-34.40234591369949</v>
+        <v>-29.31887591369949</v>
       </c>
       <c r="Q16">
-        <v>333.8976540863005</v>
+        <v>338.9811240863005</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09380260081112533</v>
+        <v>0.09371284219622669</v>
       </c>
       <c r="T16">
-        <v>0.9352230745408374</v>
+        <v>0.9339104745307407</v>
       </c>
       <c r="U16">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V16">
-        <v>0.1355484589871162</v>
+        <v>0.1453833248063904</v>
       </c>
       <c r="W16">
-        <v>0.1916805599729107</v>
+        <v>0.1766805599729107</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.5421938359484649</v>
+        <v>0.5815332992255617</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1092648812604006</v>
+        <v>0.1069376888515878</v>
       </c>
       <c r="C17">
-        <v>1498.329423252032</v>
+        <v>1549.022127982258</v>
       </c>
       <c r="D17">
-        <v>1348.869423252031</v>
+        <v>1399.562127982258</v>
       </c>
       <c r="E17">
         <v>-2335.56</v>
@@ -2687,37 +2687,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M17">
-        <v>107.3515655909993</v>
+        <v>100.0894655909993</v>
       </c>
       <c r="N17">
-        <v>-53.02656559099927</v>
+        <v>-45.76446559099927</v>
       </c>
       <c r="O17">
-        <v>-13.25664139774982</v>
+        <v>-11.44111639774982</v>
       </c>
       <c r="P17">
-        <v>-39.76992419324945</v>
+        <v>-34.32334919324945</v>
       </c>
       <c r="Q17">
-        <v>328.5300758067506</v>
+        <v>333.9766508067506</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09436733729125621</v>
+        <v>0.09427652269265288</v>
       </c>
       <c r="T17">
-        <v>0.9462256989472001</v>
+        <v>0.9448976565840436</v>
       </c>
       <c r="U17">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V17">
-        <v>0.1265118950546418</v>
+        <v>0.1356911031526311</v>
       </c>
       <c r="W17">
-        <v>0.1936842970855523</v>
+        <v>0.1786842970855522</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.5060475802185673</v>
+        <v>0.5427644126105242</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1159194133400486</v>
+        <v>0.1085470550182131</v>
       </c>
       <c r="C18">
-        <v>1338.041872374434</v>
+        <v>1480.84949608119</v>
       </c>
       <c r="D18">
-        <v>1220.857872374434</v>
+        <v>1363.66549608119</v>
       </c>
       <c r="E18">
         <v>-2303.284</v>
@@ -2769,45 +2769,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M18">
-        <v>130.0008166303992</v>
+        <v>106.7620966303992</v>
       </c>
       <c r="N18">
-        <v>-75.6758166303992</v>
+        <v>-52.43709663039921</v>
       </c>
       <c r="O18">
-        <v>-18.9189541575998</v>
+        <v>-13.1092741575998</v>
       </c>
       <c r="P18">
-        <v>-56.7568624727994</v>
+        <v>-39.32782247279941</v>
       </c>
       <c r="Q18">
-        <v>311.5431375272006</v>
+        <v>328.9721775272006</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09505881263165525</v>
+        <v>0.09485362415327971</v>
       </c>
       <c r="T18">
-        <v>0.9596975459490248</v>
+        <v>0.9561464382100441</v>
       </c>
       <c r="U18">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V18">
-        <v>0.1044704975862758</v>
+        <v>0.1272104092055916</v>
       </c>
       <c r="W18">
-        <v>0.2254375670591136</v>
+        <v>0.1804375670591136</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.4178819903451031</v>
+        <v>0.5088416368223665</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1179787795066739</v>
+        <v>0.1162303719764195</v>
       </c>
       <c r="C19">
-        <v>1270.933011333972</v>
+        <v>1299.809916714188</v>
       </c>
       <c r="D19">
-        <v>1186.025011333972</v>
+        <v>1214.901916714188</v>
       </c>
       <c r="E19">
         <v>-2271.008</v>
@@ -2851,37 +2851,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M19">
-        <v>138.1258676697992</v>
+        <v>132.6389476697992</v>
       </c>
       <c r="N19">
-        <v>-83.80086766979917</v>
+        <v>-78.31394766979918</v>
       </c>
       <c r="O19">
-        <v>-20.95021691744979</v>
+        <v>-19.57848691744979</v>
       </c>
       <c r="P19">
-        <v>-62.85065075234938</v>
+        <v>-58.73546075234938</v>
       </c>
       <c r="Q19">
-        <v>305.4493492476506</v>
+        <v>309.5645392476506</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09565229230191613</v>
+        <v>0.09559396997630845</v>
       </c>
       <c r="T19">
-        <v>0.9712601669845551</v>
+        <v>0.9705771563058302</v>
       </c>
       <c r="U19">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V19">
-        <v>0.09832517419884776</v>
+        <v>0.1023926247802427</v>
       </c>
       <c r="W19">
-        <v>0.2269845699769619</v>
+        <v>0.2169845699769619</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.393300696795391</v>
+        <v>0.409570499120971</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1200381456732993</v>
+        <v>0.1181897381430449</v>
       </c>
       <c r="C20">
-        <v>1205.756677429335</v>
+        <v>1234.650281927802</v>
       </c>
       <c r="D20">
-        <v>1153.124677429335</v>
+        <v>1182.018281927802</v>
       </c>
       <c r="E20">
         <v>-2238.732</v>
@@ -2933,37 +2933,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M20">
-        <v>146.2509187091991</v>
+        <v>140.4412387091991</v>
       </c>
       <c r="N20">
-        <v>-91.92591870919912</v>
+        <v>-86.11623870919911</v>
       </c>
       <c r="O20">
-        <v>-22.98147967729978</v>
+        <v>-21.52905967729978</v>
       </c>
       <c r="P20">
-        <v>-68.94443903189935</v>
+        <v>-64.58717903189932</v>
       </c>
       <c r="Q20">
-        <v>299.3555609681007</v>
+        <v>303.7128209681007</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09626024708608585</v>
+        <v>0.09620121351260491</v>
       </c>
       <c r="T20">
-        <v>0.9831048031672937</v>
+        <v>0.9824134630900476</v>
       </c>
       <c r="U20">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V20">
-        <v>0.09286266452113399</v>
+        <v>0.09670414562578482</v>
       </c>
       <c r="W20">
-        <v>0.2283596836817159</v>
+        <v>0.2183596836817159</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.371450658084536</v>
+        <v>0.3868165825031392</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1220975118399246</v>
+        <v>0.1201491043096702</v>
       </c>
       <c r="C21">
-        <v>1142.356386619158</v>
+        <v>1171.223851112985</v>
       </c>
       <c r="D21">
-        <v>1122.000386619158</v>
+        <v>1150.867851112985</v>
       </c>
       <c r="E21">
         <v>-2206.456</v>
@@ -3015,37 +3015,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M21">
-        <v>154.3759697485991</v>
+        <v>148.2435297485991</v>
       </c>
       <c r="N21">
-        <v>-100.0509697485991</v>
+        <v>-93.91852974859907</v>
       </c>
       <c r="O21">
-        <v>-25.01274243714977</v>
+        <v>-23.47963243714977</v>
       </c>
       <c r="P21">
-        <v>-75.0382273114493</v>
+        <v>-70.4388973114493</v>
       </c>
       <c r="Q21">
-        <v>293.2617726885507</v>
+        <v>297.8611026885507</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09688321309949433</v>
+        <v>0.09682345071646423</v>
       </c>
       <c r="T21">
-        <v>0.9952418995026923</v>
+        <v>0.9945420243627643</v>
       </c>
       <c r="U21">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V21">
-        <v>0.08797515586212695</v>
+        <v>0.09161445375074351</v>
       </c>
       <c r="W21">
-        <v>0.2295900485754432</v>
+        <v>0.2195900485754431</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3519006234485078</v>
+        <v>0.366457815002974</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.12415687800655</v>
+        <v>0.1221084704762956</v>
       </c>
       <c r="C22">
-        <v>1080.592105642077</v>
+        <v>1109.397114272727</v>
       </c>
       <c r="D22">
-        <v>1092.512105642076</v>
+        <v>1121.317114272727</v>
       </c>
       <c r="E22">
         <v>-2174.18</v>
@@ -3097,37 +3097,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M22">
-        <v>162.501020787999</v>
+        <v>156.045820787999</v>
       </c>
       <c r="N22">
-        <v>-108.176020787999</v>
+        <v>-101.720820787999</v>
       </c>
       <c r="O22">
-        <v>-27.04400519699976</v>
+        <v>-25.43020519699976</v>
       </c>
       <c r="P22">
-        <v>-81.13201559099926</v>
+        <v>-76.29061559099927</v>
       </c>
       <c r="Q22">
-        <v>287.1679844090007</v>
+        <v>292.0093844090007</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.097521753263238</v>
+        <v>0.09746124385042002</v>
       </c>
       <c r="T22">
-        <v>1.007682423246476</v>
+        <v>1.006973799667299</v>
       </c>
       <c r="U22">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V22">
-        <v>0.0835763980690206</v>
+        <v>0.08703373106320632</v>
       </c>
       <c r="W22">
-        <v>0.2306973769797977</v>
+        <v>0.2206973769797977</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3343055922760824</v>
+        <v>0.3481349242528253</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1262162441731753</v>
+        <v>0.1240678366429209</v>
       </c>
       <c r="C23">
-        <v>1020.338145590339</v>
+        <v>1049.04993062947</v>
       </c>
       <c r="D23">
-        <v>1064.534145590339</v>
+        <v>1093.245930629469</v>
       </c>
       <c r="E23">
         <v>-2141.904</v>
@@ -3179,37 +3179,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M23">
-        <v>170.626071827399</v>
+        <v>163.848111827399</v>
       </c>
       <c r="N23">
-        <v>-116.301071827399</v>
+        <v>-109.523111827399</v>
       </c>
       <c r="O23">
-        <v>-29.07526795684974</v>
+        <v>-27.38077795684974</v>
       </c>
       <c r="P23">
-        <v>-87.22580387054923</v>
+        <v>-82.14233387054922</v>
       </c>
       <c r="Q23">
-        <v>281.0741961294508</v>
+        <v>286.1576661294508</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09817645900074734</v>
+        <v>0.09811518364599496</v>
       </c>
       <c r="T23">
-        <v>1.020437896958457</v>
+        <v>1.019720303460556</v>
       </c>
       <c r="U23">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V23">
-        <v>0.07959656958954343</v>
+        <v>0.08288926767924412</v>
       </c>
       <c r="W23">
-        <v>0.2316992455361185</v>
+        <v>0.2216992455361185</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3183862783581737</v>
+        <v>0.3315570707169765</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1282756103398006</v>
+        <v>0.1260272028095463</v>
       </c>
       <c r="C24">
-        <v>961.4813710605837</v>
+        <v>990.0738960618756</v>
       </c>
       <c r="D24">
-        <v>1037.953371060584</v>
+        <v>1066.545896061876</v>
       </c>
       <c r="E24">
         <v>-2109.628</v>
@@ -3261,37 +3261,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M24">
-        <v>178.7511228667989</v>
+        <v>171.6504028667989</v>
       </c>
       <c r="N24">
-        <v>-124.4261228667989</v>
+        <v>-117.3254028667989</v>
       </c>
       <c r="O24">
-        <v>-31.10653071669973</v>
+        <v>-29.33135071669973</v>
       </c>
       <c r="P24">
-        <v>-93.3195921500992</v>
+        <v>-87.99405215009919</v>
       </c>
       <c r="Q24">
-        <v>274.9804078499008</v>
+        <v>280.3059478499008</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09884795206485948</v>
+        <v>0.09878589112863592</v>
       </c>
       <c r="T24">
-        <v>1.03352043409895</v>
+        <v>1.032793640684409</v>
       </c>
       <c r="U24">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V24">
-        <v>0.07597854369910964</v>
+        <v>0.07912157369382393</v>
       </c>
       <c r="W24">
-        <v>0.2326100351327738</v>
+        <v>0.2226100351327737</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3039141747964386</v>
+        <v>0.3164862947752958</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1303349765064259</v>
+        <v>0.1279865689761716</v>
       </c>
       <c r="C25">
-        <v>903.9196710671099</v>
+        <v>932.3709440680209</v>
       </c>
       <c r="D25">
-        <v>1012.66767106711</v>
+        <v>1041.118944068021</v>
       </c>
       <c r="E25">
         <v>-2077.352</v>
@@ -3343,37 +3343,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M25">
-        <v>186.8761739061989</v>
+        <v>179.4526939061988</v>
       </c>
       <c r="N25">
-        <v>-132.5511739061989</v>
+        <v>-125.1276939061989</v>
       </c>
       <c r="O25">
-        <v>-33.13779347654972</v>
+        <v>-31.28192347654971</v>
       </c>
       <c r="P25">
-        <v>-99.41338042964915</v>
+        <v>-93.84577042964915</v>
       </c>
       <c r="Q25">
-        <v>268.8866195703508</v>
+        <v>274.4542295703509</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09953688650726025</v>
+        <v>0.09947401958485198</v>
       </c>
       <c r="T25">
-        <v>1.046942777398936</v>
+        <v>1.046206545108882</v>
       </c>
       <c r="U25">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V25">
-        <v>0.07267512875567009</v>
+        <v>0.07568150527235333</v>
       </c>
       <c r="W25">
-        <v>0.2334416256340677</v>
+        <v>0.2234416256340677</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2907005150226804</v>
+        <v>0.3027260210894134</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1323943426730513</v>
+        <v>0.1299459351427969</v>
       </c>
       <c r="C26">
-        <v>847.560648141411</v>
+        <v>875.8521421908089</v>
       </c>
       <c r="D26">
-        <v>988.584648141411</v>
+        <v>1016.876142190809</v>
       </c>
       <c r="E26">
         <v>-2045.076</v>
@@ -3425,37 +3425,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M26">
-        <v>195.0012249455988</v>
+        <v>187.2549849455988</v>
       </c>
       <c r="N26">
-        <v>-140.6762249455988</v>
+        <v>-132.9299849455988</v>
       </c>
       <c r="O26">
-        <v>-35.1690562363997</v>
+        <v>-33.2324962363997</v>
       </c>
       <c r="P26">
-        <v>-105.5071687091991</v>
+        <v>-99.69748870919909</v>
       </c>
       <c r="Q26">
-        <v>262.7928312908009</v>
+        <v>268.6025112908009</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1002439508034084</v>
+        <v>0.1001802566846527</v>
       </c>
       <c r="T26">
-        <v>1.060718340259448</v>
+        <v>1.05997242070242</v>
       </c>
       <c r="U26">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V26">
-        <v>0.06964699839085051</v>
+        <v>0.07252810921933862</v>
       </c>
       <c r="W26">
-        <v>0.2342039169269204</v>
+        <v>0.2242039169269204</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.278587993563402</v>
+        <v>0.2901124368773544</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1344537088396767</v>
+        <v>0.1319053013094223</v>
       </c>
       <c r="C27">
-        <v>792.320490139749</v>
+        <v>820.4366527707872</v>
       </c>
       <c r="D27">
-        <v>965.6204901397491</v>
+        <v>993.736652770787</v>
       </c>
       <c r="E27">
         <v>-2012.8</v>
@@ -3507,37 +3507,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M27">
-        <v>203.1262759849988</v>
+        <v>195.0572759849988</v>
       </c>
       <c r="N27">
-        <v>-148.8012759849988</v>
+        <v>-140.7322759849988</v>
       </c>
       <c r="O27">
-        <v>-37.20031899624969</v>
+        <v>-35.18306899624969</v>
       </c>
       <c r="P27">
-        <v>-111.6009569887491</v>
+        <v>-105.5492069887491</v>
       </c>
       <c r="Q27">
-        <v>256.6990430112509</v>
+        <v>262.7507930112509</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1009698701474539</v>
+        <v>0.1009053267737814</v>
       </c>
       <c r="T27">
-        <v>1.074861251462908</v>
+        <v>1.074105386311785</v>
       </c>
       <c r="U27">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V27">
-        <v>0.06686111845521649</v>
+        <v>0.06962698485056507</v>
       </c>
       <c r="W27">
-        <v>0.234905224916345</v>
+        <v>0.224905224916345</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2674444738208659</v>
+        <v>0.2785079394022603</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.136513075006302</v>
+        <v>0.1338646674760476</v>
       </c>
       <c r="C28">
-        <v>738.122995723913</v>
+        <v>766.0508324333153</v>
       </c>
       <c r="D28">
-        <v>943.6989957239131</v>
+        <v>971.6268324333153</v>
       </c>
       <c r="E28">
         <v>-1980.524</v>
@@ -3589,37 +3589,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M28">
-        <v>211.2513270243987</v>
+        <v>202.8595670243987</v>
       </c>
       <c r="N28">
-        <v>-156.9263270243987</v>
+        <v>-148.5345670243987</v>
       </c>
       <c r="O28">
-        <v>-39.23158175609969</v>
+        <v>-37.13364175609968</v>
       </c>
       <c r="P28">
-        <v>-117.6947452682991</v>
+        <v>-111.4009252682991</v>
       </c>
       <c r="Q28">
-        <v>250.6052547317009</v>
+        <v>256.8990747317009</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1017154089332303</v>
+        <v>0.1016499933518054</v>
       </c>
       <c r="T28">
-        <v>1.089386403509704</v>
+        <v>1.088620323964647</v>
       </c>
       <c r="U28">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V28">
-        <v>0.06428953697616968</v>
+        <v>0.0669490238947741</v>
       </c>
       <c r="W28">
-        <v>0.2355525861373523</v>
+        <v>0.2255525861373523</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2571581479046787</v>
+        <v>0.2677960955790963</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1385724411729273</v>
+        <v>0.135824033642673</v>
       </c>
       <c r="C29">
-        <v>684.8987296364701</v>
+        <v>712.6274491732881</v>
       </c>
       <c r="D29">
-        <v>922.7507296364701</v>
+        <v>950.4794491732881</v>
       </c>
       <c r="E29">
         <v>-1948.248</v>
@@ -3671,37 +3671,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M29">
-        <v>219.3763780637987</v>
+        <v>210.6618580637987</v>
       </c>
       <c r="N29">
-        <v>-165.0513780637987</v>
+        <v>-156.3368580637987</v>
       </c>
       <c r="O29">
-        <v>-41.26284451594967</v>
+        <v>-39.08421451594967</v>
       </c>
       <c r="P29">
-        <v>-123.788533547849</v>
+        <v>-117.252643547849</v>
       </c>
       <c r="Q29">
-        <v>244.511466452151</v>
+        <v>251.047356452151</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1024813734391649</v>
+        <v>0.102415061753885</v>
       </c>
       <c r="T29">
-        <v>1.104309504927645</v>
+        <v>1.103532931142245</v>
       </c>
       <c r="U29">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V29">
-        <v>0.06190844301408933</v>
+        <v>0.06446943041718987</v>
       </c>
       <c r="W29">
-        <v>0.2361519946753219</v>
+        <v>0.226151994675322</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2476337720563573</v>
+        <v>0.2578777216687594</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1406318073395527</v>
+        <v>0.1377833998092983</v>
       </c>
       <c r="C30">
-        <v>632.584288040202</v>
+        <v>660.1049995025446</v>
       </c>
       <c r="D30">
-        <v>902.712288040202</v>
+        <v>930.2329995025447</v>
       </c>
       <c r="E30">
         <v>-1915.972</v>
@@ -3753,37 +3753,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M30">
-        <v>227.5014291031986</v>
+        <v>218.4641491031986</v>
       </c>
       <c r="N30">
-        <v>-173.1764291031986</v>
+        <v>-164.1391491031986</v>
       </c>
       <c r="O30">
-        <v>-43.29410727579966</v>
+        <v>-41.03478727579966</v>
       </c>
       <c r="P30">
-        <v>-129.882321827399</v>
+        <v>-123.104361827399</v>
       </c>
       <c r="Q30">
-        <v>238.417678172601</v>
+        <v>245.195638172601</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1032686147369311</v>
+        <v>0.1032013820560223</v>
       </c>
       <c r="T30">
-        <v>1.119647136940529</v>
+        <v>1.11885977740811</v>
       </c>
       <c r="U30">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V30">
-        <v>0.05969742719215756</v>
+        <v>0.06216695075943309</v>
       </c>
       <c r="W30">
-        <v>0.2367085883177224</v>
+        <v>0.2267085883177224</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2387897087686303</v>
+        <v>0.2486678030377324</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.142691173506178</v>
+        <v>0.1397427659759236</v>
       </c>
       <c r="C31">
-        <v>581.1216575462654</v>
+        <v>608.4271110509017</v>
       </c>
       <c r="D31">
-        <v>883.5256575462653</v>
+        <v>910.8311110509017</v>
       </c>
       <c r="E31">
         <v>-1883.696</v>
@@ -3835,37 +3835,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M31">
-        <v>235.6264801425986</v>
+        <v>226.2664401425986</v>
       </c>
       <c r="N31">
-        <v>-181.3014801425986</v>
+        <v>-171.9414401425986</v>
       </c>
       <c r="O31">
-        <v>-45.32537003564964</v>
+        <v>-42.98536003564964</v>
       </c>
       <c r="P31">
-        <v>-135.9761101069489</v>
+        <v>-128.9560801069489</v>
       </c>
       <c r="Q31">
-        <v>232.3238898930511</v>
+        <v>239.3439198930511</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.104078031845902</v>
+        <v>0.1040098522258254</v>
       </c>
       <c r="T31">
-        <v>1.135416814925607</v>
+        <v>1.134618365822309</v>
       </c>
       <c r="U31">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V31">
-        <v>0.05763889522001421</v>
+        <v>0.06002326280221126</v>
       </c>
       <c r="W31">
-        <v>0.2372267961916814</v>
+        <v>0.2272267961916814</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2305555808800569</v>
+        <v>0.2400930512088451</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1447505396728033</v>
+        <v>0.141702132142549</v>
       </c>
       <c r="C32">
-        <v>530.4576542820823</v>
+        <v>557.5420183995495</v>
       </c>
       <c r="D32">
-        <v>865.1376542820823</v>
+        <v>892.2220183995494</v>
       </c>
       <c r="E32">
         <v>-1851.42</v>
@@ -3917,37 +3917,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M32">
-        <v>243.7515311819985</v>
+        <v>234.0687311819985</v>
       </c>
       <c r="N32">
-        <v>-189.4265311819985</v>
+        <v>-179.7437311819985</v>
       </c>
       <c r="O32">
-        <v>-47.35663279549964</v>
+        <v>-44.93593279549963</v>
       </c>
       <c r="P32">
-        <v>-142.0698983864989</v>
+        <v>-134.8077983864989</v>
       </c>
       <c r="Q32">
-        <v>226.2301016135011</v>
+        <v>233.4922016135011</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1049105751579863</v>
+        <v>0.1048414215433372</v>
       </c>
       <c r="T32">
-        <v>1.15163705513883</v>
+        <v>1.15082719961977</v>
       </c>
       <c r="U32">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V32">
-        <v>0.0557175987126804</v>
+        <v>0.05802248737547089</v>
       </c>
       <c r="W32">
-        <v>0.2377104568740432</v>
+        <v>0.2277104568740432</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2228703948507216</v>
+        <v>0.2320899495018836</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1468099058394287</v>
+        <v>0.1436614983091743</v>
       </c>
       <c r="C33">
-        <v>480.5434315761394</v>
+        <v>507.402101883095</v>
       </c>
       <c r="D33">
-        <v>847.4994315761393</v>
+        <v>874.3581018830949</v>
       </c>
       <c r="E33">
         <v>-1819.144</v>
@@ -3999,37 +3999,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M33">
-        <v>251.8765822213985</v>
+        <v>241.8710222213984</v>
       </c>
       <c r="N33">
-        <v>-197.5515822213985</v>
+        <v>-187.5460222213985</v>
       </c>
       <c r="O33">
-        <v>-49.38789555534962</v>
+        <v>-46.88650555534961</v>
       </c>
       <c r="P33">
-        <v>-148.1636866660488</v>
+        <v>-140.6595166660488</v>
       </c>
       <c r="Q33">
-        <v>220.1363133339512</v>
+        <v>227.6404833339512</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1057672501602759</v>
+        <v>0.1056970943193276</v>
       </c>
       <c r="T33">
-        <v>1.168327447242291</v>
+        <v>1.167505854686723</v>
       </c>
       <c r="U33">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V33">
-        <v>0.05392025681872297</v>
+        <v>0.05615079423432667</v>
       </c>
       <c r="W33">
-        <v>0.2381629136414139</v>
+        <v>0.2281629136414138</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2156810272748919</v>
+        <v>0.2246031769373067</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.148869272006054</v>
+        <v>0.1456208644757996</v>
       </c>
       <c r="C34">
-        <v>431.334046662743</v>
+        <v>457.9634807082421</v>
       </c>
       <c r="D34">
-        <v>830.5660466627429</v>
+        <v>857.1954807082419</v>
       </c>
       <c r="E34">
         <v>-1786.868</v>
@@ -4081,37 +4081,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M34">
-        <v>260.0016332607984</v>
+        <v>249.6733132607984</v>
       </c>
       <c r="N34">
-        <v>-205.6766332607984</v>
+        <v>-195.3483132607984</v>
       </c>
       <c r="O34">
-        <v>-51.4191583151996</v>
+        <v>-48.8370783151996</v>
       </c>
       <c r="P34">
-        <v>-154.2574749455988</v>
+        <v>-146.5112349455988</v>
       </c>
       <c r="Q34">
-        <v>214.0425250544012</v>
+        <v>221.7887650544012</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1066491214861623</v>
+        <v>0.1065779339416706</v>
       </c>
       <c r="T34">
-        <v>1.185508733231148</v>
+        <v>1.184675058432116</v>
       </c>
       <c r="U34">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V34">
-        <v>0.05223524879313789</v>
+        <v>0.05439608191450396</v>
       </c>
       <c r="W34">
-        <v>0.2385870918608239</v>
+        <v>0.2285870918608238</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2089409951725515</v>
+        <v>0.2175843276580158</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1509286381726794</v>
+        <v>0.147580230642425</v>
       </c>
       <c r="C35">
-        <v>382.7880783137232</v>
+        <v>409.1856530695866</v>
       </c>
       <c r="D35">
-        <v>814.2960783137231</v>
+        <v>840.6936530695866</v>
       </c>
       <c r="E35">
         <v>-1754.592</v>
@@ -4163,37 +4163,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M35">
-        <v>268.1266843001983</v>
+        <v>257.4756043001984</v>
       </c>
       <c r="N35">
-        <v>-213.8016843001984</v>
+        <v>-203.1506043001984</v>
       </c>
       <c r="O35">
-        <v>-53.45042107504959</v>
+        <v>-50.7876510750496</v>
       </c>
       <c r="P35">
-        <v>-160.3512632251488</v>
+        <v>-152.3629532251488</v>
       </c>
       <c r="Q35">
-        <v>207.9487367748512</v>
+        <v>215.9370467748512</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1075573173292394</v>
+        <v>0.1074850672840836</v>
       </c>
       <c r="T35">
-        <v>1.203202893428628</v>
+        <v>1.202356775722148</v>
       </c>
       <c r="U35">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V35">
-        <v>0.0506523624660731</v>
+        <v>0.05274771579588262</v>
       </c>
       <c r="W35">
-        <v>0.2389855623093605</v>
+        <v>0.2289855623093605</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2026094498642924</v>
+        <v>0.2109908631835304</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1529880043393047</v>
+        <v>0.1495395968090503</v>
       </c>
       <c r="C36">
-        <v>334.8672885480082</v>
+        <v>361.0311770489675</v>
       </c>
       <c r="D36">
-        <v>798.6512885480083</v>
+        <v>824.8151770489674</v>
       </c>
       <c r="E36">
         <v>-1722.316</v>
@@ -4245,37 +4245,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M36">
-        <v>276.2517353395983</v>
+        <v>265.2778953395983</v>
       </c>
       <c r="N36">
-        <v>-221.9267353395983</v>
+        <v>-210.9528953395983</v>
       </c>
       <c r="O36">
-        <v>-55.48168383489958</v>
+        <v>-52.73822383489959</v>
       </c>
       <c r="P36">
-        <v>-166.4450515046988</v>
+        <v>-158.2146715046987</v>
       </c>
       <c r="Q36">
-        <v>201.8549484953012</v>
+        <v>210.0853284953013</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1084930342584703</v>
+        <v>0.1084196895156606</v>
       </c>
       <c r="T36">
-        <v>1.221433240298759</v>
+        <v>1.220574302627029</v>
       </c>
       <c r="U36">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V36">
-        <v>0.04916258709942388</v>
+        <v>0.05119631239012137</v>
       </c>
       <c r="W36">
-        <v>0.239360593319748</v>
+        <v>0.229360593319748</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1966503483976956</v>
+        <v>0.2047852495604855</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.15504737050593</v>
+        <v>0.1514989629756757</v>
       </c>
       <c r="C37">
-        <v>287.536322602826</v>
+        <v>313.4653870062707</v>
       </c>
       <c r="D37">
-        <v>783.5963226028259</v>
+        <v>809.5253870062708</v>
       </c>
       <c r="E37">
         <v>-1690.04</v>
@@ -4327,37 +4327,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M37">
-        <v>284.3767863789983</v>
+        <v>273.0801863789983</v>
       </c>
       <c r="N37">
-        <v>-230.0517863789983</v>
+        <v>-218.7551863789983</v>
       </c>
       <c r="O37">
-        <v>-57.51294659474958</v>
+        <v>-54.68879659474958</v>
       </c>
       <c r="P37">
-        <v>-172.5388397842488</v>
+        <v>-164.0663897842487</v>
       </c>
       <c r="Q37">
-        <v>195.7611602157513</v>
+        <v>204.2336102157513</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1094575424778314</v>
+        <v>0.1093830693543631</v>
       </c>
       <c r="T37">
-        <v>1.24022452091874</v>
+        <v>1.239352368821291</v>
       </c>
       <c r="U37">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V37">
-        <v>0.04775794175372605</v>
+        <v>0.04973356060754647</v>
       </c>
       <c r="W37">
-        <v>0.2397141939866848</v>
+        <v>0.2297141939866847</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1910317670149042</v>
+        <v>0.1989342424301859</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1571067366725554</v>
+        <v>0.153458329142301</v>
       </c>
       <c r="C38">
-        <v>240.7624422112051</v>
+        <v>266.4561409401183</v>
       </c>
       <c r="D38">
-        <v>769.0984422112051</v>
+        <v>794.7921409401181</v>
       </c>
       <c r="E38">
         <v>-1657.764</v>
@@ -4409,37 +4409,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M38">
-        <v>292.5018374183982</v>
+        <v>280.8824774183982</v>
       </c>
       <c r="N38">
-        <v>-238.1768374183982</v>
+        <v>-226.5574774183982</v>
       </c>
       <c r="O38">
-        <v>-59.54420935459956</v>
+        <v>-56.63936935459955</v>
       </c>
       <c r="P38">
-        <v>-178.6326280637987</v>
+        <v>-169.9181080637987</v>
       </c>
       <c r="Q38">
-        <v>189.6673719362013</v>
+        <v>198.3818919362014</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1104521915790475</v>
+        <v>0.110376554813025</v>
       </c>
       <c r="T38">
-        <v>1.259603029058095</v>
+        <v>1.258717249584123</v>
       </c>
       <c r="U38">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V38">
-        <v>0.046431332260567</v>
+        <v>0.04835207281289241</v>
       </c>
       <c r="W38">
-        <v>0.240048150172125</v>
+        <v>0.230048150172125</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.185725329042268</v>
+        <v>0.1934082912515697</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1591661028391808</v>
+        <v>0.1554176953089264</v>
       </c>
       <c r="C39">
-        <v>194.5152879505631</v>
+        <v>219.9735949434248</v>
       </c>
       <c r="D39">
-        <v>755.127287950563</v>
+        <v>780.5855949434247</v>
       </c>
       <c r="E39">
         <v>-1625.488</v>
@@ -4491,37 +4491,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M39">
-        <v>300.6268884577982</v>
+        <v>288.6847684577982</v>
       </c>
       <c r="N39">
-        <v>-246.3018884577982</v>
+        <v>-234.3597684577982</v>
       </c>
       <c r="O39">
-        <v>-61.57547211444955</v>
+        <v>-58.58994211444954</v>
       </c>
       <c r="P39">
-        <v>-184.7264163433487</v>
+        <v>-175.7698263433486</v>
       </c>
       <c r="Q39">
-        <v>183.5735836566514</v>
+        <v>192.5301736566514</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.111478416842207</v>
+        <v>0.1114015794925969</v>
       </c>
       <c r="T39">
-        <v>1.279596727932033</v>
+        <v>1.278696888466411</v>
       </c>
       <c r="U39">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V39">
-        <v>0.04517643138865978</v>
+        <v>0.04704526003416559</v>
       </c>
       <c r="W39">
-        <v>0.2403640546718658</v>
+        <v>0.2303640546718658</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1807057255546392</v>
+        <v>0.1881810401366624</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1612254690058061</v>
+        <v>0.1573770614755517</v>
       </c>
       <c r="C40">
-        <v>148.7666670316676</v>
+        <v>173.9900014232064</v>
       </c>
       <c r="D40">
-        <v>741.6546670316676</v>
+        <v>766.8780014232065</v>
       </c>
       <c r="E40">
         <v>-1593.212</v>
@@ -4573,37 +4573,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M40">
-        <v>308.7519394971981</v>
+        <v>296.4870594971981</v>
       </c>
       <c r="N40">
-        <v>-254.4269394971981</v>
+        <v>-242.1620594971981</v>
       </c>
       <c r="O40">
-        <v>-63.60673487429953</v>
+        <v>-60.54051487429953</v>
       </c>
       <c r="P40">
-        <v>-190.8202046228986</v>
+        <v>-181.6215446228986</v>
       </c>
       <c r="Q40">
-        <v>177.4797953771014</v>
+        <v>186.6784553771014</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1125377461461136</v>
+        <v>0.1124596694844129</v>
       </c>
       <c r="T40">
-        <v>1.300235384834163</v>
+        <v>1.299321031828773</v>
       </c>
       <c r="U40">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V40">
-        <v>0.04398757793106348</v>
+        <v>0.04580722687537175</v>
       </c>
       <c r="W40">
-        <v>0.2406633326189886</v>
+        <v>0.2306633326189886</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1759503117242539</v>
+        <v>0.183228907501487</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1632848351724314</v>
+        <v>0.159336427642177</v>
       </c>
       <c r="C41">
-        <v>103.4903634064115</v>
+        <v>128.4795282138373</v>
       </c>
       <c r="D41">
-        <v>728.6543634064114</v>
+        <v>753.6435282138372</v>
       </c>
       <c r="E41">
         <v>-1560.936</v>
@@ -4655,37 +4655,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M41">
-        <v>316.876990536598</v>
+        <v>304.289350536598</v>
       </c>
       <c r="N41">
-        <v>-262.5519905365981</v>
+        <v>-249.964350536598</v>
       </c>
       <c r="O41">
-        <v>-65.63799763414951</v>
+        <v>-62.49108763414951</v>
       </c>
       <c r="P41">
-        <v>-196.9139929024485</v>
+        <v>-187.4732629024485</v>
       </c>
       <c r="Q41">
-        <v>171.3860070975515</v>
+        <v>180.8267370975515</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1136318075583449</v>
+        <v>0.1135524509513705</v>
       </c>
       <c r="T41">
-        <v>1.321550719011772</v>
+        <v>1.320621376612851</v>
       </c>
       <c r="U41">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V41">
-        <v>0.04285969131744646</v>
+        <v>0.04463268259651607</v>
       </c>
       <c r="W41">
-        <v>0.2409472629790795</v>
+        <v>0.2309472629790795</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1714387652697859</v>
+        <v>0.1785307303860643</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1653442013390568</v>
+        <v>0.1612957938088024</v>
       </c>
       <c r="C42">
-        <v>58.66196750301583</v>
+        <v>83.41809610257906</v>
       </c>
       <c r="D42">
-        <v>716.1019675030158</v>
+        <v>740.8580961025789</v>
       </c>
       <c r="E42">
         <v>-1528.66</v>
@@ -4737,37 +4737,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M42">
-        <v>325.002041575998</v>
+        <v>312.091641575998</v>
       </c>
       <c r="N42">
-        <v>-270.677041575998</v>
+        <v>-257.7666415759981</v>
       </c>
       <c r="O42">
-        <v>-67.66926039399951</v>
+        <v>-64.44166039399951</v>
       </c>
       <c r="P42">
-        <v>-203.0077811819985</v>
+        <v>-193.3249811819985</v>
       </c>
       <c r="Q42">
-        <v>165.2922188180015</v>
+        <v>174.9750188180015</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1147623376843173</v>
+        <v>0.1146816584672267</v>
       </c>
       <c r="T42">
-        <v>1.343576564328635</v>
+        <v>1.342631732889732</v>
       </c>
       <c r="U42">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V42">
-        <v>0.0417881990345103</v>
+        <v>0.04351686553160316</v>
       </c>
       <c r="W42">
-        <v>0.2412169968211659</v>
+        <v>0.2312169968211659</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1671527961380412</v>
+        <v>0.1740674621264127</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1674035675056821</v>
+        <v>0.1632551599754277</v>
       </c>
       <c r="C43">
-        <v>14.25872326192348</v>
+        <v>38.78323261733431</v>
       </c>
       <c r="D43">
-        <v>703.9747232619235</v>
+        <v>728.4992326173343</v>
       </c>
       <c r="E43">
         <v>-1496.384</v>
@@ -4819,37 +4819,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M43">
-        <v>333.127092615398</v>
+        <v>319.893932615398</v>
       </c>
       <c r="N43">
-        <v>-278.802092615398</v>
+        <v>-265.568932615398</v>
       </c>
       <c r="O43">
-        <v>-69.7005231538495</v>
+        <v>-66.3922331538495</v>
       </c>
       <c r="P43">
-        <v>-209.1015694615485</v>
+        <v>-199.1766994615485</v>
       </c>
       <c r="Q43">
-        <v>159.1984305384515</v>
+        <v>169.1233005384515</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1159311908654075</v>
+        <v>0.1158491442039594</v>
       </c>
       <c r="T43">
-        <v>1.366349048469798</v>
+        <v>1.36538820293871</v>
       </c>
       <c r="U43">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V43">
-        <v>0.04076897466781492</v>
+        <v>0.04245547856741771</v>
       </c>
       <c r="W43">
-        <v>0.2414735729148578</v>
+        <v>0.2314735729148578</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1630758986712597</v>
+        <v>0.1698219142696709</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1694629336723074</v>
+        <v>0.1652145261420531</v>
       </c>
       <c r="C44">
-        <v>-29.74060954438596</v>
+        <v>-5.446059791203197</v>
       </c>
       <c r="D44">
-        <v>692.251390455614</v>
+        <v>716.5459402087965</v>
       </c>
       <c r="E44">
         <v>-1464.108</v>
@@ -4901,37 +4901,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M44">
-        <v>341.2521436547979</v>
+        <v>327.6962236547979</v>
       </c>
       <c r="N44">
-        <v>-286.9271436547979</v>
+        <v>-273.3712236547979</v>
       </c>
       <c r="O44">
-        <v>-71.73178591369948</v>
+        <v>-68.34280591369948</v>
       </c>
       <c r="P44">
-        <v>-215.1953577410985</v>
+        <v>-205.0284177410985</v>
       </c>
       <c r="Q44">
-        <v>153.1046422589015</v>
+        <v>163.2715822589016</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1171403493286041</v>
+        <v>0.1170568880695449</v>
       </c>
       <c r="T44">
-        <v>1.389906790684794</v>
+        <v>1.388929378851447</v>
       </c>
       <c r="U44">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V44">
-        <v>0.03979828479477172</v>
+        <v>0.04144463383962206</v>
       </c>
       <c r="W44">
-        <v>0.2417179310993263</v>
+        <v>0.2317179310993263</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1591931391790868</v>
+        <v>0.1657785353584883</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1715222998389328</v>
+        <v>0.1671738923086784</v>
       </c>
       <c r="C45">
-        <v>-73.35587946014493</v>
+        <v>-49.2894227996112</v>
       </c>
       <c r="D45">
-        <v>680.912120539855</v>
+        <v>704.9785772003888</v>
       </c>
       <c r="E45">
         <v>-1431.832</v>
@@ -4983,37 +4983,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M45">
-        <v>349.3771946941979</v>
+        <v>335.4985146941979</v>
       </c>
       <c r="N45">
-        <v>-295.0521946941979</v>
+        <v>-281.1735146941979</v>
       </c>
       <c r="O45">
-        <v>-73.76304867354948</v>
+        <v>-70.29337867354947</v>
       </c>
       <c r="P45">
-        <v>-221.2891460206484</v>
+        <v>-210.8801360206484</v>
       </c>
       <c r="Q45">
-        <v>147.0108539793516</v>
+        <v>157.4198639793516</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1183919344045446</v>
+        <v>0.1183070089128702</v>
       </c>
       <c r="T45">
-        <v>1.414291120345931</v>
+        <v>1.41329656093656</v>
       </c>
       <c r="U45">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V45">
-        <v>0.03887274328791655</v>
+        <v>0.04048080514567736</v>
       </c>
       <c r="W45">
-        <v>0.2419509237868428</v>
+        <v>0.2319509237868428</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1554909731516663</v>
+        <v>0.1619232205827095</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1735816660055581</v>
+        <v>0.1691332584753037</v>
       </c>
       <c r="C46">
-        <v>-116.6056554901422</v>
+        <v>-92.76524991387419</v>
       </c>
       <c r="D46">
-        <v>669.9383445098578</v>
+        <v>693.7787500861259</v>
       </c>
       <c r="E46">
         <v>-1399.556</v>
@@ -5065,37 +5065,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M46">
-        <v>357.5022457335978</v>
+        <v>343.3008057335978</v>
       </c>
       <c r="N46">
-        <v>-303.1772457335978</v>
+        <v>-288.9758057335978</v>
       </c>
       <c r="O46">
-        <v>-75.79431143339946</v>
+        <v>-72.24395143339946</v>
       </c>
       <c r="P46">
-        <v>-227.3829343001984</v>
+        <v>-216.7318543001984</v>
       </c>
       <c r="Q46">
-        <v>140.9170656998016</v>
+        <v>151.5681456998016</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1196882189474829</v>
+        <v>0.1196017769291715</v>
       </c>
       <c r="T46">
-        <v>1.439546318923537</v>
+        <v>1.438533999524713</v>
       </c>
       <c r="U46">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V46">
-        <v>0.03798927184955482</v>
+        <v>0.03956078684691196</v>
       </c>
       <c r="W46">
-        <v>0.2421733258976539</v>
+        <v>0.2321733258976539</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1519570873982192</v>
+        <v>0.1582431473876479</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1756410321721835</v>
+        <v>0.1710926246419291</v>
       </c>
       <c r="C47">
-        <v>-159.5073285715071</v>
+        <v>-135.8907840658424</v>
       </c>
       <c r="D47">
-        <v>659.3126714284929</v>
+        <v>682.9292159341577</v>
       </c>
       <c r="E47">
         <v>-1367.28</v>
@@ -5147,37 +5147,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M47">
-        <v>365.6272967729978</v>
+        <v>351.1030967729978</v>
       </c>
       <c r="N47">
-        <v>-311.3022967729978</v>
+        <v>-296.7780967729978</v>
       </c>
       <c r="O47">
-        <v>-77.82557419324945</v>
+        <v>-74.19452419324945</v>
       </c>
       <c r="P47">
-        <v>-233.4767225797484</v>
+        <v>-222.5835725797484</v>
       </c>
       <c r="Q47">
-        <v>134.8232774202517</v>
+        <v>145.7164274202516</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1210316411101644</v>
+        <v>0.1209436274187927</v>
       </c>
       <c r="T47">
-        <v>1.465719888358511</v>
+        <v>1.464689163152435</v>
       </c>
       <c r="U47">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V47">
-        <v>0.0371450658084536</v>
+        <v>0.03868165825031392</v>
       </c>
       <c r="W47">
-        <v>0.2423858434702068</v>
+        <v>0.2323858434702068</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1485802632338143</v>
+        <v>0.1547266330012557</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1777003983388088</v>
+        <v>0.1730519908085544</v>
       </c>
       <c r="C48">
-        <v>-202.0772035397958</v>
+        <v>-178.6822061932221</v>
       </c>
       <c r="D48">
-        <v>649.0187964602039</v>
+        <v>672.4137938067779</v>
       </c>
       <c r="E48">
         <v>-1335.004</v>
@@ -5229,37 +5229,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M48">
-        <v>373.7523478123977</v>
+        <v>358.9053878123977</v>
       </c>
       <c r="N48">
-        <v>-319.4273478123977</v>
+        <v>-304.5803878123977</v>
       </c>
       <c r="O48">
-        <v>-79.85683695309943</v>
+        <v>-76.14509695309943</v>
       </c>
       <c r="P48">
-        <v>-239.5705108592983</v>
+        <v>-228.4352908592983</v>
       </c>
       <c r="Q48">
-        <v>128.7294891407017</v>
+        <v>139.8647091407017</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1224248196492415</v>
+        <v>0.1223351760746963</v>
       </c>
       <c r="T48">
-        <v>1.492862849254038</v>
+        <v>1.491813036544146</v>
       </c>
       <c r="U48">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V48">
-        <v>0.03633756437783504</v>
+        <v>0.03784075263617667</v>
       </c>
       <c r="W48">
-        <v>0.2425891211483009</v>
+        <v>0.2325891211483009</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1453502575113402</v>
+        <v>0.1513630105447067</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1797597645054342</v>
+        <v>0.1750113569751798</v>
       </c>
       <c r="C49">
-        <v>-244.3305826122996</v>
+        <v>-221.154715760181</v>
       </c>
       <c r="D49">
-        <v>639.0414173877003</v>
+        <v>662.217284239819</v>
       </c>
       <c r="E49">
         <v>-1302.728</v>
@@ -5311,37 +5311,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M49">
-        <v>381.8773988517977</v>
+        <v>366.7076788517977</v>
       </c>
       <c r="N49">
-        <v>-327.5523988517977</v>
+        <v>-312.3826788517977</v>
       </c>
       <c r="O49">
-        <v>-81.88809971294943</v>
+        <v>-78.09566971294942</v>
       </c>
       <c r="P49">
-        <v>-245.6642991388483</v>
+        <v>-234.2870091388482</v>
       </c>
       <c r="Q49">
-        <v>122.6357008611517</v>
+        <v>134.0129908611518</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1238705709633781</v>
+        <v>0.123779236000634</v>
       </c>
       <c r="T49">
-        <v>1.521030072824869</v>
+        <v>1.519960452327998</v>
       </c>
       <c r="U49">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V49">
-        <v>0.03556442471022153</v>
+        <v>0.03703563023966227</v>
       </c>
       <c r="W49">
-        <v>0.2427837487124335</v>
+        <v>0.2327837487124335</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1422576988408861</v>
+        <v>0.1481425209586491</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1818191306720595</v>
+        <v>0.1769707231418051</v>
       </c>
       <c r="C50">
-        <v>-286.2818412875915</v>
+        <v>-263.3226040612865</v>
       </c>
       <c r="D50">
-        <v>629.3661587124084</v>
+        <v>652.3253959387132</v>
       </c>
       <c r="E50">
         <v>-1270.452</v>
@@ -5393,37 +5393,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M50">
-        <v>390.0024498911976</v>
+        <v>374.5099698911976</v>
       </c>
       <c r="N50">
-        <v>-335.6774498911976</v>
+        <v>-320.1849698911976</v>
       </c>
       <c r="O50">
-        <v>-83.91936247279941</v>
+        <v>-80.04624247279939</v>
       </c>
       <c r="P50">
-        <v>-251.7580874183982</v>
+        <v>-240.1387274183982</v>
       </c>
       <c r="Q50">
-        <v>116.5419125816018</v>
+        <v>128.1612725816018</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1253719280972892</v>
+        <v>0.1252788366929539</v>
       </c>
       <c r="T50">
-        <v>1.550280651148424</v>
+        <v>1.549190461026614</v>
       </c>
       <c r="U50">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V50">
-        <v>0.03482349919542525</v>
+        <v>0.03626405460966931</v>
       </c>
       <c r="W50">
-        <v>0.2429702667947273</v>
+        <v>0.2329702667947273</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.139293996781701</v>
+        <v>0.1450562184386772</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1838784968386848</v>
+        <v>0.1789300893084304</v>
       </c>
       <c r="C51">
-        <v>-327.9444974530734</v>
+        <v>-305.1993210522564</v>
       </c>
       <c r="D51">
-        <v>619.9795025469266</v>
+        <v>642.7246789477433</v>
       </c>
       <c r="E51">
         <v>-1238.176</v>
@@ -5475,37 +5475,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M51">
-        <v>398.1275009305976</v>
+        <v>382.3122609305976</v>
       </c>
       <c r="N51">
-        <v>-343.8025009305976</v>
+        <v>-327.9872609305976</v>
       </c>
       <c r="O51">
-        <v>-85.9506252326494</v>
+        <v>-81.9968152326494</v>
       </c>
       <c r="P51">
-        <v>-257.8518756979482</v>
+        <v>-245.9904456979482</v>
       </c>
       <c r="Q51">
-        <v>110.4481243020518</v>
+        <v>122.3095543020518</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1269321619815498</v>
+        <v>0.1268372452555608</v>
       </c>
       <c r="T51">
-        <v>1.580678310974864</v>
+        <v>1.579566744576155</v>
       </c>
       <c r="U51">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V51">
-        <v>0.03411281553837575</v>
+        <v>0.03552397186253319</v>
       </c>
       <c r="W51">
-        <v>0.2431491718940703</v>
+        <v>0.2331491718940703</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.136451262153503</v>
+        <v>0.1420958874501328</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1859378630053102</v>
+        <v>0.1808894554750558</v>
       </c>
       <c r="C52">
-        <v>-369.3312743991867</v>
+        <v>-346.7975363647456</v>
       </c>
       <c r="D52">
-        <v>610.8687256008134</v>
+        <v>633.4024636352543</v>
       </c>
       <c r="E52">
         <v>-1205.9</v>
@@ -5557,37 +5557,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M52">
-        <v>406.2525519699975</v>
+        <v>390.1145519699975</v>
       </c>
       <c r="N52">
-        <v>-351.9275519699975</v>
+        <v>-335.7895519699975</v>
       </c>
       <c r="O52">
-        <v>-87.98188799249938</v>
+        <v>-83.94738799249939</v>
       </c>
       <c r="P52">
-        <v>-263.9456639774982</v>
+        <v>-251.8421639774982</v>
       </c>
       <c r="Q52">
-        <v>104.3543360225019</v>
+        <v>116.4578360225019</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1285548052211808</v>
+        <v>0.128457990160672</v>
       </c>
       <c r="T52">
-        <v>1.612291877194362</v>
+        <v>1.611158079467678</v>
       </c>
       <c r="U52">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V52">
-        <v>0.03343055922760824</v>
+        <v>0.03481349242528253</v>
       </c>
       <c r="W52">
-        <v>0.2433209207894395</v>
+        <v>0.2333209207894395</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1337222369104329</v>
+        <v>0.1392539697011301</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1879972291719355</v>
+        <v>0.1828488216416811</v>
       </c>
       <c r="C53">
-        <v>-410.4541583580208</v>
+        <v>-388.129195087218</v>
       </c>
       <c r="D53">
-        <v>602.0218416419793</v>
+        <v>624.346804912782</v>
       </c>
       <c r="E53">
         <v>-1173.624</v>
@@ -5639,37 +5639,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M53">
-        <v>414.3776030093975</v>
+        <v>397.9168430093975</v>
       </c>
       <c r="N53">
-        <v>-360.0526030093975</v>
+        <v>-343.5918430093975</v>
       </c>
       <c r="O53">
-        <v>-90.01315075234938</v>
+        <v>-85.89796075234938</v>
       </c>
       <c r="P53">
-        <v>-270.0394522570481</v>
+        <v>-257.6938822570481</v>
       </c>
       <c r="Q53">
-        <v>98.26054774295187</v>
+        <v>110.6061177429519</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1302436787971233</v>
+        <v>0.1301448879190531</v>
       </c>
       <c r="T53">
-        <v>1.645195793055471</v>
+        <v>1.644038856599671</v>
       </c>
       <c r="U53">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V53">
-        <v>0.03277505806628259</v>
+        <v>0.03413087492674758</v>
       </c>
       <c r="W53">
-        <v>0.24348593443401</v>
+        <v>0.23348593443401</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1311002322651303</v>
+        <v>0.1365234997069903</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1900565953385608</v>
+        <v>0.1848081878083065</v>
       </c>
       <c r="C54">
-        <v>-451.324451113491</v>
+        <v>-429.2055688283224</v>
       </c>
       <c r="D54">
-        <v>593.4275488865092</v>
+        <v>615.5464311716776</v>
       </c>
       <c r="E54">
         <v>-1141.348</v>
@@ -5721,37 +5721,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M54">
-        <v>422.5026540487975</v>
+        <v>405.7191340487975</v>
       </c>
       <c r="N54">
-        <v>-368.1776540487975</v>
+        <v>-351.3941340487975</v>
       </c>
       <c r="O54">
-        <v>-92.04441351219937</v>
+        <v>-87.84853351219937</v>
       </c>
       <c r="P54">
-        <v>-276.1332405365981</v>
+        <v>-263.5456005365981</v>
       </c>
       <c r="Q54">
-        <v>92.16675946340189</v>
+        <v>104.7543994634019</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1320029221053967</v>
+        <v>0.1319020730840334</v>
       </c>
       <c r="T54">
-        <v>1.679470705410793</v>
+        <v>1.678289666112165</v>
       </c>
       <c r="U54">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V54">
-        <v>0.03214476848808484</v>
+        <v>0.03347451194738705</v>
       </c>
       <c r="W54">
-        <v>0.2436446013999432</v>
+        <v>0.2336446013999432</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1285790739523394</v>
+        <v>0.1338980477895482</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1921159615051862</v>
+        <v>0.1867675539749318</v>
       </c>
       <c r="C55">
-        <v>-491.9528181686526</v>
+        <v>-470.0373025217598</v>
       </c>
       <c r="D55">
-        <v>585.0751818313473</v>
+        <v>606.9906974782402</v>
       </c>
       <c r="E55">
         <v>-1109.072</v>
@@ -5803,37 +5803,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M55">
-        <v>430.6277050881974</v>
+        <v>413.5214250881974</v>
       </c>
       <c r="N55">
-        <v>-376.3027050881974</v>
+        <v>-359.1964250881974</v>
       </c>
       <c r="O55">
-        <v>-94.07567627204935</v>
+        <v>-89.79910627204934</v>
       </c>
       <c r="P55">
-        <v>-282.227028816148</v>
+        <v>-269.397318816148</v>
       </c>
       <c r="Q55">
-        <v>86.07297118385196</v>
+        <v>98.902681183852</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1338370268310434</v>
+        <v>0.1337340320858213</v>
       </c>
       <c r="T55">
-        <v>1.715204124674853</v>
+        <v>1.713997956880509</v>
       </c>
       <c r="U55">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V55">
-        <v>0.03153826342227192</v>
+        <v>0.03284291738234201</v>
       </c>
       <c r="W55">
-        <v>0.2437972809331996</v>
+        <v>0.2337972809331996</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1261530536890877</v>
+        <v>0.1313716695293681</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1941753276718116</v>
+        <v>0.1887269201415572</v>
       </c>
       <c r="C56">
-        <v>-532.3493329018079</v>
+        <v>-510.6344573813012</v>
       </c>
       <c r="D56">
-        <v>576.9546670981921</v>
+        <v>598.6695426186989</v>
       </c>
       <c r="E56">
         <v>-1076.796</v>
@@ -5885,37 +5885,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M56">
-        <v>438.7527561275974</v>
+        <v>421.3237161275973</v>
       </c>
       <c r="N56">
-        <v>-384.4277561275974</v>
+        <v>-366.9987161275973</v>
       </c>
       <c r="O56">
-        <v>-96.10693903189934</v>
+        <v>-91.74967903189933</v>
       </c>
       <c r="P56">
-        <v>-288.320817095698</v>
+        <v>-275.249037095698</v>
       </c>
       <c r="Q56">
-        <v>79.97918290430198</v>
+        <v>93.05096290430203</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1357508752404139</v>
+        <v>0.1356456414789914</v>
       </c>
       <c r="T56">
-        <v>1.752491170863437</v>
+        <v>1.751258782030085</v>
       </c>
       <c r="U56">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V56">
-        <v>0.03095422150704466</v>
+        <v>0.03223471520859494</v>
       </c>
       <c r="W56">
-        <v>0.2439443056689281</v>
+        <v>0.233944305668928</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1238168860281786</v>
+        <v>0.1289388608343798</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1962346938384369</v>
+        <v>0.1906862863081825</v>
       </c>
       <c r="C57">
-        <v>-572.5235170957724</v>
+        <v>-551.0065503703993</v>
       </c>
       <c r="D57">
-        <v>569.0564829042276</v>
+        <v>590.5734496296008</v>
       </c>
       <c r="E57">
         <v>-1044.52</v>
@@ -5967,37 +5967,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M57">
-        <v>446.8778071669973</v>
+        <v>429.1260071669973</v>
       </c>
       <c r="N57">
-        <v>-392.5528071669973</v>
+        <v>-374.8010071669973</v>
       </c>
       <c r="O57">
-        <v>-98.13820179174932</v>
+        <v>-93.70025179174932</v>
       </c>
       <c r="P57">
-        <v>-294.414605375248</v>
+        <v>-281.100755375248</v>
       </c>
       <c r="Q57">
-        <v>73.88539462475205</v>
+        <v>87.19924462475205</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1377497835790898</v>
+        <v>0.1376422112896356</v>
       </c>
       <c r="T57">
-        <v>1.791435419104846</v>
+        <v>1.790175643852976</v>
       </c>
       <c r="U57">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V57">
-        <v>0.03039141747964386</v>
+        <v>0.03164862947752958</v>
       </c>
       <c r="W57">
-        <v>0.24408598405063</v>
+        <v>0.23408598405063</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1215656699185754</v>
+        <v>0.1265945179101183</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1982940600050622</v>
+        <v>0.1926456524748079</v>
       </c>
       <c r="C58">
-        <v>-612.4843781831673</v>
+        <v>-591.1625905119349</v>
       </c>
       <c r="D58">
-        <v>561.3716218168327</v>
+        <v>582.6934094880652</v>
       </c>
       <c r="E58">
         <v>-1012.244</v>
@@ -6049,37 +6049,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M58">
-        <v>455.0028582063973</v>
+        <v>436.9282982063972</v>
       </c>
       <c r="N58">
-        <v>-400.6778582063973</v>
+        <v>-382.6032982063973</v>
       </c>
       <c r="O58">
-        <v>-100.1694645515993</v>
+        <v>-95.65082455159931</v>
       </c>
       <c r="P58">
-        <v>-300.5083936547979</v>
+        <v>-286.9524736547979</v>
       </c>
       <c r="Q58">
-        <v>67.79160634520207</v>
+        <v>81.34752634520208</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1398395513877055</v>
+        <v>0.139729534273491</v>
       </c>
       <c r="T58">
-        <v>1.832149860448139</v>
+        <v>1.830861453940543</v>
       </c>
       <c r="U58">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V58">
-        <v>0.02984871359607878</v>
+        <v>0.03108347537971655</v>
       </c>
       <c r="W58">
-        <v>0.2442226024901283</v>
+        <v>0.2342226024901282</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1193948543843152</v>
+        <v>0.1243339015188661</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2003534261716876</v>
+        <v>0.1946050186414332</v>
       </c>
       <c r="C59">
-        <v>-652.2404435140322</v>
+        <v>-631.1111123293447</v>
       </c>
       <c r="D59">
-        <v>553.8915564859681</v>
+        <v>575.0208876706554</v>
       </c>
       <c r="E59">
         <v>-979.9679999999996</v>
@@ -6131,37 +6131,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M59">
-        <v>463.1279092457972</v>
+        <v>444.7305892457972</v>
       </c>
       <c r="N59">
-        <v>-408.8029092457973</v>
+        <v>-390.4055892457972</v>
       </c>
       <c r="O59">
-        <v>-102.2007273114493</v>
+        <v>-97.6013973114493</v>
       </c>
       <c r="P59">
-        <v>-306.6021819343479</v>
+        <v>-292.8041919343479</v>
       </c>
       <c r="Q59">
-        <v>61.69781806565209</v>
+        <v>75.49580806565211</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1420265176990474</v>
+        <v>0.1419139420472931</v>
       </c>
       <c r="T59">
-        <v>1.87475799673763</v>
+        <v>1.873439627287998</v>
       </c>
       <c r="U59">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V59">
-        <v>0.02932505195404231</v>
+        <v>0.03053815125024783</v>
       </c>
       <c r="W59">
-        <v>0.2443544273001705</v>
+        <v>0.2343544273001704</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1173002078161692</v>
+        <v>0.1221526050009913</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2024127923383129</v>
+        <v>0.1965643848080585</v>
       </c>
       <c r="C60">
-        <v>-691.7997919198413</v>
+        <v>-670.8602066801034</v>
       </c>
       <c r="D60">
-        <v>546.6082080801585</v>
+        <v>567.5477933198964</v>
       </c>
       <c r="E60">
         <v>-947.692</v>
@@ -6213,37 +6213,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M60">
-        <v>471.2529602851971</v>
+        <v>452.5328802851971</v>
       </c>
       <c r="N60">
-        <v>-416.9279602851971</v>
+        <v>-398.2078802851971</v>
       </c>
       <c r="O60">
-        <v>-104.2319900712993</v>
+        <v>-99.55197007129928</v>
       </c>
       <c r="P60">
-        <v>-312.6959702138979</v>
+        <v>-298.6559102138979</v>
       </c>
       <c r="Q60">
-        <v>55.60402978610216</v>
+        <v>69.64408978610214</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1443176252633105</v>
+        <v>0.1442023692388953</v>
       </c>
       <c r="T60">
-        <v>1.919395091898049</v>
+        <v>1.918045332699617</v>
       </c>
       <c r="U60">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V60">
-        <v>0.02881944761000711</v>
+        <v>0.03001163140110563</v>
       </c>
       <c r="W60">
-        <v>0.2444817064271078</v>
+        <v>0.2344817064271078</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1152777904400284</v>
+        <v>0.1200465256044225</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2044721585049382</v>
+        <v>0.1985237509746838</v>
       </c>
       <c r="C61">
-        <v>-731.1700828195578</v>
+        <v>-710.4175492157394</v>
       </c>
       <c r="D61">
-        <v>539.5139171804419</v>
+        <v>560.2664507842603</v>
       </c>
       <c r="E61">
         <v>-915.4159999999999</v>
@@ -6295,37 +6295,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M61">
-        <v>479.3780113245971</v>
+        <v>460.3351713245971</v>
       </c>
       <c r="N61">
-        <v>-425.0530113245971</v>
+        <v>-406.0101713245971</v>
       </c>
       <c r="O61">
-        <v>-106.2632528311493</v>
+        <v>-101.5025428311493</v>
       </c>
       <c r="P61">
-        <v>-318.7897584934478</v>
+        <v>-304.5076284934478</v>
       </c>
       <c r="Q61">
-        <v>49.51024150655218</v>
+        <v>63.79237150655223</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1467204941721717</v>
+        <v>0.1466024270252098</v>
       </c>
       <c r="T61">
-        <v>1.966209606334587</v>
+        <v>1.964826926180095</v>
       </c>
       <c r="U61">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V61">
-        <v>0.02833098239627817</v>
+        <v>0.02950295968244282</v>
       </c>
       <c r="W61">
-        <v>0.2446046710073692</v>
+        <v>0.2346046710073692</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1133239295851127</v>
+        <v>0.1180118387297713</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2065315246715636</v>
+        <v>0.2004831171413092</v>
       </c>
       <c r="C62">
-        <v>-770.3585830881593</v>
+        <v>-749.790426678838</v>
       </c>
       <c r="D62">
-        <v>532.6014169118405</v>
+        <v>553.1695733211619</v>
       </c>
       <c r="E62">
         <v>-883.1399999999999</v>
@@ -6377,37 +6377,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M62">
-        <v>487.5030623639971</v>
+        <v>468.137462363997</v>
       </c>
       <c r="N62">
-        <v>-433.1780623639971</v>
+        <v>-413.812462363997</v>
       </c>
       <c r="O62">
-        <v>-108.2945155909993</v>
+        <v>-103.4531155909993</v>
       </c>
       <c r="P62">
-        <v>-324.8835467729978</v>
+        <v>-310.3593467729978</v>
       </c>
       <c r="Q62">
-        <v>43.41645322700219</v>
+        <v>57.9406532270022</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.149243506526476</v>
+        <v>0.1491224877008401</v>
       </c>
       <c r="T62">
-        <v>2.015364846492952</v>
+        <v>2.013947599334597</v>
       </c>
       <c r="U62">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V62">
-        <v>0.0278587993563402</v>
+        <v>0.02901124368773544</v>
       </c>
       <c r="W62">
-        <v>0.2447235367682886</v>
+        <v>0.2347235367682886</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1114351974253608</v>
+        <v>0.1160449747509418</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2085908908381889</v>
+        <v>0.2024424833079346</v>
       </c>
       <c r="C63">
-        <v>-809.3721918857871</v>
+        <v>-788.9857612264229</v>
       </c>
       <c r="D63">
-        <v>525.863808114213</v>
+        <v>546.2502387735771</v>
       </c>
       <c r="E63">
         <v>-850.8639999999998</v>
@@ -6459,37 +6459,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M63">
-        <v>495.628113403397</v>
+        <v>475.939753403397</v>
       </c>
       <c r="N63">
-        <v>-441.303113403397</v>
+        <v>-421.614753403397</v>
       </c>
       <c r="O63">
-        <v>-110.3257783508492</v>
+        <v>-105.4036883508493</v>
       </c>
       <c r="P63">
-        <v>-330.9773350525477</v>
+        <v>-316.2110650525477</v>
       </c>
       <c r="Q63">
-        <v>37.32266494745227</v>
+        <v>52.08893494745229</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.151895904129719</v>
+        <v>0.1517717822572719</v>
       </c>
       <c r="T63">
-        <v>2.067040868197899</v>
+        <v>2.065587281368818</v>
       </c>
       <c r="U63">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V63">
-        <v>0.02740209772754774</v>
+        <v>0.02853564952892011</v>
       </c>
       <c r="W63">
-        <v>0.2448385052911451</v>
+        <v>0.2348385052911451</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1096083909101909</v>
+        <v>0.1141425981156804</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2106502570048143</v>
+        <v>0.2044018494745599</v>
       </c>
       <c r="C64">
-        <v>-848.2174636258453</v>
+        <v>-828.0101329503957</v>
       </c>
       <c r="D64">
-        <v>519.2945363741544</v>
+        <v>539.5018670496041</v>
       </c>
       <c r="E64">
         <v>-818.588</v>
@@ -6541,37 +6541,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M64">
-        <v>503.7531644427969</v>
+        <v>483.7420444427969</v>
       </c>
       <c r="N64">
-        <v>-449.4281644427969</v>
+        <v>-429.4170444427969</v>
       </c>
       <c r="O64">
-        <v>-112.3570411106992</v>
+        <v>-107.3542611106992</v>
       </c>
       <c r="P64">
-        <v>-337.0711233320977</v>
+        <v>-322.0627833320977</v>
       </c>
       <c r="Q64">
-        <v>31.22887666790234</v>
+        <v>46.23721666790232</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1546879016068168</v>
+        <v>0.1545605133693053</v>
       </c>
       <c r="T64">
-        <v>2.121436680518897</v>
+        <v>2.11994484140484</v>
       </c>
       <c r="U64">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V64">
-        <v>0.02696012840936149</v>
+        <v>0.02807539711716333</v>
       </c>
       <c r="W64">
-        <v>0.244949765151974</v>
+        <v>0.234949765151974</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.107840513637446</v>
+        <v>0.1123015884686533</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2127096231714396</v>
+        <v>0.2063612156411852</v>
       </c>
       <c r="C65">
-        <v>-886.9006292427969</v>
+        <v>-866.8698007490411</v>
       </c>
       <c r="D65">
-        <v>512.887370757203</v>
+        <v>532.9181992509588</v>
       </c>
       <c r="E65">
         <v>-786.3119999999999</v>
@@ -6623,37 +6623,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M65">
-        <v>511.8782154821969</v>
+        <v>491.5443354821969</v>
       </c>
       <c r="N65">
-        <v>-457.5532154821969</v>
+        <v>-437.2193354821969</v>
       </c>
       <c r="O65">
-        <v>-114.3883038705492</v>
+        <v>-109.3048338705492</v>
       </c>
       <c r="P65">
-        <v>-343.1649116116477</v>
+        <v>-327.9145016116477</v>
       </c>
       <c r="Q65">
-        <v>25.13508838835236</v>
+        <v>40.38549838835235</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1576308178664605</v>
+        <v>0.1574999867036109</v>
       </c>
       <c r="T65">
-        <v>2.178772807019408</v>
+        <v>2.177240647929295</v>
       </c>
       <c r="U65">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V65">
-        <v>0.02653218986318114</v>
+        <v>0.02762975589308138</v>
       </c>
       <c r="W65">
-        <v>0.2450574929537289</v>
+        <v>0.2350574929537289</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1061287594527246</v>
+        <v>0.1105190235723255</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2147689893380649</v>
+        <v>0.2083205818078106</v>
       </c>
       <c r="C66">
-        <v>-925.4276159046958</v>
+        <v>-905.5707216887531</v>
       </c>
       <c r="D66">
-        <v>506.6363840953039</v>
+        <v>526.4932783112466</v>
       </c>
       <c r="E66">
         <v>-754.0360000000001</v>
@@ -6705,37 +6705,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M66">
-        <v>520.0032665215967</v>
+        <v>499.3466265215968</v>
       </c>
       <c r="N66">
-        <v>-465.6782665215968</v>
+        <v>-445.0216265215968</v>
       </c>
       <c r="O66">
-        <v>-116.4195666303992</v>
+        <v>-111.2554066303992</v>
       </c>
       <c r="P66">
-        <v>-349.2586998911976</v>
+        <v>-333.7662198911976</v>
       </c>
       <c r="Q66">
-        <v>19.04130010880243</v>
+        <v>34.53378010880243</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1607372294738622</v>
+        <v>0.1606027641120445</v>
       </c>
       <c r="T66">
-        <v>2.239294273881058</v>
+        <v>2.23771955481622</v>
       </c>
       <c r="U66">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V66">
-        <v>0.02611762439656894</v>
+        <v>0.02719804095725198</v>
       </c>
       <c r="W66">
-        <v>0.245161854261679</v>
+        <v>0.235161854261679</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1044704975862758</v>
+        <v>0.1087921638290079</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2168283555046903</v>
+        <v>0.2102799479744359</v>
       </c>
       <c r="C67">
-        <v>-963.8040653015721</v>
+        <v>-944.1185689818899</v>
       </c>
       <c r="D67">
-        <v>500.5359346984279</v>
+        <v>520.2214310181101</v>
       </c>
       <c r="E67">
         <v>-721.7599999999998</v>
@@ -6787,37 +6787,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M67">
-        <v>528.1283175609968</v>
+        <v>507.1489175609968</v>
       </c>
       <c r="N67">
-        <v>-473.8033175609968</v>
+        <v>-452.8239175609968</v>
       </c>
       <c r="O67">
-        <v>-118.4508293902492</v>
+        <v>-113.2059793902492</v>
       </c>
       <c r="P67">
-        <v>-355.3524881707476</v>
+        <v>-339.6179381707476</v>
       </c>
       <c r="Q67">
-        <v>12.94751182925239</v>
+        <v>28.6820618292524</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1640211503159726</v>
+        <v>0.1638828430866743</v>
       </c>
       <c r="T67">
-        <v>2.303274110277659</v>
+        <v>2.30165439923954</v>
       </c>
       <c r="U67">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V67">
-        <v>0.02571581479046788</v>
+        <v>0.02677960955790964</v>
       </c>
       <c r="W67">
-        <v>0.2452630044524614</v>
+        <v>0.2352630044524614</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1028632591618714</v>
+        <v>0.1071184382316386</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2188877216713156</v>
+        <v>0.2122393141410613</v>
       </c>
       <c r="C68">
-        <v>-1002.035350628254</v>
+        <v>-982.5187486947816</v>
       </c>
       <c r="D68">
-        <v>494.5806493717453</v>
+        <v>514.0972513052183</v>
       </c>
       <c r="E68">
         <v>-689.4839999999999</v>
@@ -6869,37 +6869,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M68">
-        <v>536.2533686003967</v>
+        <v>514.9512086003967</v>
       </c>
       <c r="N68">
-        <v>-481.9283686003967</v>
+        <v>-460.6262086003968</v>
       </c>
       <c r="O68">
-        <v>-120.4820921500992</v>
+        <v>-115.1565521500992</v>
       </c>
       <c r="P68">
-        <v>-361.4462764502975</v>
+        <v>-345.4696564502976</v>
       </c>
       <c r="Q68">
-        <v>6.853723549702465</v>
+        <v>22.83034354970243</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1674982429723247</v>
+        <v>0.1673558678833413</v>
       </c>
       <c r="T68">
-        <v>2.371017466462296</v>
+        <v>2.369350116864233</v>
       </c>
       <c r="U68">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V68">
-        <v>0.02532618123303655</v>
+        <v>0.02637385789794131</v>
       </c>
       <c r="W68">
-        <v>0.2453610894859473</v>
+        <v>0.2353610894859473</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1013047249321462</v>
+        <v>0.1054954315917652</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.220947087837941</v>
+        <v>0.2141986803076866</v>
       </c>
       <c r="C69">
-        <v>-1040.126592369106</v>
+        <v>-1020.77641528933</v>
       </c>
       <c r="D69">
-        <v>488.7654076308939</v>
+        <v>508.1155847106699</v>
       </c>
       <c r="E69">
         <v>-657.2079999999996</v>
@@ -6951,37 +6951,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M69">
-        <v>544.3784196397968</v>
+        <v>522.7534996397967</v>
       </c>
       <c r="N69">
-        <v>-490.0534196397968</v>
+        <v>-468.4284996397967</v>
       </c>
       <c r="O69">
-        <v>-122.5133549099492</v>
+        <v>-117.1071249099492</v>
       </c>
       <c r="P69">
-        <v>-367.5400647298476</v>
+        <v>-351.3213747298475</v>
       </c>
       <c r="Q69">
-        <v>0.7599352701524253</v>
+        <v>16.97862527015246</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1711860685169406</v>
+        <v>0.1710393790313213</v>
       </c>
       <c r="T69">
-        <v>2.442866480597518</v>
+        <v>2.441148605254058</v>
       </c>
       <c r="U69">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V69">
-        <v>0.02494817852806585</v>
+        <v>0.02598021822782278</v>
       </c>
       <c r="W69">
-        <v>0.2454562466079859</v>
+        <v>0.2354562466079859</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.09979271411226343</v>
+        <v>0.1039208729112912</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2230064540045663</v>
+        <v>0.2161580464743119</v>
       </c>
       <c r="C70">
-        <v>-1078.082672982118</v>
+        <v>-1058.896486092098</v>
       </c>
       <c r="D70">
-        <v>483.0853270178821</v>
+        <v>502.2715139079016</v>
       </c>
       <c r="E70">
         <v>-624.9319999999998</v>
@@ -7033,37 +7033,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M70">
-        <v>552.5034706791967</v>
+        <v>530.5557906791967</v>
       </c>
       <c r="N70">
-        <v>-498.1784706791967</v>
+        <v>-476.2307906791967</v>
       </c>
       <c r="O70">
-        <v>-124.5446176697992</v>
+        <v>-119.0576976697992</v>
       </c>
       <c r="P70">
-        <v>-373.6338530093975</v>
+        <v>-357.1730930093975</v>
       </c>
       <c r="Q70">
-        <v>-5.333853009397501</v>
+        <v>11.12690699060249</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.175104383158095</v>
+        <v>0.1749531096260501</v>
       </c>
       <c r="T70">
-        <v>2.51920605811619</v>
+        <v>2.517434499168248</v>
       </c>
       <c r="U70">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V70">
-        <v>0.02458129354971194</v>
+        <v>0.02559815619506068</v>
       </c>
       <c r="W70">
-        <v>0.2455486049911411</v>
+        <v>0.2355486049911411</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.09832517419884779</v>
+        <v>0.1023926247802427</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2250658201711916</v>
+        <v>0.2181174126409373</v>
       </c>
       <c r="C71">
-        <v>-1115.908250570884</v>
+        <v>-1096.883654776261</v>
       </c>
       <c r="D71">
-        <v>477.5357494291164</v>
+        <v>496.560345223739</v>
       </c>
       <c r="E71">
         <v>-592.6559999999995</v>
@@ -7115,37 +7115,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M71">
-        <v>560.6285217185967</v>
+        <v>538.3580817185966</v>
       </c>
       <c r="N71">
-        <v>-506.3035217185968</v>
+        <v>-484.0330817185966</v>
       </c>
       <c r="O71">
-        <v>-126.5758804296492</v>
+        <v>-121.0082704296492</v>
       </c>
       <c r="P71">
-        <v>-379.7276412889476</v>
+        <v>-363.0248112889475</v>
       </c>
       <c r="Q71">
-        <v>-11.42764128894754</v>
+        <v>5.275188711052522</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1792754922922271</v>
+        <v>0.1791193389688259</v>
       </c>
       <c r="T71">
-        <v>2.600470769668326</v>
+        <v>2.598642063657546</v>
       </c>
       <c r="U71">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V71">
-        <v>0.02422504291855669</v>
+        <v>0.02522716842411777</v>
       </c>
       <c r="W71">
-        <v>0.245638286319712</v>
+        <v>0.235638286319712</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.09690017167422671</v>
+        <v>0.1009086736964711</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.227125186337817</v>
+        <v>0.2200767788075626</v>
       </c>
       <c r="C72">
-        <v>-1153.60777162491</v>
+        <v>-1134.742403934102</v>
       </c>
       <c r="D72">
-        <v>472.11222837509</v>
+        <v>490.977596065898</v>
       </c>
       <c r="E72">
         <v>-560.3799999999997</v>
@@ -7197,37 +7197,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M72">
-        <v>568.7535727579966</v>
+        <v>546.1603727579966</v>
       </c>
       <c r="N72">
-        <v>-514.4285727579966</v>
+        <v>-491.8353727579966</v>
       </c>
       <c r="O72">
-        <v>-128.6071431894991</v>
+        <v>-122.9588431894991</v>
       </c>
       <c r="P72">
-        <v>-385.8214295684974</v>
+        <v>-368.8765295684975</v>
       </c>
       <c r="Q72">
-        <v>-17.52142956849741</v>
+        <v>-0.576529568497449</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1837246753686347</v>
+        <v>0.1835633169344534</v>
       </c>
       <c r="T72">
-        <v>2.68715312865727</v>
+        <v>2.685263465779464</v>
       </c>
       <c r="U72">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V72">
-        <v>0.02387897087686303</v>
+        <v>0.02486678030377323</v>
       </c>
       <c r="W72">
-        <v>0.2457254053246094</v>
+        <v>0.2357254053246094</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.09551588350745222</v>
+        <v>0.09946712121509294</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2291845525044423</v>
+        <v>0.2220361449741879</v>
       </c>
       <c r="C73">
-        <v>-1191.185482901503</v>
+        <v>-1172.477016810839</v>
       </c>
       <c r="D73">
-        <v>466.8105170984969</v>
+        <v>485.5189831891611</v>
       </c>
       <c r="E73">
         <v>-528.1039999999998</v>
@@ -7279,37 +7279,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M73">
-        <v>576.8786237973965</v>
+        <v>553.9626637973965</v>
       </c>
       <c r="N73">
-        <v>-522.5536237973965</v>
+        <v>-499.6376637973966</v>
       </c>
       <c r="O73">
-        <v>-130.6384059493491</v>
+        <v>-124.9094159493491</v>
       </c>
       <c r="P73">
-        <v>-391.9152178480474</v>
+        <v>-374.7282478480474</v>
       </c>
       <c r="Q73">
-        <v>-23.61521784804739</v>
+        <v>-6.42824784804742</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1884806986572083</v>
+        <v>0.1883137761390897</v>
       </c>
       <c r="T73">
-        <v>2.779813581369589</v>
+        <v>2.777858757702893</v>
       </c>
       <c r="U73">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V73">
-        <v>0.02354264734338609</v>
+        <v>0.02451654396146657</v>
       </c>
       <c r="W73">
-        <v>0.2458100702730309</v>
+        <v>0.2358100702730309</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.09417058937354428</v>
+        <v>0.0980661758458663</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2312439186710677</v>
+        <v>0.2239955111408133</v>
       </c>
       <c r="C74">
-        <v>-1228.64544251596</v>
+        <v>-1210.091588264322</v>
       </c>
       <c r="D74">
-        <v>461.6265574840398</v>
+        <v>480.1804117356782</v>
       </c>
       <c r="E74">
         <v>-495.828</v>
@@ -7361,37 +7361,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M74">
-        <v>585.0036748367964</v>
+        <v>561.7649548367964</v>
       </c>
       <c r="N74">
-        <v>-530.6786748367965</v>
+        <v>-507.4399548367964</v>
       </c>
       <c r="O74">
-        <v>-132.6696687091991</v>
+        <v>-126.8599887091991</v>
       </c>
       <c r="P74">
-        <v>-398.0090061275974</v>
+        <v>-380.5799661275973</v>
       </c>
       <c r="Q74">
-        <v>-29.70900612759738</v>
+        <v>-12.27996612759728</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1935764378949657</v>
+        <v>0.1934035538583429</v>
       </c>
       <c r="T74">
-        <v>2.879092637847074</v>
+        <v>2.877067999049425</v>
       </c>
       <c r="U74">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V74">
-        <v>0.0232156661302835</v>
+        <v>0.0241760364064462</v>
       </c>
       <c r="W74">
-        <v>0.2458923834173296</v>
+        <v>0.2358923834173295</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.0928626645211339</v>
+        <v>0.09670414562578478</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.233303284837693</v>
+        <v>0.2259548773074386</v>
       </c>
       <c r="C75">
-        <v>-1265.991530300936</v>
+        <v>-1247.590035009549</v>
       </c>
       <c r="D75">
-        <v>456.5564696990641</v>
+        <v>474.9579649904505</v>
       </c>
       <c r="E75">
         <v>-463.5520000000001</v>
@@ -7443,37 +7443,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M75">
-        <v>593.1287258761963</v>
+        <v>569.5672458761964</v>
       </c>
       <c r="N75">
-        <v>-538.8037258761963</v>
+        <v>-515.2422458761964</v>
       </c>
       <c r="O75">
-        <v>-134.7009314690491</v>
+        <v>-128.8105614690491</v>
       </c>
       <c r="P75">
-        <v>-404.1027944071472</v>
+        <v>-386.4316844071473</v>
       </c>
       <c r="Q75">
-        <v>-35.80279440714719</v>
+        <v>-18.1316844071473</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.199049639298483</v>
+        <v>0.1988703521493927</v>
       </c>
       <c r="T75">
-        <v>2.985725698508077</v>
+        <v>2.983626073088292</v>
       </c>
       <c r="U75">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V75">
-        <v>0.02289764330658099</v>
+        <v>0.02384485782553598</v>
       </c>
       <c r="W75">
-        <v>0.2459724414069899</v>
+        <v>0.2359724414069899</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.09159057322632402</v>
+        <v>0.09537943130214388</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2353626510043184</v>
+        <v>0.227914243474064</v>
       </c>
       <c r="C76">
-        <v>-1303.227457490553</v>
+        <v>-1284.976105201857</v>
       </c>
       <c r="D76">
-        <v>451.5965425094474</v>
+        <v>469.8478947981428</v>
       </c>
       <c r="E76">
         <v>-431.2759999999998</v>
@@ -7525,37 +7525,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M76">
-        <v>601.2537769155964</v>
+        <v>577.3695369155963</v>
       </c>
       <c r="N76">
-        <v>-546.9287769155965</v>
+        <v>-523.0445369155964</v>
       </c>
       <c r="O76">
-        <v>-136.7321942288991</v>
+        <v>-130.7611342288991</v>
       </c>
       <c r="P76">
-        <v>-410.1965826866974</v>
+        <v>-392.2834026866973</v>
       </c>
       <c r="Q76">
-        <v>-41.89658268669734</v>
+        <v>-23.98340268669727</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2049438561945784</v>
+        <v>0.2047576733859078</v>
       </c>
       <c r="T76">
-        <v>3.100561302296849</v>
+        <v>3.098380922053227</v>
       </c>
       <c r="U76">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V76">
-        <v>0.02258821569432989</v>
+        <v>0.02352263001708279</v>
       </c>
       <c r="W76">
-        <v>0.2460503356671999</v>
+        <v>0.2360503356671999</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09035286277731946</v>
+        <v>0.09409052006833107</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2374220171709437</v>
+        <v>0.2298736096406893</v>
       </c>
       <c r="C77">
-        <v>-1340.356775780065</v>
+        <v>-1322.25338740806</v>
       </c>
       <c r="D77">
-        <v>446.7432242199352</v>
+        <v>464.8466125919392</v>
       </c>
       <c r="E77">
         <v>-399</v>
@@ -7607,37 +7607,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M77">
-        <v>609.3788279549963</v>
+        <v>585.1718279549963</v>
       </c>
       <c r="N77">
-        <v>-555.0538279549962</v>
+        <v>-530.8468279549963</v>
       </c>
       <c r="O77">
-        <v>-138.7634569887491</v>
+        <v>-132.7117069887491</v>
       </c>
       <c r="P77">
-        <v>-416.2903709662472</v>
+        <v>-398.1351209662473</v>
       </c>
       <c r="Q77">
-        <v>-47.99037096624716</v>
+        <v>-29.83512096624725</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2113096104423616</v>
+        <v>0.2111159803213441</v>
       </c>
       <c r="T77">
-        <v>3.224583754388723</v>
+        <v>3.222316158935356</v>
       </c>
       <c r="U77">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V77">
-        <v>0.02228703948507216</v>
+        <v>0.02320899495018836</v>
       </c>
       <c r="W77">
-        <v>0.2461261527471377</v>
+        <v>0.2361261527471377</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.08914815794028874</v>
+        <v>0.09283597980075331</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.239481383337569</v>
+        <v>0.2318329758073147</v>
       </c>
       <c r="C78">
-        <v>-1377.382885807543</v>
+        <v>-1359.425319010673</v>
       </c>
       <c r="D78">
-        <v>441.9931141924569</v>
+        <v>459.9506809893269</v>
       </c>
       <c r="E78">
         <v>-366.7239999999997</v>
@@ -7689,37 +7689,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M78">
-        <v>617.5038789943962</v>
+        <v>592.9741189943962</v>
       </c>
       <c r="N78">
-        <v>-563.1788789943962</v>
+        <v>-538.6491189943963</v>
       </c>
       <c r="O78">
-        <v>-140.7947197485991</v>
+        <v>-134.6622797485991</v>
       </c>
       <c r="P78">
-        <v>-422.3841592457972</v>
+        <v>-403.9868392457972</v>
       </c>
       <c r="Q78">
-        <v>-54.08415924579714</v>
+        <v>-35.68683924579722</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2182058442107933</v>
+        <v>0.2180041461680668</v>
       </c>
       <c r="T78">
-        <v>3.358941410821587</v>
+        <v>3.35657933222433</v>
       </c>
       <c r="U78">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V78">
-        <v>0.02199378896553174</v>
+        <v>0.02290361343768588</v>
       </c>
       <c r="W78">
-        <v>0.2461999746407614</v>
+        <v>0.2361999746407614</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.08797515586212701</v>
+        <v>0.0916144537507434</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2415407495041944</v>
+        <v>0.23379234197394</v>
       </c>
       <c r="C79">
-        <v>-1414.309045100153</v>
+        <v>-1396.495194086562</v>
       </c>
       <c r="D79">
-        <v>437.3429548998473</v>
+        <v>455.1568059134383</v>
       </c>
       <c r="E79">
         <v>-334.4479999999999</v>
@@ -7771,37 +7771,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M79">
-        <v>625.6289300337962</v>
+        <v>600.7764100337962</v>
       </c>
       <c r="N79">
-        <v>-571.3039300337962</v>
+        <v>-546.4514100337963</v>
       </c>
       <c r="O79">
-        <v>-142.825982508449</v>
+        <v>-136.6128525084491</v>
       </c>
       <c r="P79">
-        <v>-428.4779475253471</v>
+        <v>-409.8385575253472</v>
       </c>
       <c r="Q79">
-        <v>-60.17794752534712</v>
+        <v>-41.53855752534719</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2257017504808278</v>
+        <v>0.2254912829579827</v>
       </c>
       <c r="T79">
-        <v>3.504982341726873</v>
+        <v>3.50251756406017</v>
       </c>
       <c r="U79">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V79">
-        <v>0.02170815534260275</v>
+        <v>0.02260616391252112</v>
       </c>
       <c r="W79">
-        <v>0.2462718790826026</v>
+        <v>0.2362718790826026</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.08683262137041114</v>
+        <v>0.0904246556500844</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2436001156708197</v>
+        <v>0.2357517081405654</v>
       </c>
       <c r="C80">
-        <v>-1451.138375524041</v>
+        <v>-1433.46617079799</v>
       </c>
       <c r="D80">
-        <v>432.7896244759584</v>
+        <v>450.4618292020097</v>
       </c>
       <c r="E80">
         <v>-302.172</v>
@@ -7853,37 +7853,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M80">
-        <v>633.7539810731961</v>
+        <v>608.578701073196</v>
       </c>
       <c r="N80">
-        <v>-579.4289810731962</v>
+        <v>-554.253701073196</v>
       </c>
       <c r="O80">
-        <v>-144.857245268299</v>
+        <v>-138.563425268299</v>
       </c>
       <c r="P80">
-        <v>-434.5717358048971</v>
+        <v>-415.690275804897</v>
       </c>
       <c r="Q80">
-        <v>-66.27173580489711</v>
+        <v>-47.39027580489699</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.233879102775411</v>
+        <v>0.2336590685469819</v>
       </c>
       <c r="T80">
-        <v>3.664299720896277</v>
+        <v>3.661722907881087</v>
       </c>
       <c r="U80">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V80">
-        <v>0.02142984565872323</v>
+        <v>0.02231634129825804</v>
       </c>
       <c r="W80">
-        <v>0.2463419398208068</v>
+        <v>0.2363419398208068</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.08571938263489287</v>
+        <v>0.08926536519303219</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2456594818374451</v>
+        <v>0.2377110743071907</v>
       </c>
       <c r="C81">
-        <v>-1487.873870273644</v>
+        <v>-1470.341278330898</v>
       </c>
       <c r="D81">
-        <v>428.3301297263563</v>
+        <v>445.862721669102</v>
       </c>
       <c r="E81">
         <v>-269.8959999999997</v>
@@ -7935,37 +7935,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M81">
-        <v>641.8790321125962</v>
+        <v>616.3809921125961</v>
       </c>
       <c r="N81">
-        <v>-587.5540321125961</v>
+        <v>-562.0559921125962</v>
       </c>
       <c r="O81">
-        <v>-146.888508028149</v>
+        <v>-140.513998028149</v>
       </c>
       <c r="P81">
-        <v>-440.6655240844471</v>
+        <v>-421.5419940844471</v>
       </c>
       <c r="Q81">
-        <v>-72.36552408444709</v>
+        <v>-53.24199408444713</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.242835250526621</v>
+        <v>0.2426047384777906</v>
       </c>
       <c r="T81">
-        <v>3.838790183796099</v>
+        <v>3.836090665399234</v>
       </c>
       <c r="U81">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V81">
-        <v>0.02115858178962546</v>
+        <v>0.02203385596536869</v>
       </c>
       <c r="W81">
-        <v>0.2464102268694363</v>
+        <v>0.2364102268694363</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.08463432715850194</v>
+        <v>0.08813542386147466</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2477188480040704</v>
+        <v>0.239670440473816</v>
       </c>
       <c r="C82">
-        <v>-1524.51840043328</v>
+        <v>-1507.123423412442</v>
       </c>
       <c r="D82">
-        <v>423.9615995667204</v>
+        <v>441.3565765875578</v>
       </c>
       <c r="E82">
         <v>-237.6199999999999</v>
@@ -8017,37 +8017,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M82">
-        <v>650.004083151996</v>
+        <v>624.1832831519961</v>
       </c>
       <c r="N82">
-        <v>-595.6790831519961</v>
+        <v>-569.8582831519961</v>
       </c>
       <c r="O82">
-        <v>-148.919770787999</v>
+        <v>-142.464570787999</v>
       </c>
       <c r="P82">
-        <v>-446.7593123639971</v>
+        <v>-427.3937123639971</v>
       </c>
       <c r="Q82">
-        <v>-78.45931236399707</v>
+        <v>-59.0937123639971</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.252687013052952</v>
+        <v>0.2524449754016801</v>
       </c>
       <c r="T82">
-        <v>4.030729692985904</v>
+        <v>4.027895198669196</v>
       </c>
       <c r="U82">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V82">
-        <v>0.02089409951725515</v>
+        <v>0.02175843276580158</v>
       </c>
       <c r="W82">
-        <v>0.24647680674185</v>
+        <v>0.23647680674185</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.08357639806902051</v>
+        <v>0.08703373106320622</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2497782141706957</v>
+        <v>0.2416298066404414</v>
       </c>
       <c r="C83">
-        <v>-1561.074721141282</v>
+        <v>-1543.81539643728</v>
       </c>
       <c r="D83">
-        <v>419.6812788587187</v>
+        <v>436.9406035627206</v>
       </c>
       <c r="E83">
         <v>-205.3439999999996</v>
@@ -8099,37 +8099,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M83">
-        <v>658.129134191396</v>
+        <v>631.985574191396</v>
       </c>
       <c r="N83">
-        <v>-603.8041341913961</v>
+        <v>-577.6605741913961</v>
       </c>
       <c r="O83">
-        <v>-150.951033547849</v>
+        <v>-144.415143547849</v>
       </c>
       <c r="P83">
-        <v>-452.8531006435471</v>
+        <v>-433.2454306435471</v>
       </c>
       <c r="Q83">
-        <v>-84.55310064354705</v>
+        <v>-64.94543064354707</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2635758032136337</v>
+        <v>0.2633210267386107</v>
       </c>
       <c r="T83">
-        <v>4.242873361037795</v>
+        <v>4.239889682809681</v>
       </c>
       <c r="U83">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V83">
-        <v>0.02063614767136311</v>
+        <v>0.02148981013906329</v>
       </c>
       <c r="W83">
-        <v>0.2465417426667967</v>
+        <v>0.2365417426667967</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.08254459068545239</v>
+        <v>0.08595924055625304</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2518375803373211</v>
+        <v>0.2435891728070667</v>
       </c>
       <c r="C84">
-        <v>-1597.545477384452</v>
+        <v>-1580.419877229708</v>
       </c>
       <c r="D84">
-        <v>415.4865226155482</v>
+        <v>432.6121227702924</v>
       </c>
       <c r="E84">
         <v>-173.0679999999998</v>
@@ -8181,37 +8181,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M84">
-        <v>666.254185230796</v>
+        <v>639.787865230796</v>
       </c>
       <c r="N84">
-        <v>-611.9291852307961</v>
+        <v>-585.4628652307961</v>
       </c>
       <c r="O84">
-        <v>-152.982296307699</v>
+        <v>-146.365716307699</v>
       </c>
       <c r="P84">
-        <v>-458.946888923097</v>
+        <v>-439.0971489230971</v>
       </c>
       <c r="Q84">
-        <v>-90.64688892309704</v>
+        <v>-70.79714892309704</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2756744589477245</v>
+        <v>0.2754055282240891</v>
       </c>
       <c r="T84">
-        <v>4.478588547762117</v>
+        <v>4.475439109632441</v>
       </c>
       <c r="U84">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V84">
-        <v>0.02038448733390746</v>
+        <v>0.02122773928370886</v>
       </c>
       <c r="W84">
-        <v>0.246605094788696</v>
+        <v>0.236605094788696</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.08153794933562974</v>
+        <v>0.08491095713483532</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2538969465039465</v>
+        <v>0.2455485389736921</v>
       </c>
       <c r="C85">
-        <v>-1633.933209448464</v>
+        <v>-1616.939440466682</v>
       </c>
       <c r="D85">
-        <v>411.3747905515363</v>
+        <v>428.3685595333181</v>
       </c>
       <c r="E85">
         <v>-140.7919999999995</v>
@@ -8263,37 +8263,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M85">
-        <v>674.379236270196</v>
+        <v>647.590156270196</v>
       </c>
       <c r="N85">
-        <v>-620.054236270196</v>
+        <v>-593.265156270196</v>
       </c>
       <c r="O85">
-        <v>-155.013559067549</v>
+        <v>-148.316289067549</v>
       </c>
       <c r="P85">
-        <v>-465.040677202647</v>
+        <v>-444.948867202647</v>
       </c>
       <c r="Q85">
-        <v>-96.74067720264702</v>
+        <v>-76.64886720264701</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2891964859446495</v>
+        <v>0.2889117357666826</v>
       </c>
       <c r="T85">
-        <v>4.742034932924595</v>
+        <v>4.738700233728466</v>
       </c>
       <c r="U85">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V85">
-        <v>0.02013889110096882</v>
+        <v>0.02097198338872441</v>
       </c>
       <c r="W85">
-        <v>0.246666920353441</v>
+        <v>0.236666920353441</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.08055556440387523</v>
+        <v>0.08388793355489754</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2559563126705717</v>
+        <v>0.2475079051403174</v>
       </c>
       <c r="C86">
-        <v>-1670.240358047803</v>
+        <v>-1653.376560784756</v>
       </c>
       <c r="D86">
-        <v>407.3436419521964</v>
+        <v>424.2074392152438</v>
       </c>
       <c r="E86">
         <v>-108.5160000000001</v>
@@ -8345,37 +8345,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M86">
-        <v>682.5042873095958</v>
+        <v>655.3924473095958</v>
       </c>
       <c r="N86">
-        <v>-628.1792873095958</v>
+        <v>-601.0674473095958</v>
       </c>
       <c r="O86">
-        <v>-157.0448218273989</v>
+        <v>-150.2668618273989</v>
       </c>
       <c r="P86">
-        <v>-471.1344654821968</v>
+        <v>-450.8005854821968</v>
       </c>
       <c r="Q86">
-        <v>-102.8344654821968</v>
+        <v>-82.50058548219681</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3044087663161899</v>
+        <v>0.3041062192521001</v>
       </c>
       <c r="T86">
-        <v>5.038412116232379</v>
+        <v>5.034868998336493</v>
       </c>
       <c r="U86">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V86">
-        <v>0.01989914239738586</v>
+        <v>0.02072231691981103</v>
       </c>
       <c r="W86">
-        <v>0.2467272738809302</v>
+        <v>0.2367272738809302</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.07959656958954353</v>
+        <v>0.08288926767924421</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2580156788371971</v>
+        <v>0.2494672713069427</v>
       </c>
       <c r="C87">
-        <v>-1706.469269157024</v>
+        <v>-1689.733617592242</v>
       </c>
       <c r="D87">
-        <v>403.3907308429758</v>
+        <v>420.1263824077584</v>
       </c>
       <c r="E87">
         <v>-76.23999999999978</v>
@@ -8427,37 +8427,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M87">
-        <v>690.6293383489958</v>
+        <v>663.1947383489958</v>
       </c>
       <c r="N87">
-        <v>-636.3043383489958</v>
+        <v>-608.8697383489957</v>
       </c>
       <c r="O87">
-        <v>-159.0760845872489</v>
+        <v>-152.2174345872489</v>
       </c>
       <c r="P87">
-        <v>-477.2282537617468</v>
+        <v>-456.6523037617468</v>
       </c>
       <c r="Q87">
-        <v>-108.9282537617468</v>
+        <v>-88.35230376174678</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3216493507372693</v>
+        <v>0.3213266338689068</v>
       </c>
       <c r="T87">
-        <v>5.374306257314537</v>
+        <v>5.370526931558927</v>
       </c>
       <c r="U87">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V87">
-        <v>0.01966503483976955</v>
+        <v>0.02047852495604855</v>
       </c>
       <c r="W87">
-        <v>0.2467862073254197</v>
+        <v>0.2367862073254197</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.07866013935907834</v>
+        <v>0.08191409982419429</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2600750450038224</v>
+        <v>0.2514266374735681</v>
       </c>
       <c r="C88">
-        <v>-1742.622198563402</v>
+        <v>-1726.012899606237</v>
       </c>
       <c r="D88">
-        <v>399.5138014365978</v>
+        <v>416.1231003937625</v>
       </c>
       <c r="E88">
         <v>-43.96399999999994</v>
@@ -8509,37 +8509,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M88">
-        <v>698.7543893883958</v>
+        <v>670.9970293883957</v>
       </c>
       <c r="N88">
-        <v>-644.4293893883957</v>
+        <v>-616.6720293883957</v>
       </c>
       <c r="O88">
-        <v>-161.1073473470989</v>
+        <v>-154.1680073470989</v>
       </c>
       <c r="P88">
-        <v>-483.3220420412968</v>
+        <v>-462.5040220412968</v>
       </c>
       <c r="Q88">
-        <v>-115.0220420412968</v>
+        <v>-94.20402204129675</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3413528757899314</v>
+        <v>0.3410071077166859</v>
       </c>
       <c r="T88">
-        <v>5.758185275694148</v>
+        <v>5.75413599809885</v>
       </c>
       <c r="U88">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.01943637164395828</v>
+        <v>0.02024040257283868</v>
       </c>
       <c r="W88">
-        <v>0.2468437702246884</v>
+        <v>0.2368437702246884</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.07774548657583324</v>
+        <v>0.08096161029135485</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2621344111704478</v>
+        <v>0.2533860036401934</v>
       </c>
       <c r="C89">
-        <v>-1778.701316159567</v>
+        <v>-1762.216609132724</v>
       </c>
       <c r="D89">
-        <v>395.7106838404325</v>
+        <v>412.1953908672762</v>
       </c>
       <c r="E89">
         <v>-11.6880000000001</v>
@@ -8591,37 +8591,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M89">
-        <v>706.8794404277957</v>
+        <v>678.7993204277956</v>
       </c>
       <c r="N89">
-        <v>-652.5544404277957</v>
+        <v>-624.4743204277956</v>
       </c>
       <c r="O89">
-        <v>-163.1386101069489</v>
+        <v>-156.1185801069489</v>
       </c>
       <c r="P89">
-        <v>-489.4158303208468</v>
+        <v>-468.3557403208467</v>
       </c>
       <c r="Q89">
-        <v>-121.1158303208468</v>
+        <v>-100.0557403208467</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3640877123891569</v>
+        <v>0.3637153467718155</v>
       </c>
       <c r="T89">
-        <v>6.201122604593698</v>
+        <v>6.196761844106454</v>
       </c>
       <c r="U89">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.01921296507333807</v>
+        <v>0.02000775426740376</v>
       </c>
       <c r="W89">
-        <v>0.2469000098389166</v>
+        <v>0.2369000098389165</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.07685186029335223</v>
+        <v>0.08003101706961491</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2641937773370731</v>
+        <v>0.2553453698068188</v>
       </c>
       <c r="C90">
-        <v>-1814.708709993263</v>
+        <v>-1798.346866106518</v>
       </c>
       <c r="D90">
-        <v>391.9792900067365</v>
+        <v>408.3411338934819</v>
       </c>
       <c r="E90">
         <v>20.58800000000019</v>
@@ -8673,37 +8673,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M90">
-        <v>715.0044914671956</v>
+        <v>686.6016114671957</v>
       </c>
       <c r="N90">
-        <v>-660.6794914671957</v>
+        <v>-632.2766114671956</v>
       </c>
       <c r="O90">
-        <v>-165.1698728667989</v>
+        <v>-158.0691528667989</v>
       </c>
       <c r="P90">
-        <v>-495.5096186003968</v>
+        <v>-474.2074586003967</v>
       </c>
       <c r="Q90">
-        <v>-127.2096186003968</v>
+        <v>-105.9074586003967</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3906116884215867</v>
+        <v>0.3902082923361335</v>
       </c>
       <c r="T90">
-        <v>6.717882821643173</v>
+        <v>6.71315866444866</v>
       </c>
       <c r="U90">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.01899463592477741</v>
+        <v>0.01978039342345598</v>
       </c>
       <c r="W90">
-        <v>0.246954971280094</v>
+        <v>0.236954971280094</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.07597854369910961</v>
+        <v>0.079121573693824</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2662531435036985</v>
+        <v>0.2573047359734441</v>
       </c>
       <c r="C91">
-        <v>-1850.646390090124</v>
+        <v>-1834.405711906684</v>
       </c>
       <c r="D91">
-        <v>388.3176099098764</v>
+        <v>404.5582880933159</v>
       </c>
       <c r="E91">
         <v>52.86400000000003</v>
@@ -8755,37 +8755,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M91">
-        <v>723.1295425065956</v>
+        <v>694.4039025065956</v>
       </c>
       <c r="N91">
-        <v>-668.8045425065957</v>
+        <v>-640.0789025065956</v>
       </c>
       <c r="O91">
-        <v>-167.2011356266489</v>
+        <v>-160.0197256266489</v>
       </c>
       <c r="P91">
-        <v>-501.6034068799468</v>
+        <v>-480.0591768799467</v>
       </c>
       <c r="Q91">
-        <v>-133.3034068799467</v>
+        <v>-111.7591768799467</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4219582055508219</v>
+        <v>0.4215181370939639</v>
       </c>
       <c r="T91">
-        <v>7.328599441792554</v>
+        <v>7.323445815762174</v>
       </c>
       <c r="U91">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.01878121304921811</v>
+        <v>0.01955814181195648</v>
       </c>
       <c r="W91">
-        <v>0.2470086976327057</v>
+        <v>0.2370086976327057</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.07512485219687237</v>
+        <v>0.07823256724782601</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2683125096703238</v>
+        <v>0.2592641021400694</v>
       </c>
       <c r="C92">
-        <v>-1886.516292064166</v>
+        <v>-1870.395112961807</v>
       </c>
       <c r="D92">
-        <v>384.7237079358343</v>
+        <v>400.8448870381927</v>
       </c>
       <c r="E92">
         <v>85.14000000000033</v>
@@ -8837,37 +8837,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M92">
-        <v>731.2545935459956</v>
+        <v>702.2061935459956</v>
       </c>
       <c r="N92">
-        <v>-676.9295935459957</v>
+        <v>-647.8811935459955</v>
       </c>
       <c r="O92">
-        <v>-169.2323983864989</v>
+        <v>-161.9702983864989</v>
       </c>
       <c r="P92">
-        <v>-507.6971951594967</v>
+        <v>-485.9108951594966</v>
       </c>
       <c r="Q92">
-        <v>-139.3971951594967</v>
+        <v>-117.6108951594966</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4595740261059041</v>
+        <v>0.4590899508033602</v>
       </c>
       <c r="T92">
-        <v>8.06145938597181</v>
+        <v>8.055790397338392</v>
       </c>
       <c r="U92">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.0185725329042268</v>
+        <v>0.01934082912515696</v>
       </c>
       <c r="W92">
-        <v>0.2470612300663705</v>
+        <v>0.2370612300663704</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.07429013161690712</v>
+        <v>0.07736331650062789</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2703718758369492</v>
+        <v>0.2612234683066948</v>
       </c>
       <c r="C93">
-        <v>-1922.320280529636</v>
+        <v>-1906.316964158527</v>
       </c>
       <c r="D93">
-        <v>381.1957194703645</v>
+        <v>397.1990358414733</v>
       </c>
       <c r="E93">
         <v>117.4160000000002</v>
@@ -8919,37 +8919,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M93">
-        <v>739.3796445853956</v>
+        <v>710.0084845853955</v>
       </c>
       <c r="N93">
-        <v>-685.0546445853956</v>
+        <v>-655.6834845853955</v>
       </c>
       <c r="O93">
-        <v>-171.2636611463489</v>
+        <v>-163.9208711463489</v>
       </c>
       <c r="P93">
-        <v>-513.7909834390467</v>
+        <v>-491.7626134390466</v>
       </c>
       <c r="Q93">
-        <v>-145.4909834390467</v>
+        <v>-123.4626134390466</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5055489178954489</v>
+        <v>0.5050110564481781</v>
       </c>
       <c r="T93">
-        <v>8.957177095524232</v>
+        <v>8.950878219264881</v>
       </c>
       <c r="U93">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.01836843913604848</v>
+        <v>0.01912829254136403</v>
       </c>
       <c r="W93">
-        <v>0.2471126079410536</v>
+        <v>0.2371126079410536</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.07347375654419386</v>
+        <v>0.07651317016545622</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2724312420035745</v>
+        <v>0.2631828344733201</v>
       </c>
       <c r="C94">
-        <v>-1958.060152326831</v>
+        <v>-1942.173092065726</v>
       </c>
       <c r="D94">
-        <v>377.7318476731686</v>
+        <v>393.6189079342742</v>
       </c>
       <c r="E94">
         <v>149.692</v>
@@ -9001,37 +9001,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M94">
-        <v>747.5046956247954</v>
+        <v>717.8107756247954</v>
       </c>
       <c r="N94">
-        <v>-693.1796956247954</v>
+        <v>-663.4857756247955</v>
       </c>
       <c r="O94">
-        <v>-173.2949239061988</v>
+        <v>-165.8714439061989</v>
       </c>
       <c r="P94">
-        <v>-519.8847717185965</v>
+        <v>-497.6143317185966</v>
       </c>
       <c r="Q94">
-        <v>-151.5847717185965</v>
+        <v>-129.3143317185966</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5630175326323803</v>
+        <v>0.5624124385042005</v>
       </c>
       <c r="T94">
-        <v>10.07682423246477</v>
+        <v>10.06973799667299</v>
       </c>
       <c r="U94">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.01816878218891752</v>
+        <v>0.01892037631808833</v>
       </c>
       <c r="W94">
-        <v>0.2471628689054175</v>
+        <v>0.2371628689054175</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.07267512875567017</v>
+        <v>0.07568150527235329</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2744906081701999</v>
+        <v>0.2651422006399455</v>
       </c>
       <c r="C95">
-        <v>-1993.737639573637</v>
+        <v>-1977.96525798592</v>
       </c>
       <c r="D95">
-        <v>374.3303604263634</v>
+        <v>390.1027420140805</v>
       </c>
       <c r="E95">
         <v>181.9680000000003</v>
@@ -9083,37 +9083,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M95">
-        <v>755.6297466641954</v>
+        <v>725.6130666641955</v>
       </c>
       <c r="N95">
-        <v>-701.3047466641954</v>
+        <v>-671.2880666641954</v>
       </c>
       <c r="O95">
-        <v>-175.3261866660488</v>
+        <v>-167.8220166660489</v>
       </c>
       <c r="P95">
-        <v>-525.9785599981465</v>
+        <v>-503.4660499981466</v>
       </c>
       <c r="Q95">
-        <v>-157.6785599981465</v>
+        <v>-135.1660499981465</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6369057515798632</v>
+        <v>0.6362142154333721</v>
       </c>
       <c r="T95">
-        <v>11.5163705513883</v>
+        <v>11.50827199619771</v>
       </c>
       <c r="U95">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.01797341893957432</v>
+        <v>0.01871693141144222</v>
       </c>
       <c r="W95">
-        <v>0.2472120489888274</v>
+        <v>0.2372120489888273</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07189367575829742</v>
+        <v>0.07486772564576893</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2765499743368252</v>
+        <v>0.2671015668065708</v>
       </c>
       <c r="C96">
-        <v>-2029.354412553648</v>
+        <v>-2013.695160844539</v>
       </c>
       <c r="D96">
-        <v>370.9895874463524</v>
+        <v>386.6488391554611</v>
       </c>
       <c r="E96">
         <v>214.2440000000001</v>
@@ -9165,37 +9165,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M96">
-        <v>763.7547977035954</v>
+        <v>733.4153577035953</v>
       </c>
       <c r="N96">
-        <v>-709.4297977035953</v>
+        <v>-679.0903577035954</v>
       </c>
       <c r="O96">
-        <v>-177.3574494258988</v>
+        <v>-169.7725894258988</v>
       </c>
       <c r="P96">
-        <v>-532.0723482776965</v>
+        <v>-509.3177682776965</v>
       </c>
       <c r="Q96">
-        <v>-163.7723482776965</v>
+        <v>-141.0177682776965</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7354233768431738</v>
+        <v>0.7346165846722675</v>
       </c>
       <c r="T96">
-        <v>13.43576564328636</v>
+        <v>13.42631732889733</v>
       </c>
       <c r="U96">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.01778221235511077</v>
+        <v>0.01851781511983113</v>
       </c>
       <c r="W96">
-        <v>0.2472601826874838</v>
+        <v>0.2372601826874838</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07112884942044317</v>
+        <v>0.07407126047932444</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2786093405034505</v>
+        <v>0.2690609329731962</v>
       </c>
       <c r="C97">
-        <v>-2064.91208245102</v>
+        <v>-2049.364439927079</v>
       </c>
       <c r="D97">
-        <v>367.70791754898</v>
+        <v>383.2555600729216</v>
       </c>
       <c r="E97">
         <v>246.5200000000004</v>
@@ -9247,37 +9247,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M97">
-        <v>771.8798487429954</v>
+        <v>741.2176487429954</v>
       </c>
       <c r="N97">
-        <v>-717.5548487429953</v>
+        <v>-686.8926487429953</v>
       </c>
       <c r="O97">
-        <v>-179.3887121857488</v>
+        <v>-171.7231621857488</v>
       </c>
       <c r="P97">
-        <v>-538.1661365572465</v>
+        <v>-515.1694865572465</v>
       </c>
       <c r="Q97">
-        <v>-169.8661365572465</v>
+        <v>-146.8694865572465</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8733480522118091</v>
+        <v>0.8723799016067215</v>
       </c>
       <c r="T97">
-        <v>16.12291877194364</v>
+        <v>16.1115807946768</v>
       </c>
       <c r="U97">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.01759503117242539</v>
+        <v>0.0183228907501487</v>
       </c>
       <c r="W97">
-        <v>0.2473073030451159</v>
+        <v>0.2373073030451159</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07038012468970167</v>
+        <v>0.07329156300059492</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2806687066700759</v>
+        <v>0.2710202991398215</v>
       </c>
       <c r="C98">
-        <v>-2100.412203941433</v>
+        <v>-2084.974677473365</v>
       </c>
       <c r="D98">
-        <v>364.4837960585665</v>
+        <v>379.921322526635</v>
       </c>
       <c r="E98">
         <v>278.7959999999998</v>
@@ -9329,37 +9329,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M98">
-        <v>780.0048997823952</v>
+        <v>749.0199397823951</v>
       </c>
       <c r="N98">
-        <v>-725.6798997823953</v>
+        <v>-694.6949397823951</v>
       </c>
       <c r="O98">
-        <v>-181.4199749455988</v>
+        <v>-173.6737349455988</v>
       </c>
       <c r="P98">
-        <v>-544.2599248367965</v>
+        <v>-521.0212048367963</v>
       </c>
       <c r="Q98">
-        <v>-175.9599248367965</v>
+        <v>-152.7212048367963</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.080235065264759</v>
+        <v>1.0790248770084</v>
       </c>
       <c r="T98">
-        <v>20.1536484649295</v>
+        <v>20.13947599334596</v>
       </c>
       <c r="U98">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.01741174959771263</v>
+        <v>0.01813202730483466</v>
       </c>
       <c r="W98">
-        <v>0.2473534417286307</v>
+        <v>0.2373534417286307</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.06964699839085042</v>
+        <v>0.07252810921933872</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2827280728367012</v>
+        <v>0.2729796653064468</v>
       </c>
       <c r="C99">
-        <v>-2135.856277647936</v>
+        <v>-2120.52740113758</v>
       </c>
       <c r="D99">
-        <v>361.3157223520641</v>
+        <v>376.6445988624192</v>
       </c>
       <c r="E99">
         <v>311.0720000000001</v>
@@ -9411,37 +9411,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M99">
-        <v>788.1299508217952</v>
+        <v>756.8222308217952</v>
       </c>
       <c r="N99">
-        <v>-733.8049508217953</v>
+        <v>-702.4972308217953</v>
       </c>
       <c r="O99">
-        <v>-183.4512377054488</v>
+        <v>-175.6243077054488</v>
       </c>
       <c r="P99">
-        <v>-550.3537131163464</v>
+        <v>-526.8729231163464</v>
       </c>
       <c r="Q99">
-        <v>-182.0537131163464</v>
+        <v>-158.5729231163464</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.425046753686345</v>
+        <v>1.423433169344533</v>
       </c>
       <c r="T99">
-        <v>26.87153128657267</v>
+        <v>26.85263465779461</v>
       </c>
       <c r="U99">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.01723224702454033</v>
+        <v>0.01794509918828997</v>
       </c>
       <c r="W99">
-        <v>0.2473986290990833</v>
+        <v>0.2373986290990833</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.06892898809816128</v>
+        <v>0.07178039675315984</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2847874390033265</v>
+        <v>0.2749390314730722</v>
       </c>
       <c r="C100">
-        <v>-2171.245752469812</v>
+        <v>-2156.024086322068</v>
       </c>
       <c r="D100">
-        <v>358.2022475301877</v>
+        <v>373.4239136779316</v>
       </c>
       <c r="E100">
         <v>343.348</v>
@@ -9493,37 +9493,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M100">
-        <v>796.2550018611952</v>
+        <v>764.6245218611951</v>
       </c>
       <c r="N100">
-        <v>-741.9300018611953</v>
+        <v>-710.2995218611952</v>
       </c>
       <c r="O100">
-        <v>-185.4825004652988</v>
+        <v>-177.5748804652988</v>
       </c>
       <c r="P100">
-        <v>-556.4475013958964</v>
+        <v>-532.7246413958965</v>
       </c>
       <c r="Q100">
-        <v>-188.1475013958964</v>
+        <v>-164.4246413958965</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.114670130529518</v>
+        <v>2.112249754016799</v>
       </c>
       <c r="T100">
-        <v>40.307296929859</v>
+        <v>40.27895198669192</v>
       </c>
       <c r="U100">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.01705640776918788</v>
+        <v>0.0177619859312666</v>
       </c>
       <c r="W100">
-        <v>0.2474428942783022</v>
+        <v>0.2374428942783022</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.06822563107675139</v>
+        <v>0.07104794372506629</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2868468051699519</v>
+        <v>0.2768983976396975</v>
       </c>
       <c r="C101">
-        <v>-2206.582027792079</v>
+        <v>-2191.466158392417</v>
       </c>
       <c r="D101">
-        <v>355.1419722079211</v>
+        <v>370.2578416075831</v>
       </c>
       <c r="E101">
         <v>375.6240000000003</v>
@@ -9575,37 +9575,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M101">
-        <v>804.3800529005952</v>
+        <v>772.4268129005951</v>
       </c>
       <c r="N101">
-        <v>-750.0550529005952</v>
+        <v>-718.1018129005952</v>
       </c>
       <c r="O101">
-        <v>-187.5137632251488</v>
+        <v>-179.5254532251488</v>
       </c>
       <c r="P101">
-        <v>-562.5412896754465</v>
+        <v>-538.5763596754464</v>
       </c>
       <c r="Q101">
-        <v>-194.2412896754465</v>
+        <v>-170.2763596754464</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.183540261059036</v>
+        <v>4.178699508033599</v>
       </c>
       <c r="T101">
-        <v>80.614593859718</v>
+        <v>80.55790397338384</v>
       </c>
       <c r="U101">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V101">
-        <v>0.01688412082202436</v>
+        <v>0.01758257193196087</v>
       </c>
       <c r="W101">
-        <v>0.2474862652114762</v>
+        <v>0.2374862652114762</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.06753648328809736</v>
+        <v>0.07033028772784344</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/belgium/belgium_transportation.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_transportation.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08786114271702496</v>
+        <v>0.0877197644852014</v>
       </c>
       <c r="C2">
-        <v>2667.924043089088</v>
+        <v>2642.508986601059</v>
       </c>
       <c r="D2">
-        <v>2034.324043089088</v>
+        <v>2041.184986601059</v>
       </c>
       <c r="E2">
-        <v>-2819.7</v>
+        <v>-2787.424</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32.276</v>
       </c>
       <c r="G2">
         <v>633.6</v>
@@ -1457,28 +1457,28 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.81509303939995</v>
       </c>
       <c r="N2">
-        <v>54.32499999999999</v>
+        <v>52.50990696060004</v>
       </c>
       <c r="O2">
-        <v>13.58125</v>
+        <v>13.12747674015001</v>
       </c>
       <c r="P2">
-        <v>40.74374999999999</v>
+        <v>39.38243022045003</v>
       </c>
       <c r="Q2">
-        <v>409.04375</v>
+        <v>407.68243022045</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08786114271702496</v>
+        <v>0.08817978773760848</v>
       </c>
       <c r="T2">
-        <v>0.819849959918586</v>
+        <v>0.8260609444634238</v>
       </c>
       <c r="U2">
         <v>0.05623661666253409</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>29.92959524430728</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0877197644852014</v>
+        <v>0.08757838625337784</v>
       </c>
       <c r="C3">
-        <v>2642.508986601059</v>
+        <v>2617.140365035455</v>
       </c>
       <c r="D3">
-        <v>2041.184986601059</v>
+        <v>2048.092365035455</v>
       </c>
       <c r="E3">
-        <v>-2787.424</v>
+        <v>-2755.148</v>
       </c>
       <c r="F3">
-        <v>32.276</v>
+        <v>64.55199999999999</v>
       </c>
       <c r="G3">
         <v>633.6</v>
@@ -1539,28 +1539,28 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M3">
-        <v>1.81509303939995</v>
+        <v>3.6301860787999</v>
       </c>
       <c r="N3">
-        <v>52.50990696060004</v>
+        <v>50.69481392120009</v>
       </c>
       <c r="O3">
-        <v>13.12747674015001</v>
+        <v>12.67370348030002</v>
       </c>
       <c r="P3">
-        <v>39.38243022045003</v>
+        <v>38.02111044090007</v>
       </c>
       <c r="Q3">
-        <v>407.68243022045</v>
+        <v>406.3211104409001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08817978773760848</v>
+        <v>0.08850493571779575</v>
       </c>
       <c r="T3">
-        <v>0.8260609444634238</v>
+        <v>0.8323986837948909</v>
       </c>
       <c r="U3">
         <v>0.05623661666253409</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>29.92959524430728</v>
+        <v>14.96479762215364</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08757838625337784</v>
+        <v>0.0875090080215543</v>
       </c>
       <c r="C4">
-        <v>2617.140365035455</v>
+        <v>2588.271135746089</v>
       </c>
       <c r="D4">
-        <v>2048.092365035455</v>
+        <v>2051.499135746089</v>
       </c>
       <c r="E4">
-        <v>-2755.148</v>
+        <v>-2722.872</v>
       </c>
       <c r="F4">
-        <v>64.55199999999999</v>
+        <v>96.82799999999999</v>
       </c>
       <c r="G4">
         <v>633.6</v>
@@ -1621,45 +1621,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M4">
-        <v>3.6301860787999</v>
+        <v>5.75512871819985</v>
       </c>
       <c r="N4">
-        <v>50.69481392120009</v>
+        <v>48.56987128180014</v>
       </c>
       <c r="O4">
-        <v>12.67370348030002</v>
+        <v>12.14246782045003</v>
       </c>
       <c r="P4">
-        <v>38.02111044090007</v>
+        <v>36.4274034613501</v>
       </c>
       <c r="Q4">
-        <v>406.3211104409001</v>
+        <v>404.7274034613501</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08850493571779575</v>
+        <v>0.08883678778004873</v>
       </c>
       <c r="T4">
-        <v>0.8323986837948909</v>
+        <v>0.8388670981641202</v>
       </c>
       <c r="U4">
-        <v>0.05623661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04217746249690056</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>14.96479762215364</v>
+        <v>9.439406598883567</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0875090080215543</v>
+        <v>0.08741562978973072</v>
       </c>
       <c r="C5">
-        <v>2588.271135746089</v>
+        <v>2560.598342830819</v>
       </c>
       <c r="D5">
-        <v>2051.499135746089</v>
+        <v>2056.102342830819</v>
       </c>
       <c r="E5">
-        <v>-2722.872</v>
+        <v>-2690.596</v>
       </c>
       <c r="F5">
-        <v>96.82799999999999</v>
+        <v>129.104</v>
       </c>
       <c r="G5">
         <v>633.6</v>
@@ -1703,45 +1703,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M5">
-        <v>5.75512871819985</v>
+        <v>7.776788157599801</v>
       </c>
       <c r="N5">
-        <v>48.56987128180014</v>
+        <v>46.54821184240019</v>
       </c>
       <c r="O5">
-        <v>12.14246782045003</v>
+        <v>11.63705296060005</v>
       </c>
       <c r="P5">
-        <v>36.4274034613501</v>
+        <v>34.91115888180014</v>
       </c>
       <c r="Q5">
-        <v>404.7274034613501</v>
+        <v>403.2111588818001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08883678778004873</v>
+        <v>0.08917555342693198</v>
       </c>
       <c r="T5">
-        <v>0.8388670981641202</v>
+        <v>0.8454702711660418</v>
       </c>
       <c r="U5">
-        <v>0.05943661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y5">
-        <v>9.439406598883567</v>
+        <v>6.985531674398426</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08741562978973072</v>
+        <v>0.08734175155790717</v>
       </c>
       <c r="C6">
-        <v>2560.598342830819</v>
+        <v>2531.978934087565</v>
       </c>
       <c r="D6">
-        <v>2056.102342830819</v>
+        <v>2059.758934087566</v>
       </c>
       <c r="E6">
-        <v>-2690.596</v>
+        <v>-2658.32</v>
       </c>
       <c r="F6">
-        <v>129.104</v>
+        <v>161.38</v>
       </c>
       <c r="G6">
         <v>633.6</v>
@@ -1785,45 +1785,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M6">
-        <v>7.776788157599801</v>
+        <v>9.882365196999752</v>
       </c>
       <c r="N6">
-        <v>46.54821184240019</v>
+        <v>44.44263480300024</v>
       </c>
       <c r="O6">
-        <v>11.63705296060005</v>
+        <v>11.11065870075006</v>
       </c>
       <c r="P6">
-        <v>34.91115888180014</v>
+        <v>33.33197610225018</v>
       </c>
       <c r="Q6">
-        <v>403.2111588818001</v>
+        <v>401.6319761022502</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08917555342693198</v>
+        <v>0.08952145098217068</v>
       </c>
       <c r="T6">
-        <v>0.8454702711660418</v>
+        <v>0.8522124583364249</v>
       </c>
       <c r="U6">
-        <v>0.06023661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04517746249690056</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.985531674398426</v>
+        <v>5.497165801613247</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08734175155790717</v>
+        <v>0.0872378733260836</v>
       </c>
       <c r="C7">
-        <v>2531.978934087565</v>
+        <v>2504.86642581341</v>
       </c>
       <c r="D7">
-        <v>2059.758934087566</v>
+        <v>2064.92242581341</v>
       </c>
       <c r="E7">
-        <v>-2658.32</v>
+        <v>-2626.044</v>
       </c>
       <c r="F7">
-        <v>161.38</v>
+        <v>193.656</v>
       </c>
       <c r="G7">
         <v>633.6</v>
@@ -1867,28 +1867,28 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M7">
-        <v>9.882365196999752</v>
+        <v>11.8588382363997</v>
       </c>
       <c r="N7">
-        <v>44.44263480300024</v>
+        <v>42.46616176360028</v>
       </c>
       <c r="O7">
-        <v>11.11065870075006</v>
+        <v>10.61654044090007</v>
       </c>
       <c r="P7">
-        <v>33.33197610225018</v>
+        <v>31.84962132270021</v>
       </c>
       <c r="Q7">
-        <v>401.6319761022502</v>
+        <v>400.1496213227002</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08952145098217068</v>
+        <v>0.08987470805986125</v>
       </c>
       <c r="T7">
-        <v>0.8522124583364249</v>
+        <v>0.8590980962976672</v>
       </c>
       <c r="U7">
         <v>0.06123661666253409</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>5.497165801613247</v>
+        <v>4.580971501344372</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0872378733260836</v>
+        <v>0.08744899509426006</v>
       </c>
       <c r="C8">
-        <v>2504.86642581341</v>
+        <v>2462.123184702351</v>
       </c>
       <c r="D8">
-        <v>2064.92242581341</v>
+        <v>2054.455184702351</v>
       </c>
       <c r="E8">
-        <v>-2626.044</v>
+        <v>-2593.768</v>
       </c>
       <c r="F8">
-        <v>193.656</v>
+        <v>225.932</v>
       </c>
       <c r="G8">
         <v>633.6</v>
@@ -1949,45 +1949,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M8">
-        <v>11.8588382363997</v>
+        <v>15.19090327579965</v>
       </c>
       <c r="N8">
-        <v>42.46616176360029</v>
+        <v>39.13409672420034</v>
       </c>
       <c r="O8">
-        <v>10.61654044090007</v>
+        <v>9.783524181050085</v>
       </c>
       <c r="P8">
-        <v>31.84962132270022</v>
+        <v>29.35057254315026</v>
       </c>
       <c r="Q8">
-        <v>400.1496213227002</v>
+        <v>397.6505725431502</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08987470805986125</v>
+        <v>0.09023556206395378</v>
       </c>
       <c r="T8">
-        <v>0.8590980962976672</v>
+        <v>0.8661318124946352</v>
       </c>
       <c r="U8">
-        <v>0.06123661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04592746249690056</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.580971501344373</v>
+        <v>3.576153373745995</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08744899509426005</v>
+        <v>0.08755811686243652</v>
       </c>
       <c r="C9">
-        <v>2462.123184702351</v>
+        <v>2424.478509119288</v>
       </c>
       <c r="D9">
-        <v>2054.455184702351</v>
+        <v>2049.086509119289</v>
       </c>
       <c r="E9">
-        <v>-2593.768</v>
+        <v>-2561.492</v>
       </c>
       <c r="F9">
-        <v>225.932</v>
+        <v>258.208</v>
       </c>
       <c r="G9">
         <v>633.6</v>
@@ -2031,45 +2031,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M9">
-        <v>15.19090327579965</v>
+        <v>18.0840147151996</v>
       </c>
       <c r="N9">
-        <v>39.13409672420033</v>
+        <v>36.24098528480039</v>
       </c>
       <c r="O9">
-        <v>9.783524181050083</v>
+        <v>9.060246321200097</v>
       </c>
       <c r="P9">
-        <v>29.35057254315025</v>
+        <v>27.18073896360029</v>
       </c>
       <c r="Q9">
-        <v>397.6505725431502</v>
+        <v>395.4807389636003</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09023556206395378</v>
+        <v>0.09060426072030919</v>
       </c>
       <c r="T9">
-        <v>0.8661318124946352</v>
+        <v>0.8733184355654504</v>
       </c>
       <c r="U9">
-        <v>0.06723661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.05042746249690056</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>3.576153373745993</v>
+        <v>3.004034273116349</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08755811686243652</v>
+        <v>0.08830998863061296</v>
       </c>
       <c r="C10">
-        <v>2424.478509119288</v>
+        <v>2355.96043175377</v>
       </c>
       <c r="D10">
-        <v>2049.086509119289</v>
+        <v>2012.84443175377</v>
       </c>
       <c r="E10">
-        <v>-2561.492</v>
+        <v>-2529.216</v>
       </c>
       <c r="F10">
-        <v>258.208</v>
+        <v>290.484</v>
       </c>
       <c r="G10">
         <v>633.6</v>
@@ -2113,45 +2113,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M10">
-        <v>18.0840147151996</v>
+        <v>23.74317935459955</v>
       </c>
       <c r="N10">
-        <v>36.24098528480039</v>
+        <v>30.58182064540044</v>
       </c>
       <c r="O10">
-        <v>9.060246321200097</v>
+        <v>7.645455161350109</v>
       </c>
       <c r="P10">
-        <v>27.18073896360029</v>
+        <v>22.93636548405033</v>
       </c>
       <c r="Q10">
-        <v>395.4807389636003</v>
+        <v>391.2363654840503</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09060426072030919</v>
+        <v>0.09098106264383725</v>
       </c>
       <c r="T10">
-        <v>0.8733184355654504</v>
+        <v>0.8806630063960635</v>
       </c>
       <c r="U10">
-        <v>0.07003661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.05252746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.004034273116349</v>
+        <v>2.288025507817094</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08830998863061296</v>
+        <v>0.08835986039878939</v>
       </c>
       <c r="C11">
-        <v>2355.96043175377</v>
+        <v>2321.325774795429</v>
       </c>
       <c r="D11">
-        <v>2012.84443175377</v>
+        <v>2010.485774795428</v>
       </c>
       <c r="E11">
-        <v>-2529.216</v>
+        <v>-2496.94</v>
       </c>
       <c r="F11">
-        <v>290.484</v>
+        <v>322.76</v>
       </c>
       <c r="G11">
         <v>633.6</v>
@@ -2195,28 +2195,28 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M11">
-        <v>23.74317935459955</v>
+        <v>26.3813103939995</v>
       </c>
       <c r="N11">
-        <v>30.58182064540044</v>
+        <v>27.94368960600049</v>
       </c>
       <c r="O11">
-        <v>7.645455161350109</v>
+        <v>6.985922401500122</v>
       </c>
       <c r="P11">
-        <v>22.93636548405033</v>
+        <v>20.95776720450036</v>
       </c>
       <c r="Q11">
-        <v>391.2363654840503</v>
+        <v>389.2577672045004</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09098106264383725</v>
+        <v>0.0913662379434437</v>
       </c>
       <c r="T11">
-        <v>0.8806630063960635</v>
+        <v>0.8881707899118014</v>
       </c>
       <c r="U11">
         <v>0.0817366166625341</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>2.288025507817094</v>
+        <v>2.059222957035385</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08835986039878939</v>
+        <v>0.08958123216696584</v>
       </c>
       <c r="C12">
-        <v>2321.325774795429</v>
+        <v>2232.962943883706</v>
       </c>
       <c r="D12">
-        <v>2010.485774795428</v>
+        <v>1954.398943883705</v>
       </c>
       <c r="E12">
-        <v>-2496.94</v>
+        <v>-2464.664</v>
       </c>
       <c r="F12">
-        <v>322.76</v>
+        <v>355.036</v>
       </c>
       <c r="G12">
         <v>633.6</v>
@@ -2277,45 +2277,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M12">
-        <v>26.3813103939995</v>
+        <v>34.06095263339945</v>
       </c>
       <c r="N12">
-        <v>27.94368960600049</v>
+        <v>20.26404736660054</v>
       </c>
       <c r="O12">
-        <v>6.985922401500122</v>
+        <v>5.066011841650134</v>
       </c>
       <c r="P12">
-        <v>20.95776720450036</v>
+        <v>15.1980355249504</v>
       </c>
       <c r="Q12">
-        <v>389.2577672045004</v>
+        <v>383.4980355249504</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0913662379434437</v>
+        <v>0.09176006886776042</v>
       </c>
       <c r="T12">
-        <v>0.8881707899118014</v>
+        <v>0.8958472876638482</v>
       </c>
       <c r="U12">
-        <v>0.0817366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.06130246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.059222957035385</v>
+        <v>1.59493483886678</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08958123216696584</v>
+        <v>0.09532691692515077</v>
       </c>
       <c r="C13">
-        <v>2232.962943883706</v>
+        <v>1973.954473533167</v>
       </c>
       <c r="D13">
-        <v>1954.398943883705</v>
+        <v>1727.666473533167</v>
       </c>
       <c r="E13">
-        <v>-2464.664</v>
+        <v>-2432.388</v>
       </c>
       <c r="F13">
-        <v>355.036</v>
+        <v>387.312</v>
       </c>
       <c r="G13">
         <v>633.6</v>
@@ -2359,45 +2359,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M13">
-        <v>34.06095263339945</v>
+        <v>59.1567244727994</v>
       </c>
       <c r="N13">
-        <v>20.26404736660054</v>
+        <v>-4.831724472799415</v>
       </c>
       <c r="O13">
-        <v>5.066011841650134</v>
+        <v>-1.207931118199854</v>
       </c>
       <c r="P13">
-        <v>15.1980355249504</v>
+        <v>-3.623793354599561</v>
       </c>
       <c r="Q13">
-        <v>383.4980355249504</v>
+        <v>364.6762066454004</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09176006886776042</v>
+        <v>0.09227996688885678</v>
       </c>
       <c r="T13">
-        <v>0.8958472876638482</v>
+        <v>0.9059810677806942</v>
       </c>
       <c r="U13">
-        <v>0.09593661666253409</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V13">
-        <v>0.25</v>
+        <v>0.229580831613568</v>
       </c>
       <c r="W13">
-        <v>0.07195246249690057</v>
+        <v>0.1176712171913068</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y13">
-        <v>1.59493483886678</v>
+        <v>0.9183233264542721</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09532691692515077</v>
+        <v>0.09639628309177613</v>
       </c>
       <c r="C14">
-        <v>1973.954473533167</v>
+        <v>1905.163774011502</v>
       </c>
       <c r="D14">
-        <v>1727.666473533167</v>
+        <v>1691.151774011502</v>
       </c>
       <c r="E14">
-        <v>-2432.388</v>
+        <v>-2400.112</v>
       </c>
       <c r="F14">
-        <v>387.312</v>
+        <v>419.588</v>
       </c>
       <c r="G14">
         <v>633.6</v>
@@ -2441,37 +2441,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M14">
-        <v>59.1567244727994</v>
+        <v>64.08645151219936</v>
       </c>
       <c r="N14">
-        <v>-4.831724472799415</v>
+        <v>-9.761451512199372</v>
       </c>
       <c r="O14">
-        <v>-1.207931118199854</v>
+        <v>-2.440362878049843</v>
       </c>
       <c r="P14">
-        <v>-3.623793354599561</v>
+        <v>-7.321088634149529</v>
       </c>
       <c r="Q14">
-        <v>364.6762066454004</v>
+        <v>360.9789113658505</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09227996688885678</v>
+        <v>0.09281421938183215</v>
       </c>
       <c r="T14">
-        <v>0.9059810677806942</v>
+        <v>0.9163946432724264</v>
       </c>
       <c r="U14">
         <v>0.1527366166625341</v>
       </c>
       <c r="V14">
-        <v>0.229580831613568</v>
+        <v>0.2119207676432935</v>
       </c>
       <c r="W14">
-        <v>0.1176712171913068</v>
+        <v>0.1203685556121704</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.9183233264542721</v>
+        <v>0.847683070573174</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09639628309177613</v>
+        <v>0.1053283226849624</v>
       </c>
       <c r="C15">
-        <v>1905.163774011502</v>
+        <v>1619.135712434033</v>
       </c>
       <c r="D15">
-        <v>1691.151774011502</v>
+        <v>1437.399712434033</v>
       </c>
       <c r="E15">
-        <v>-2400.112</v>
+        <v>-2367.836</v>
       </c>
       <c r="F15">
-        <v>419.588</v>
+        <v>451.864</v>
       </c>
       <c r="G15">
         <v>633.6</v>
@@ -2523,45 +2523,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M15">
-        <v>64.08645151219936</v>
+        <v>93.41683455159931</v>
       </c>
       <c r="N15">
-        <v>-9.761451512199372</v>
+        <v>-39.09183455159932</v>
       </c>
       <c r="O15">
-        <v>-2.440362878049843</v>
+        <v>-9.77295863789983</v>
       </c>
       <c r="P15">
-        <v>-7.321088634149529</v>
+        <v>-29.31887591369949</v>
       </c>
       <c r="Q15">
-        <v>360.9789113658505</v>
+        <v>338.9811240863005</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09281421938183215</v>
+        <v>0.09371284219622669</v>
       </c>
       <c r="T15">
-        <v>0.9163946432724264</v>
+        <v>0.9339104745307407</v>
       </c>
       <c r="U15">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V15">
-        <v>0.2119207676432935</v>
+        <v>0.1453833248063904</v>
       </c>
       <c r="W15">
-        <v>0.1203685556121704</v>
+        <v>0.1766805599729107</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y15">
-        <v>0.847683070573174</v>
+        <v>0.5815332992255617</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1053283226849624</v>
+        <v>0.1069376888515878</v>
       </c>
       <c r="C16">
-        <v>1619.135712434033</v>
+        <v>1549.022127982257</v>
       </c>
       <c r="D16">
-        <v>1437.399712434033</v>
+        <v>1399.562127982258</v>
       </c>
       <c r="E16">
-        <v>-2367.836</v>
+        <v>-2335.56</v>
       </c>
       <c r="F16">
-        <v>451.864</v>
+        <v>484.14</v>
       </c>
       <c r="G16">
         <v>633.6</v>
@@ -2605,37 +2605,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M16">
-        <v>93.41683455159931</v>
+        <v>100.0894655909993</v>
       </c>
       <c r="N16">
-        <v>-39.09183455159932</v>
+        <v>-45.76446559099928</v>
       </c>
       <c r="O16">
-        <v>-9.77295863789983</v>
+        <v>-11.44111639774982</v>
       </c>
       <c r="P16">
-        <v>-29.31887591369949</v>
+        <v>-34.32334919324946</v>
       </c>
       <c r="Q16">
-        <v>338.9811240863005</v>
+        <v>333.9766508067506</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09371284219622669</v>
+        <v>0.09427652269265288</v>
       </c>
       <c r="T16">
-        <v>0.9339104745307407</v>
+        <v>0.9448976565840436</v>
       </c>
       <c r="U16">
         <v>0.2067366166625341</v>
       </c>
       <c r="V16">
-        <v>0.1453833248063904</v>
+        <v>0.1356911031526311</v>
       </c>
       <c r="W16">
-        <v>0.1766805599729107</v>
+        <v>0.1786842970855522</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.5815332992255617</v>
+        <v>0.5427644126105242</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1069376888515878</v>
+        <v>0.1085470550182131</v>
       </c>
       <c r="C17">
-        <v>1549.022127982258</v>
+        <v>1480.84949608119</v>
       </c>
       <c r="D17">
-        <v>1399.562127982258</v>
+        <v>1363.66549608119</v>
       </c>
       <c r="E17">
-        <v>-2335.56</v>
+        <v>-2303.284</v>
       </c>
       <c r="F17">
-        <v>484.14</v>
+        <v>516.4159999999999</v>
       </c>
       <c r="G17">
         <v>633.6</v>
@@ -2687,37 +2687,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M17">
-        <v>100.0894655909993</v>
+        <v>106.7620966303992</v>
       </c>
       <c r="N17">
-        <v>-45.76446559099927</v>
+        <v>-52.43709663039921</v>
       </c>
       <c r="O17">
-        <v>-11.44111639774982</v>
+        <v>-13.1092741575998</v>
       </c>
       <c r="P17">
-        <v>-34.32334919324945</v>
+        <v>-39.32782247279941</v>
       </c>
       <c r="Q17">
-        <v>333.9766508067506</v>
+        <v>328.9721775272006</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09427652269265288</v>
+        <v>0.09485362415327971</v>
       </c>
       <c r="T17">
-        <v>0.9448976565840436</v>
+        <v>0.9561464382100441</v>
       </c>
       <c r="U17">
         <v>0.2067366166625341</v>
       </c>
       <c r="V17">
-        <v>0.1356911031526311</v>
+        <v>0.1272104092055916</v>
       </c>
       <c r="W17">
-        <v>0.1786842970855522</v>
+        <v>0.1804375670591136</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.5427644126105242</v>
+        <v>0.5088416368223665</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1085470550182131</v>
+        <v>0.1162303719764195</v>
       </c>
       <c r="C18">
-        <v>1480.84949608119</v>
+        <v>1299.809916714188</v>
       </c>
       <c r="D18">
-        <v>1363.66549608119</v>
+        <v>1214.901916714188</v>
       </c>
       <c r="E18">
-        <v>-2303.284</v>
+        <v>-2271.008</v>
       </c>
       <c r="F18">
-        <v>516.4159999999999</v>
+        <v>548.692</v>
       </c>
       <c r="G18">
         <v>633.6</v>
@@ -2769,45 +2769,45 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M18">
-        <v>106.7620966303992</v>
+        <v>132.6389476697992</v>
       </c>
       <c r="N18">
-        <v>-52.43709663039921</v>
+        <v>-78.31394766979918</v>
       </c>
       <c r="O18">
-        <v>-13.1092741575998</v>
+        <v>-19.57848691744979</v>
       </c>
       <c r="P18">
-        <v>-39.32782247279941</v>
+        <v>-58.73546075234938</v>
       </c>
       <c r="Q18">
-        <v>328.9721775272006</v>
+        <v>309.5645392476506</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09485362415327971</v>
+        <v>0.09559396997630845</v>
       </c>
       <c r="T18">
-        <v>0.9561464382100441</v>
+        <v>0.9705771563058302</v>
       </c>
       <c r="U18">
-        <v>0.2067366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V18">
-        <v>0.1272104092055916</v>
+        <v>0.1023926247802427</v>
       </c>
       <c r="W18">
-        <v>0.1804375670591136</v>
+        <v>0.2169845699769619</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.5088416368223665</v>
+        <v>0.409570499120971</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1162303719764195</v>
+        <v>0.1181897381430449</v>
       </c>
       <c r="C19">
-        <v>1299.809916714188</v>
+        <v>1234.650281927801</v>
       </c>
       <c r="D19">
-        <v>1214.901916714188</v>
+        <v>1182.018281927801</v>
       </c>
       <c r="E19">
-        <v>-2271.008</v>
+        <v>-2238.732</v>
       </c>
       <c r="F19">
-        <v>548.692</v>
+        <v>580.9680000000001</v>
       </c>
       <c r="G19">
         <v>633.6</v>
@@ -2851,37 +2851,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M19">
-        <v>132.6389476697992</v>
+        <v>140.4412387091991</v>
       </c>
       <c r="N19">
-        <v>-78.31394766979918</v>
+        <v>-86.11623870919914</v>
       </c>
       <c r="O19">
-        <v>-19.57848691744979</v>
+        <v>-21.52905967729978</v>
       </c>
       <c r="P19">
-        <v>-58.73546075234938</v>
+        <v>-64.58717903189935</v>
       </c>
       <c r="Q19">
-        <v>309.5645392476506</v>
+        <v>303.7128209681007</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09559396997630845</v>
+        <v>0.09620121351260491</v>
       </c>
       <c r="T19">
-        <v>0.9705771563058302</v>
+        <v>0.9824134630900476</v>
       </c>
       <c r="U19">
         <v>0.2417366166625341</v>
       </c>
       <c r="V19">
-        <v>0.1023926247802427</v>
+        <v>0.09670414562578479</v>
       </c>
       <c r="W19">
-        <v>0.2169845699769619</v>
+        <v>0.2183596836817159</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.409570499120971</v>
+        <v>0.3868165825031392</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1181897381430449</v>
+        <v>0.1201491043096702</v>
       </c>
       <c r="C20">
-        <v>1234.650281927802</v>
+        <v>1171.223851112985</v>
       </c>
       <c r="D20">
-        <v>1182.018281927802</v>
+        <v>1150.867851112985</v>
       </c>
       <c r="E20">
-        <v>-2238.732</v>
+        <v>-2206.456</v>
       </c>
       <c r="F20">
-        <v>580.968</v>
+        <v>613.244</v>
       </c>
       <c r="G20">
         <v>633.6</v>
@@ -2933,37 +2933,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M20">
-        <v>140.4412387091991</v>
+        <v>148.2435297485991</v>
       </c>
       <c r="N20">
-        <v>-86.11623870919911</v>
+        <v>-93.91852974859907</v>
       </c>
       <c r="O20">
-        <v>-21.52905967729978</v>
+        <v>-23.47963243714977</v>
       </c>
       <c r="P20">
-        <v>-64.58717903189932</v>
+        <v>-70.4388973114493</v>
       </c>
       <c r="Q20">
-        <v>303.7128209681007</v>
+        <v>297.8611026885507</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09620121351260491</v>
+        <v>0.09682345071646423</v>
       </c>
       <c r="T20">
-        <v>0.9824134630900476</v>
+        <v>0.9945420243627643</v>
       </c>
       <c r="U20">
         <v>0.2417366166625341</v>
       </c>
       <c r="V20">
-        <v>0.09670414562578482</v>
+        <v>0.09161445375074351</v>
       </c>
       <c r="W20">
-        <v>0.2183596836817159</v>
+        <v>0.2195900485754431</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3868165825031392</v>
+        <v>0.366457815002974</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1201491043096702</v>
+        <v>0.1221084704762956</v>
       </c>
       <c r="C21">
-        <v>1171.223851112985</v>
+        <v>1109.397114272727</v>
       </c>
       <c r="D21">
-        <v>1150.867851112985</v>
+        <v>1121.317114272727</v>
       </c>
       <c r="E21">
-        <v>-2206.456</v>
+        <v>-2174.18</v>
       </c>
       <c r="F21">
-        <v>613.244</v>
+        <v>645.52</v>
       </c>
       <c r="G21">
         <v>633.6</v>
@@ -3015,37 +3015,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M21">
-        <v>148.2435297485991</v>
+        <v>156.045820787999</v>
       </c>
       <c r="N21">
-        <v>-93.91852974859907</v>
+        <v>-101.720820787999</v>
       </c>
       <c r="O21">
-        <v>-23.47963243714977</v>
+        <v>-25.43020519699976</v>
       </c>
       <c r="P21">
-        <v>-70.4388973114493</v>
+        <v>-76.29061559099927</v>
       </c>
       <c r="Q21">
-        <v>297.8611026885507</v>
+        <v>292.0093844090007</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09682345071646423</v>
+        <v>0.09746124385042002</v>
       </c>
       <c r="T21">
-        <v>0.9945420243627643</v>
+        <v>1.006973799667299</v>
       </c>
       <c r="U21">
         <v>0.2417366166625341</v>
       </c>
       <c r="V21">
-        <v>0.09161445375074351</v>
+        <v>0.08703373106320632</v>
       </c>
       <c r="W21">
-        <v>0.2195900485754431</v>
+        <v>0.2206973769797977</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.366457815002974</v>
+        <v>0.3481349242528253</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1221084704762956</v>
+        <v>0.1240678366429209</v>
       </c>
       <c r="C22">
-        <v>1109.397114272727</v>
+        <v>1049.049930629469</v>
       </c>
       <c r="D22">
-        <v>1121.317114272727</v>
+        <v>1093.245930629469</v>
       </c>
       <c r="E22">
-        <v>-2174.18</v>
+        <v>-2141.904</v>
       </c>
       <c r="F22">
-        <v>645.52</v>
+        <v>677.796</v>
       </c>
       <c r="G22">
         <v>633.6</v>
@@ -3097,37 +3097,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M22">
-        <v>156.045820787999</v>
+        <v>163.848111827399</v>
       </c>
       <c r="N22">
-        <v>-101.720820787999</v>
+        <v>-109.523111827399</v>
       </c>
       <c r="O22">
-        <v>-25.43020519699976</v>
+        <v>-27.38077795684975</v>
       </c>
       <c r="P22">
-        <v>-76.29061559099927</v>
+        <v>-82.14233387054924</v>
       </c>
       <c r="Q22">
-        <v>292.0093844090007</v>
+        <v>286.1576661294508</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09746124385042002</v>
+        <v>0.09811518364599496</v>
       </c>
       <c r="T22">
-        <v>1.006973799667299</v>
+        <v>1.019720303460556</v>
       </c>
       <c r="U22">
         <v>0.2417366166625341</v>
       </c>
       <c r="V22">
-        <v>0.08703373106320632</v>
+        <v>0.08288926767924411</v>
       </c>
       <c r="W22">
-        <v>0.2206973769797977</v>
+        <v>0.2216992455361185</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3481349242528253</v>
+        <v>0.3315570707169765</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1240678366429209</v>
+        <v>0.1260272028095463</v>
       </c>
       <c r="C23">
-        <v>1049.04993062947</v>
+        <v>990.0738960618756</v>
       </c>
       <c r="D23">
-        <v>1093.245930629469</v>
+        <v>1066.545896061876</v>
       </c>
       <c r="E23">
-        <v>-2141.904</v>
+        <v>-2109.628</v>
       </c>
       <c r="F23">
-        <v>677.7959999999999</v>
+        <v>710.072</v>
       </c>
       <c r="G23">
         <v>633.6</v>
@@ -3179,37 +3179,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M23">
-        <v>163.848111827399</v>
+        <v>171.6504028667989</v>
       </c>
       <c r="N23">
-        <v>-109.523111827399</v>
+        <v>-117.3254028667989</v>
       </c>
       <c r="O23">
-        <v>-27.38077795684974</v>
+        <v>-29.33135071669973</v>
       </c>
       <c r="P23">
-        <v>-82.14233387054922</v>
+        <v>-87.99405215009919</v>
       </c>
       <c r="Q23">
-        <v>286.1576661294508</v>
+        <v>280.3059478499008</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09811518364599496</v>
+        <v>0.09878589112863592</v>
       </c>
       <c r="T23">
-        <v>1.019720303460556</v>
+        <v>1.032793640684409</v>
       </c>
       <c r="U23">
         <v>0.2417366166625341</v>
       </c>
       <c r="V23">
-        <v>0.08288926767924412</v>
+        <v>0.07912157369382393</v>
       </c>
       <c r="W23">
-        <v>0.2216992455361185</v>
+        <v>0.2226100351327737</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3315570707169765</v>
+        <v>0.3164862947752958</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1260272028095463</v>
+        <v>0.1279865689761716</v>
       </c>
       <c r="C24">
-        <v>990.0738960618756</v>
+        <v>932.3709440680209</v>
       </c>
       <c r="D24">
-        <v>1066.545896061876</v>
+        <v>1041.118944068021</v>
       </c>
       <c r="E24">
-        <v>-2109.628</v>
+        <v>-2077.352</v>
       </c>
       <c r="F24">
-        <v>710.072</v>
+        <v>742.348</v>
       </c>
       <c r="G24">
         <v>633.6</v>
@@ -3261,37 +3261,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M24">
-        <v>171.6504028667989</v>
+        <v>179.4526939061988</v>
       </c>
       <c r="N24">
-        <v>-117.3254028667989</v>
+        <v>-125.1276939061989</v>
       </c>
       <c r="O24">
-        <v>-29.33135071669973</v>
+        <v>-31.28192347654971</v>
       </c>
       <c r="P24">
-        <v>-87.99405215009919</v>
+        <v>-93.84577042964915</v>
       </c>
       <c r="Q24">
-        <v>280.3059478499008</v>
+        <v>274.4542295703509</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09878589112863592</v>
+        <v>0.09947401958485198</v>
       </c>
       <c r="T24">
-        <v>1.032793640684409</v>
+        <v>1.046206545108882</v>
       </c>
       <c r="U24">
         <v>0.2417366166625341</v>
       </c>
       <c r="V24">
-        <v>0.07912157369382393</v>
+        <v>0.07568150527235333</v>
       </c>
       <c r="W24">
-        <v>0.2226100351327737</v>
+        <v>0.2234416256340677</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3164862947752958</v>
+        <v>0.3027260210894134</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1279865689761716</v>
+        <v>0.129945935142797</v>
       </c>
       <c r="C25">
-        <v>932.3709440680209</v>
+        <v>875.8521421908085</v>
       </c>
       <c r="D25">
-        <v>1041.118944068021</v>
+        <v>1016.876142190809</v>
       </c>
       <c r="E25">
-        <v>-2077.352</v>
+        <v>-2045.076</v>
       </c>
       <c r="F25">
-        <v>742.348</v>
+        <v>774.624</v>
       </c>
       <c r="G25">
         <v>633.6</v>
@@ -3343,37 +3343,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M25">
-        <v>179.4526939061988</v>
+        <v>187.2549849455988</v>
       </c>
       <c r="N25">
-        <v>-125.1276939061989</v>
+        <v>-132.9299849455988</v>
       </c>
       <c r="O25">
-        <v>-31.28192347654971</v>
+        <v>-33.2324962363997</v>
       </c>
       <c r="P25">
-        <v>-93.84577042964915</v>
+        <v>-99.69748870919912</v>
       </c>
       <c r="Q25">
-        <v>274.4542295703509</v>
+        <v>268.6025112908009</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09947401958485198</v>
+        <v>0.1001802566846527</v>
       </c>
       <c r="T25">
-        <v>1.046206545108882</v>
+        <v>1.05997242070242</v>
       </c>
       <c r="U25">
         <v>0.2417366166625341</v>
       </c>
       <c r="V25">
-        <v>0.07568150527235333</v>
+        <v>0.07252810921933861</v>
       </c>
       <c r="W25">
-        <v>0.2234416256340677</v>
+        <v>0.2242039169269204</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3027260210894134</v>
+        <v>0.2901124368773544</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1299459351427969</v>
+        <v>0.1319053013094223</v>
       </c>
       <c r="C26">
-        <v>875.8521421908089</v>
+        <v>820.4366527707872</v>
       </c>
       <c r="D26">
-        <v>1016.876142190809</v>
+        <v>993.736652770787</v>
       </c>
       <c r="E26">
-        <v>-2045.076</v>
+        <v>-2012.8</v>
       </c>
       <c r="F26">
-        <v>774.6239999999999</v>
+        <v>806.9</v>
       </c>
       <c r="G26">
         <v>633.6</v>
@@ -3425,37 +3425,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M26">
-        <v>187.2549849455988</v>
+        <v>195.0572759849988</v>
       </c>
       <c r="N26">
-        <v>-132.9299849455988</v>
+        <v>-140.7322759849988</v>
       </c>
       <c r="O26">
-        <v>-33.2324962363997</v>
+        <v>-35.18306899624969</v>
       </c>
       <c r="P26">
-        <v>-99.69748870919909</v>
+        <v>-105.5492069887491</v>
       </c>
       <c r="Q26">
-        <v>268.6025112908009</v>
+        <v>262.7507930112509</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1001802566846527</v>
+        <v>0.1009053267737814</v>
       </c>
       <c r="T26">
-        <v>1.05997242070242</v>
+        <v>1.074105386311785</v>
       </c>
       <c r="U26">
         <v>0.2417366166625341</v>
       </c>
       <c r="V26">
-        <v>0.07252810921933862</v>
+        <v>0.06962698485056507</v>
       </c>
       <c r="W26">
-        <v>0.2242039169269204</v>
+        <v>0.224905224916345</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2901124368773544</v>
+        <v>0.2785079394022603</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1319053013094223</v>
+        <v>0.1338646674760476</v>
       </c>
       <c r="C27">
-        <v>820.4366527707872</v>
+        <v>766.0508324333153</v>
       </c>
       <c r="D27">
-        <v>993.736652770787</v>
+        <v>971.6268324333153</v>
       </c>
       <c r="E27">
-        <v>-2012.8</v>
+        <v>-1980.524</v>
       </c>
       <c r="F27">
-        <v>806.9</v>
+        <v>839.176</v>
       </c>
       <c r="G27">
         <v>633.6</v>
@@ -3507,37 +3507,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M27">
-        <v>195.0572759849988</v>
+        <v>202.8595670243987</v>
       </c>
       <c r="N27">
-        <v>-140.7322759849988</v>
+        <v>-148.5345670243987</v>
       </c>
       <c r="O27">
-        <v>-35.18306899624969</v>
+        <v>-37.13364175609968</v>
       </c>
       <c r="P27">
-        <v>-105.5492069887491</v>
+        <v>-111.4009252682991</v>
       </c>
       <c r="Q27">
-        <v>262.7507930112509</v>
+        <v>256.8990747317009</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1009053267737814</v>
+        <v>0.1016499933518054</v>
       </c>
       <c r="T27">
-        <v>1.074105386311785</v>
+        <v>1.088620323964647</v>
       </c>
       <c r="U27">
         <v>0.2417366166625341</v>
       </c>
       <c r="V27">
-        <v>0.06962698485056507</v>
+        <v>0.0669490238947741</v>
       </c>
       <c r="W27">
-        <v>0.224905224916345</v>
+        <v>0.2255525861373523</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2785079394022603</v>
+        <v>0.2677960955790963</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1338646674760476</v>
+        <v>0.135824033642673</v>
       </c>
       <c r="C28">
-        <v>766.0508324333153</v>
+        <v>712.6274491732881</v>
       </c>
       <c r="D28">
-        <v>971.6268324333153</v>
+        <v>950.4794491732881</v>
       </c>
       <c r="E28">
-        <v>-1980.524</v>
+        <v>-1948.248</v>
       </c>
       <c r="F28">
-        <v>839.176</v>
+        <v>871.452</v>
       </c>
       <c r="G28">
         <v>633.6</v>
@@ -3589,37 +3589,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M28">
-        <v>202.8595670243987</v>
+        <v>210.6618580637987</v>
       </c>
       <c r="N28">
-        <v>-148.5345670243987</v>
+        <v>-156.3368580637987</v>
       </c>
       <c r="O28">
-        <v>-37.13364175609968</v>
+        <v>-39.08421451594967</v>
       </c>
       <c r="P28">
-        <v>-111.4009252682991</v>
+        <v>-117.252643547849</v>
       </c>
       <c r="Q28">
-        <v>256.8990747317009</v>
+        <v>251.047356452151</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1016499933518054</v>
+        <v>0.102415061753885</v>
       </c>
       <c r="T28">
-        <v>1.088620323964647</v>
+        <v>1.103532931142245</v>
       </c>
       <c r="U28">
         <v>0.2417366166625341</v>
       </c>
       <c r="V28">
-        <v>0.0669490238947741</v>
+        <v>0.06446943041718987</v>
       </c>
       <c r="W28">
-        <v>0.2255525861373523</v>
+        <v>0.226151994675322</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2677960955790963</v>
+        <v>0.2578777216687594</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.135824033642673</v>
+        <v>0.1377833998092983</v>
       </c>
       <c r="C29">
-        <v>712.6274491732881</v>
+        <v>660.1049995025446</v>
       </c>
       <c r="D29">
-        <v>950.4794491732881</v>
+        <v>930.2329995025447</v>
       </c>
       <c r="E29">
-        <v>-1948.248</v>
+        <v>-1915.972</v>
       </c>
       <c r="F29">
-        <v>871.452</v>
+        <v>903.7280000000001</v>
       </c>
       <c r="G29">
         <v>633.6</v>
@@ -3671,37 +3671,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M29">
-        <v>210.6618580637987</v>
+        <v>218.4641491031986</v>
       </c>
       <c r="N29">
-        <v>-156.3368580637987</v>
+        <v>-164.1391491031986</v>
       </c>
       <c r="O29">
-        <v>-39.08421451594967</v>
+        <v>-41.03478727579966</v>
       </c>
       <c r="P29">
-        <v>-117.252643547849</v>
+        <v>-123.104361827399</v>
       </c>
       <c r="Q29">
-        <v>251.047356452151</v>
+        <v>245.195638172601</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.102415061753885</v>
+        <v>0.1032013820560223</v>
       </c>
       <c r="T29">
-        <v>1.103532931142245</v>
+        <v>1.11885977740811</v>
       </c>
       <c r="U29">
         <v>0.2417366166625341</v>
       </c>
       <c r="V29">
-        <v>0.06446943041718987</v>
+        <v>0.06216695075943309</v>
       </c>
       <c r="W29">
-        <v>0.226151994675322</v>
+        <v>0.2267085883177224</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2578777216687594</v>
+        <v>0.2486678030377324</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1377833998092983</v>
+        <v>0.1397427659759236</v>
       </c>
       <c r="C30">
-        <v>660.1049995025446</v>
+        <v>608.4271110509014</v>
       </c>
       <c r="D30">
-        <v>930.2329995025447</v>
+        <v>910.8311110509017</v>
       </c>
       <c r="E30">
-        <v>-1915.972</v>
+        <v>-1883.696</v>
       </c>
       <c r="F30">
-        <v>903.7280000000001</v>
+        <v>936.0040000000001</v>
       </c>
       <c r="G30">
         <v>633.6</v>
@@ -3753,37 +3753,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M30">
-        <v>218.4641491031986</v>
+        <v>226.2664401425986</v>
       </c>
       <c r="N30">
-        <v>-164.1391491031986</v>
+        <v>-171.9414401425986</v>
       </c>
       <c r="O30">
-        <v>-41.03478727579966</v>
+        <v>-42.98536003564966</v>
       </c>
       <c r="P30">
-        <v>-123.104361827399</v>
+        <v>-128.956080106949</v>
       </c>
       <c r="Q30">
-        <v>245.195638172601</v>
+        <v>239.343919893051</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1032013820560223</v>
+        <v>0.1040098522258254</v>
       </c>
       <c r="T30">
-        <v>1.11885977740811</v>
+        <v>1.134618365822309</v>
       </c>
       <c r="U30">
         <v>0.2417366166625341</v>
       </c>
       <c r="V30">
-        <v>0.06216695075943309</v>
+        <v>0.06002326280221125</v>
       </c>
       <c r="W30">
-        <v>0.2267085883177224</v>
+        <v>0.2272267961916814</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2486678030377324</v>
+        <v>0.2400930512088449</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1397427659759236</v>
+        <v>0.141702132142549</v>
       </c>
       <c r="C31">
-        <v>608.4271110509017</v>
+        <v>557.5420183995495</v>
       </c>
       <c r="D31">
-        <v>910.8311110509017</v>
+        <v>892.2220183995494</v>
       </c>
       <c r="E31">
-        <v>-1883.696</v>
+        <v>-1851.42</v>
       </c>
       <c r="F31">
-        <v>936.0039999999999</v>
+        <v>968.28</v>
       </c>
       <c r="G31">
         <v>633.6</v>
@@ -3835,37 +3835,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M31">
-        <v>226.2664401425986</v>
+        <v>234.0687311819985</v>
       </c>
       <c r="N31">
-        <v>-171.9414401425986</v>
+        <v>-179.7437311819985</v>
       </c>
       <c r="O31">
-        <v>-42.98536003564964</v>
+        <v>-44.93593279549963</v>
       </c>
       <c r="P31">
-        <v>-128.9560801069489</v>
+        <v>-134.8077983864989</v>
       </c>
       <c r="Q31">
-        <v>239.3439198930511</v>
+        <v>233.4922016135011</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1040098522258254</v>
+        <v>0.1048414215433372</v>
       </c>
       <c r="T31">
-        <v>1.134618365822309</v>
+        <v>1.15082719961977</v>
       </c>
       <c r="U31">
         <v>0.2417366166625341</v>
       </c>
       <c r="V31">
-        <v>0.06002326280221126</v>
+        <v>0.05802248737547089</v>
       </c>
       <c r="W31">
-        <v>0.2272267961916814</v>
+        <v>0.2277104568740432</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2400930512088451</v>
+        <v>0.2320899495018836</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.141702132142549</v>
+        <v>0.1436614983091743</v>
       </c>
       <c r="C32">
-        <v>557.5420183995495</v>
+        <v>507.402101883095</v>
       </c>
       <c r="D32">
-        <v>892.2220183995494</v>
+        <v>874.3581018830949</v>
       </c>
       <c r="E32">
-        <v>-1851.42</v>
+        <v>-1819.144</v>
       </c>
       <c r="F32">
-        <v>968.28</v>
+        <v>1000.556</v>
       </c>
       <c r="G32">
         <v>633.6</v>
@@ -3917,37 +3917,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M32">
-        <v>234.0687311819985</v>
+        <v>241.8710222213984</v>
       </c>
       <c r="N32">
-        <v>-179.7437311819985</v>
+        <v>-187.5460222213985</v>
       </c>
       <c r="O32">
-        <v>-44.93593279549963</v>
+        <v>-46.88650555534961</v>
       </c>
       <c r="P32">
-        <v>-134.8077983864989</v>
+        <v>-140.6595166660488</v>
       </c>
       <c r="Q32">
-        <v>233.4922016135011</v>
+        <v>227.6404833339512</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1048414215433372</v>
+        <v>0.1056970943193276</v>
       </c>
       <c r="T32">
-        <v>1.15082719961977</v>
+        <v>1.167505854686723</v>
       </c>
       <c r="U32">
         <v>0.2417366166625341</v>
       </c>
       <c r="V32">
-        <v>0.05802248737547089</v>
+        <v>0.05615079423432667</v>
       </c>
       <c r="W32">
-        <v>0.2277104568740432</v>
+        <v>0.2281629136414138</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2320899495018836</v>
+        <v>0.2246031769373067</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1436614983091743</v>
+        <v>0.1456208644757996</v>
       </c>
       <c r="C33">
-        <v>507.402101883095</v>
+        <v>457.9634807082421</v>
       </c>
       <c r="D33">
-        <v>874.3581018830949</v>
+        <v>857.1954807082419</v>
       </c>
       <c r="E33">
-        <v>-1819.144</v>
+        <v>-1786.868</v>
       </c>
       <c r="F33">
-        <v>1000.556</v>
+        <v>1032.832</v>
       </c>
       <c r="G33">
         <v>633.6</v>
@@ -3999,37 +3999,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M33">
-        <v>241.8710222213984</v>
+        <v>249.6733132607984</v>
       </c>
       <c r="N33">
-        <v>-187.5460222213985</v>
+        <v>-195.3483132607984</v>
       </c>
       <c r="O33">
-        <v>-46.88650555534961</v>
+        <v>-48.8370783151996</v>
       </c>
       <c r="P33">
-        <v>-140.6595166660488</v>
+        <v>-146.5112349455988</v>
       </c>
       <c r="Q33">
-        <v>227.6404833339512</v>
+        <v>221.7887650544012</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1056970943193276</v>
+        <v>0.1065779339416706</v>
       </c>
       <c r="T33">
-        <v>1.167505854686723</v>
+        <v>1.184675058432116</v>
       </c>
       <c r="U33">
         <v>0.2417366166625341</v>
       </c>
       <c r="V33">
-        <v>0.05615079423432667</v>
+        <v>0.05439608191450396</v>
       </c>
       <c r="W33">
-        <v>0.2281629136414138</v>
+        <v>0.2285870918608238</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2246031769373067</v>
+        <v>0.2175843276580158</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1456208644757996</v>
+        <v>0.147580230642425</v>
       </c>
       <c r="C34">
-        <v>457.9634807082421</v>
+        <v>409.1856530695866</v>
       </c>
       <c r="D34">
-        <v>857.1954807082419</v>
+        <v>840.6936530695866</v>
       </c>
       <c r="E34">
-        <v>-1786.868</v>
+        <v>-1754.592</v>
       </c>
       <c r="F34">
-        <v>1032.832</v>
+        <v>1065.108</v>
       </c>
       <c r="G34">
         <v>633.6</v>
@@ -4081,37 +4081,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M34">
-        <v>249.6733132607984</v>
+        <v>257.4756043001984</v>
       </c>
       <c r="N34">
-        <v>-195.3483132607984</v>
+        <v>-203.1506043001984</v>
       </c>
       <c r="O34">
-        <v>-48.8370783151996</v>
+        <v>-50.7876510750496</v>
       </c>
       <c r="P34">
-        <v>-146.5112349455988</v>
+        <v>-152.3629532251488</v>
       </c>
       <c r="Q34">
-        <v>221.7887650544012</v>
+        <v>215.9370467748512</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1065779339416706</v>
+        <v>0.1074850672840836</v>
       </c>
       <c r="T34">
-        <v>1.184675058432116</v>
+        <v>1.202356775722148</v>
       </c>
       <c r="U34">
         <v>0.2417366166625341</v>
       </c>
       <c r="V34">
-        <v>0.05439608191450396</v>
+        <v>0.05274771579588262</v>
       </c>
       <c r="W34">
-        <v>0.2285870918608238</v>
+        <v>0.2289855623093605</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2175843276580158</v>
+        <v>0.2109908631835304</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.147580230642425</v>
+        <v>0.1495395968090503</v>
       </c>
       <c r="C35">
-        <v>409.1856530695866</v>
+        <v>361.0311770489675</v>
       </c>
       <c r="D35">
-        <v>840.6936530695866</v>
+        <v>824.8151770489674</v>
       </c>
       <c r="E35">
-        <v>-1754.592</v>
+        <v>-1722.316</v>
       </c>
       <c r="F35">
-        <v>1065.108</v>
+        <v>1097.384</v>
       </c>
       <c r="G35">
         <v>633.6</v>
@@ -4163,37 +4163,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M35">
-        <v>257.4756043001984</v>
+        <v>265.2778953395983</v>
       </c>
       <c r="N35">
-        <v>-203.1506043001984</v>
+        <v>-210.9528953395983</v>
       </c>
       <c r="O35">
-        <v>-50.7876510750496</v>
+        <v>-52.73822383489959</v>
       </c>
       <c r="P35">
-        <v>-152.3629532251488</v>
+        <v>-158.2146715046987</v>
       </c>
       <c r="Q35">
-        <v>215.9370467748512</v>
+        <v>210.0853284953013</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1074850672840836</v>
+        <v>0.1084196895156606</v>
       </c>
       <c r="T35">
-        <v>1.202356775722148</v>
+        <v>1.220574302627029</v>
       </c>
       <c r="U35">
         <v>0.2417366166625341</v>
       </c>
       <c r="V35">
-        <v>0.05274771579588262</v>
+        <v>0.05119631239012137</v>
       </c>
       <c r="W35">
-        <v>0.2289855623093605</v>
+        <v>0.229360593319748</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2109908631835304</v>
+        <v>0.2047852495604855</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1495395968090503</v>
+        <v>0.1514989629756757</v>
       </c>
       <c r="C36">
-        <v>361.0311770489675</v>
+        <v>313.4653870062707</v>
       </c>
       <c r="D36">
-        <v>824.8151770489674</v>
+        <v>809.5253870062708</v>
       </c>
       <c r="E36">
-        <v>-1722.316</v>
+        <v>-1690.04</v>
       </c>
       <c r="F36">
-        <v>1097.384</v>
+        <v>1129.66</v>
       </c>
       <c r="G36">
         <v>633.6</v>
@@ -4245,37 +4245,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M36">
-        <v>265.2778953395983</v>
+        <v>273.0801863789983</v>
       </c>
       <c r="N36">
-        <v>-210.9528953395983</v>
+        <v>-218.7551863789983</v>
       </c>
       <c r="O36">
-        <v>-52.73822383489959</v>
+        <v>-54.68879659474958</v>
       </c>
       <c r="P36">
-        <v>-158.2146715046987</v>
+        <v>-164.0663897842487</v>
       </c>
       <c r="Q36">
-        <v>210.0853284953013</v>
+        <v>204.2336102157513</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1084196895156606</v>
+        <v>0.1093830693543631</v>
       </c>
       <c r="T36">
-        <v>1.220574302627029</v>
+        <v>1.239352368821291</v>
       </c>
       <c r="U36">
         <v>0.2417366166625341</v>
       </c>
       <c r="V36">
-        <v>0.05119631239012137</v>
+        <v>0.04973356060754647</v>
       </c>
       <c r="W36">
-        <v>0.229360593319748</v>
+        <v>0.2297141939866847</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2047852495604855</v>
+        <v>0.1989342424301859</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1514989629756757</v>
+        <v>0.153458329142301</v>
       </c>
       <c r="C37">
-        <v>313.4653870062707</v>
+        <v>266.4561409401181</v>
       </c>
       <c r="D37">
-        <v>809.5253870062708</v>
+        <v>794.7921409401181</v>
       </c>
       <c r="E37">
-        <v>-1690.04</v>
+        <v>-1657.764</v>
       </c>
       <c r="F37">
-        <v>1129.66</v>
+        <v>1161.936</v>
       </c>
       <c r="G37">
         <v>633.6</v>
@@ -4327,37 +4327,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M37">
-        <v>273.0801863789983</v>
+        <v>280.8824774183983</v>
       </c>
       <c r="N37">
-        <v>-218.7551863789983</v>
+        <v>-226.5574774183983</v>
       </c>
       <c r="O37">
-        <v>-54.68879659474958</v>
+        <v>-56.63936935459957</v>
       </c>
       <c r="P37">
-        <v>-164.0663897842487</v>
+        <v>-169.9181080637987</v>
       </c>
       <c r="Q37">
-        <v>204.2336102157513</v>
+        <v>198.3818919362013</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1093830693543631</v>
+        <v>0.1103765548130251</v>
       </c>
       <c r="T37">
-        <v>1.239352368821291</v>
+        <v>1.258717249584124</v>
       </c>
       <c r="U37">
         <v>0.2417366166625341</v>
       </c>
       <c r="V37">
-        <v>0.04973356060754647</v>
+        <v>0.0483520728128924</v>
       </c>
       <c r="W37">
-        <v>0.2297141939866847</v>
+        <v>0.230048150172125</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1989342424301859</v>
+        <v>0.1934082912515696</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.153458329142301</v>
+        <v>0.1554176953089264</v>
       </c>
       <c r="C38">
-        <v>266.4561409401183</v>
+        <v>219.9735949434248</v>
       </c>
       <c r="D38">
-        <v>794.7921409401181</v>
+        <v>780.5855949434247</v>
       </c>
       <c r="E38">
-        <v>-1657.764</v>
+        <v>-1625.488</v>
       </c>
       <c r="F38">
-        <v>1161.936</v>
+        <v>1194.212</v>
       </c>
       <c r="G38">
         <v>633.6</v>
@@ -4409,37 +4409,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M38">
-        <v>280.8824774183982</v>
+        <v>288.6847684577982</v>
       </c>
       <c r="N38">
-        <v>-226.5574774183982</v>
+        <v>-234.3597684577982</v>
       </c>
       <c r="O38">
-        <v>-56.63936935459955</v>
+        <v>-58.58994211444954</v>
       </c>
       <c r="P38">
-        <v>-169.9181080637987</v>
+        <v>-175.7698263433486</v>
       </c>
       <c r="Q38">
-        <v>198.3818919362014</v>
+        <v>192.5301736566514</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.110376554813025</v>
+        <v>0.1114015794925969</v>
       </c>
       <c r="T38">
-        <v>1.258717249584123</v>
+        <v>1.278696888466411</v>
       </c>
       <c r="U38">
         <v>0.2417366166625341</v>
       </c>
       <c r="V38">
-        <v>0.04835207281289241</v>
+        <v>0.04704526003416559</v>
       </c>
       <c r="W38">
-        <v>0.230048150172125</v>
+        <v>0.2303640546718658</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1934082912515697</v>
+        <v>0.1881810401366624</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1554176953089264</v>
+        <v>0.1573770614755517</v>
       </c>
       <c r="C39">
-        <v>219.9735949434248</v>
+        <v>173.9900014232064</v>
       </c>
       <c r="D39">
-        <v>780.5855949434247</v>
+        <v>766.8780014232065</v>
       </c>
       <c r="E39">
-        <v>-1625.488</v>
+        <v>-1593.212</v>
       </c>
       <c r="F39">
-        <v>1194.212</v>
+        <v>1226.488</v>
       </c>
       <c r="G39">
         <v>633.6</v>
@@ -4491,37 +4491,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M39">
-        <v>288.6847684577982</v>
+        <v>296.4870594971981</v>
       </c>
       <c r="N39">
-        <v>-234.3597684577982</v>
+        <v>-242.1620594971981</v>
       </c>
       <c r="O39">
-        <v>-58.58994211444954</v>
+        <v>-60.54051487429953</v>
       </c>
       <c r="P39">
-        <v>-175.7698263433486</v>
+        <v>-181.6215446228986</v>
       </c>
       <c r="Q39">
-        <v>192.5301736566514</v>
+        <v>186.6784553771014</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1114015794925969</v>
+        <v>0.1124596694844129</v>
       </c>
       <c r="T39">
-        <v>1.278696888466411</v>
+        <v>1.299321031828773</v>
       </c>
       <c r="U39">
         <v>0.2417366166625341</v>
       </c>
       <c r="V39">
-        <v>0.04704526003416559</v>
+        <v>0.04580722687537175</v>
       </c>
       <c r="W39">
-        <v>0.2303640546718658</v>
+        <v>0.2306633326189886</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1881810401366624</v>
+        <v>0.183228907501487</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1573770614755517</v>
+        <v>0.159336427642177</v>
       </c>
       <c r="C40">
-        <v>173.9900014232064</v>
+        <v>128.4795282138373</v>
       </c>
       <c r="D40">
-        <v>766.8780014232065</v>
+        <v>753.6435282138372</v>
       </c>
       <c r="E40">
-        <v>-1593.212</v>
+        <v>-1560.936</v>
       </c>
       <c r="F40">
-        <v>1226.488</v>
+        <v>1258.764</v>
       </c>
       <c r="G40">
         <v>633.6</v>
@@ -4573,37 +4573,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M40">
-        <v>296.4870594971981</v>
+        <v>304.289350536598</v>
       </c>
       <c r="N40">
-        <v>-242.1620594971981</v>
+        <v>-249.964350536598</v>
       </c>
       <c r="O40">
-        <v>-60.54051487429953</v>
+        <v>-62.49108763414951</v>
       </c>
       <c r="P40">
-        <v>-181.6215446228986</v>
+        <v>-187.4732629024485</v>
       </c>
       <c r="Q40">
-        <v>186.6784553771014</v>
+        <v>180.8267370975515</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1124596694844129</v>
+        <v>0.1135524509513705</v>
       </c>
       <c r="T40">
-        <v>1.299321031828773</v>
+        <v>1.320621376612851</v>
       </c>
       <c r="U40">
         <v>0.2417366166625341</v>
       </c>
       <c r="V40">
-        <v>0.04580722687537175</v>
+        <v>0.04463268259651607</v>
       </c>
       <c r="W40">
-        <v>0.2306633326189886</v>
+        <v>0.2309472629790795</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.183228907501487</v>
+        <v>0.1785307303860643</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.159336427642177</v>
+        <v>0.1612957938088024</v>
       </c>
       <c r="C41">
-        <v>128.4795282138373</v>
+        <v>83.41809610257906</v>
       </c>
       <c r="D41">
-        <v>753.6435282138372</v>
+        <v>740.8580961025789</v>
       </c>
       <c r="E41">
-        <v>-1560.936</v>
+        <v>-1528.66</v>
       </c>
       <c r="F41">
-        <v>1258.764</v>
+        <v>1291.04</v>
       </c>
       <c r="G41">
         <v>633.6</v>
@@ -4655,37 +4655,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M41">
-        <v>304.289350536598</v>
+        <v>312.091641575998</v>
       </c>
       <c r="N41">
-        <v>-249.964350536598</v>
+        <v>-257.7666415759981</v>
       </c>
       <c r="O41">
-        <v>-62.49108763414951</v>
+        <v>-64.44166039399951</v>
       </c>
       <c r="P41">
-        <v>-187.4732629024485</v>
+        <v>-193.3249811819985</v>
       </c>
       <c r="Q41">
-        <v>180.8267370975515</v>
+        <v>174.9750188180015</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1135524509513705</v>
+        <v>0.1146816584672267</v>
       </c>
       <c r="T41">
-        <v>1.320621376612851</v>
+        <v>1.342631732889732</v>
       </c>
       <c r="U41">
         <v>0.2417366166625341</v>
       </c>
       <c r="V41">
-        <v>0.04463268259651607</v>
+        <v>0.04351686553160316</v>
       </c>
       <c r="W41">
-        <v>0.2309472629790795</v>
+        <v>0.2312169968211659</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1785307303860643</v>
+        <v>0.1740674621264127</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1612957938088024</v>
+        <v>0.1632551599754277</v>
       </c>
       <c r="C42">
-        <v>83.41809610257906</v>
+        <v>38.78323261733431</v>
       </c>
       <c r="D42">
-        <v>740.8580961025789</v>
+        <v>728.4992326173343</v>
       </c>
       <c r="E42">
-        <v>-1528.66</v>
+        <v>-1496.384</v>
       </c>
       <c r="F42">
-        <v>1291.04</v>
+        <v>1323.316</v>
       </c>
       <c r="G42">
         <v>633.6</v>
@@ -4737,37 +4737,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M42">
-        <v>312.091641575998</v>
+        <v>319.893932615398</v>
       </c>
       <c r="N42">
-        <v>-257.7666415759981</v>
+        <v>-265.568932615398</v>
       </c>
       <c r="O42">
-        <v>-64.44166039399951</v>
+        <v>-66.3922331538495</v>
       </c>
       <c r="P42">
-        <v>-193.3249811819985</v>
+        <v>-199.1766994615485</v>
       </c>
       <c r="Q42">
-        <v>174.9750188180015</v>
+        <v>169.1233005384515</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1146816584672267</v>
+        <v>0.1158491442039594</v>
       </c>
       <c r="T42">
-        <v>1.342631732889732</v>
+        <v>1.36538820293871</v>
       </c>
       <c r="U42">
         <v>0.2417366166625341</v>
       </c>
       <c r="V42">
-        <v>0.04351686553160316</v>
+        <v>0.04245547856741771</v>
       </c>
       <c r="W42">
-        <v>0.2312169968211659</v>
+        <v>0.2314735729148578</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1740674621264127</v>
+        <v>0.1698219142696709</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1632551599754277</v>
+        <v>0.1652145261420531</v>
       </c>
       <c r="C43">
-        <v>38.78323261733431</v>
+        <v>-5.446059791203425</v>
       </c>
       <c r="D43">
-        <v>728.4992326173343</v>
+        <v>716.5459402087965</v>
       </c>
       <c r="E43">
-        <v>-1496.384</v>
+        <v>-1464.108</v>
       </c>
       <c r="F43">
-        <v>1323.316</v>
+        <v>1355.592</v>
       </c>
       <c r="G43">
         <v>633.6</v>
@@ -4819,37 +4819,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M43">
-        <v>319.893932615398</v>
+        <v>327.696223654798</v>
       </c>
       <c r="N43">
-        <v>-265.568932615398</v>
+        <v>-273.371223654798</v>
       </c>
       <c r="O43">
-        <v>-66.3922331538495</v>
+        <v>-68.34280591369949</v>
       </c>
       <c r="P43">
-        <v>-199.1766994615485</v>
+        <v>-205.0284177410985</v>
       </c>
       <c r="Q43">
-        <v>169.1233005384515</v>
+        <v>163.2715822589015</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1158491442039594</v>
+        <v>0.1170568880695449</v>
       </c>
       <c r="T43">
-        <v>1.36538820293871</v>
+        <v>1.388929378851447</v>
       </c>
       <c r="U43">
         <v>0.2417366166625341</v>
       </c>
       <c r="V43">
-        <v>0.04245547856741771</v>
+        <v>0.04144463383962205</v>
       </c>
       <c r="W43">
-        <v>0.2314735729148578</v>
+        <v>0.2317179310993263</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1698219142696709</v>
+        <v>0.1657785353584882</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1652145261420531</v>
+        <v>0.1671738923086784</v>
       </c>
       <c r="C44">
-        <v>-5.446059791203197</v>
+        <v>-49.2894227996112</v>
       </c>
       <c r="D44">
-        <v>716.5459402087965</v>
+        <v>704.9785772003888</v>
       </c>
       <c r="E44">
-        <v>-1464.108</v>
+        <v>-1431.832</v>
       </c>
       <c r="F44">
-        <v>1355.592</v>
+        <v>1387.868</v>
       </c>
       <c r="G44">
         <v>633.6</v>
@@ -4901,37 +4901,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M44">
-        <v>327.6962236547979</v>
+        <v>335.4985146941979</v>
       </c>
       <c r="N44">
-        <v>-273.3712236547979</v>
+        <v>-281.1735146941979</v>
       </c>
       <c r="O44">
-        <v>-68.34280591369948</v>
+        <v>-70.29337867354947</v>
       </c>
       <c r="P44">
-        <v>-205.0284177410985</v>
+        <v>-210.8801360206484</v>
       </c>
       <c r="Q44">
-        <v>163.2715822589016</v>
+        <v>157.4198639793516</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1170568880695449</v>
+        <v>0.1183070089128702</v>
       </c>
       <c r="T44">
-        <v>1.388929378851447</v>
+        <v>1.41329656093656</v>
       </c>
       <c r="U44">
         <v>0.2417366166625341</v>
       </c>
       <c r="V44">
-        <v>0.04144463383962206</v>
+        <v>0.04048080514567736</v>
       </c>
       <c r="W44">
-        <v>0.2317179310993263</v>
+        <v>0.2319509237868428</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1657785353584883</v>
+        <v>0.1619232205827095</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1671738923086784</v>
+        <v>0.1691332584753037</v>
       </c>
       <c r="C45">
-        <v>-49.2894227996112</v>
+        <v>-92.76524991387419</v>
       </c>
       <c r="D45">
-        <v>704.9785772003888</v>
+        <v>693.7787500861259</v>
       </c>
       <c r="E45">
-        <v>-1431.832</v>
+        <v>-1399.556</v>
       </c>
       <c r="F45">
-        <v>1387.868</v>
+        <v>1420.144</v>
       </c>
       <c r="G45">
         <v>633.6</v>
@@ -4983,37 +4983,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M45">
-        <v>335.4985146941979</v>
+        <v>343.3008057335978</v>
       </c>
       <c r="N45">
-        <v>-281.1735146941979</v>
+        <v>-288.9758057335978</v>
       </c>
       <c r="O45">
-        <v>-70.29337867354947</v>
+        <v>-72.24395143339946</v>
       </c>
       <c r="P45">
-        <v>-210.8801360206484</v>
+        <v>-216.7318543001984</v>
       </c>
       <c r="Q45">
-        <v>157.4198639793516</v>
+        <v>151.5681456998016</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1183070089128702</v>
+        <v>0.1196017769291715</v>
       </c>
       <c r="T45">
-        <v>1.41329656093656</v>
+        <v>1.438533999524713</v>
       </c>
       <c r="U45">
         <v>0.2417366166625341</v>
       </c>
       <c r="V45">
-        <v>0.04048080514567736</v>
+        <v>0.03956078684691196</v>
       </c>
       <c r="W45">
-        <v>0.2319509237868428</v>
+        <v>0.2321733258976539</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1619232205827095</v>
+        <v>0.1582431473876479</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1691332584753037</v>
+        <v>0.1710926246419291</v>
       </c>
       <c r="C46">
-        <v>-92.76524991387419</v>
+        <v>-135.8907840658424</v>
       </c>
       <c r="D46">
-        <v>693.7787500861259</v>
+        <v>682.9292159341577</v>
       </c>
       <c r="E46">
-        <v>-1399.556</v>
+        <v>-1367.28</v>
       </c>
       <c r="F46">
-        <v>1420.144</v>
+        <v>1452.42</v>
       </c>
       <c r="G46">
         <v>633.6</v>
@@ -5065,37 +5065,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M46">
-        <v>343.3008057335978</v>
+        <v>351.1030967729978</v>
       </c>
       <c r="N46">
-        <v>-288.9758057335978</v>
+        <v>-296.7780967729978</v>
       </c>
       <c r="O46">
-        <v>-72.24395143339946</v>
+        <v>-74.19452419324945</v>
       </c>
       <c r="P46">
-        <v>-216.7318543001984</v>
+        <v>-222.5835725797484</v>
       </c>
       <c r="Q46">
-        <v>151.5681456998016</v>
+        <v>145.7164274202516</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1196017769291715</v>
+        <v>0.1209436274187927</v>
       </c>
       <c r="T46">
-        <v>1.438533999524713</v>
+        <v>1.464689163152435</v>
       </c>
       <c r="U46">
         <v>0.2417366166625341</v>
       </c>
       <c r="V46">
-        <v>0.03956078684691196</v>
+        <v>0.03868165825031392</v>
       </c>
       <c r="W46">
-        <v>0.2321733258976539</v>
+        <v>0.2323858434702068</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1582431473876479</v>
+        <v>0.1547266330012557</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1710926246419291</v>
+        <v>0.1730519908085544</v>
       </c>
       <c r="C47">
-        <v>-135.8907840658424</v>
+        <v>-178.6822061932221</v>
       </c>
       <c r="D47">
-        <v>682.9292159341577</v>
+        <v>672.4137938067779</v>
       </c>
       <c r="E47">
-        <v>-1367.28</v>
+        <v>-1335.004</v>
       </c>
       <c r="F47">
-        <v>1452.42</v>
+        <v>1484.696</v>
       </c>
       <c r="G47">
         <v>633.6</v>
@@ -5147,37 +5147,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M47">
-        <v>351.1030967729978</v>
+        <v>358.9053878123977</v>
       </c>
       <c r="N47">
-        <v>-296.7780967729978</v>
+        <v>-304.5803878123977</v>
       </c>
       <c r="O47">
-        <v>-74.19452419324945</v>
+        <v>-76.14509695309943</v>
       </c>
       <c r="P47">
-        <v>-222.5835725797484</v>
+        <v>-228.4352908592983</v>
       </c>
       <c r="Q47">
-        <v>145.7164274202516</v>
+        <v>139.8647091407017</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1209436274187927</v>
+        <v>0.1223351760746963</v>
       </c>
       <c r="T47">
-        <v>1.464689163152435</v>
+        <v>1.491813036544146</v>
       </c>
       <c r="U47">
         <v>0.2417366166625341</v>
       </c>
       <c r="V47">
-        <v>0.03868165825031392</v>
+        <v>0.03784075263617667</v>
       </c>
       <c r="W47">
-        <v>0.2323858434702068</v>
+        <v>0.2325891211483009</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1547266330012557</v>
+        <v>0.1513630105447067</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1730519908085544</v>
+        <v>0.1750113569751798</v>
       </c>
       <c r="C48">
-        <v>-178.6822061932221</v>
+        <v>-221.154715760181</v>
       </c>
       <c r="D48">
-        <v>672.4137938067779</v>
+        <v>662.217284239819</v>
       </c>
       <c r="E48">
-        <v>-1335.004</v>
+        <v>-1302.728</v>
       </c>
       <c r="F48">
-        <v>1484.696</v>
+        <v>1516.972</v>
       </c>
       <c r="G48">
         <v>633.6</v>
@@ -5229,37 +5229,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M48">
-        <v>358.9053878123977</v>
+        <v>366.7076788517977</v>
       </c>
       <c r="N48">
-        <v>-304.5803878123977</v>
+        <v>-312.3826788517977</v>
       </c>
       <c r="O48">
-        <v>-76.14509695309943</v>
+        <v>-78.09566971294942</v>
       </c>
       <c r="P48">
-        <v>-228.4352908592983</v>
+        <v>-234.2870091388482</v>
       </c>
       <c r="Q48">
-        <v>139.8647091407017</v>
+        <v>134.0129908611518</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1223351760746963</v>
+        <v>0.123779236000634</v>
       </c>
       <c r="T48">
-        <v>1.491813036544146</v>
+        <v>1.519960452327998</v>
       </c>
       <c r="U48">
         <v>0.2417366166625341</v>
       </c>
       <c r="V48">
-        <v>0.03784075263617667</v>
+        <v>0.03703563023966227</v>
       </c>
       <c r="W48">
-        <v>0.2325891211483009</v>
+        <v>0.2327837487124335</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1513630105447067</v>
+        <v>0.1481425209586491</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1750113569751798</v>
+        <v>0.1769707231418051</v>
       </c>
       <c r="C49">
-        <v>-221.154715760181</v>
+        <v>-263.3226040612867</v>
       </c>
       <c r="D49">
-        <v>662.217284239819</v>
+        <v>652.3253959387132</v>
       </c>
       <c r="E49">
-        <v>-1302.728</v>
+        <v>-1270.452</v>
       </c>
       <c r="F49">
-        <v>1516.972</v>
+        <v>1549.248</v>
       </c>
       <c r="G49">
         <v>633.6</v>
@@ -5311,37 +5311,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M49">
-        <v>366.7076788517977</v>
+        <v>374.5099698911976</v>
       </c>
       <c r="N49">
-        <v>-312.3826788517977</v>
+        <v>-320.1849698911976</v>
       </c>
       <c r="O49">
-        <v>-78.09566971294942</v>
+        <v>-80.04624247279941</v>
       </c>
       <c r="P49">
-        <v>-234.2870091388482</v>
+        <v>-240.1387274183982</v>
       </c>
       <c r="Q49">
-        <v>134.0129908611518</v>
+        <v>128.1612725816018</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.123779236000634</v>
+        <v>0.1252788366929539</v>
       </c>
       <c r="T49">
-        <v>1.519960452327998</v>
+        <v>1.549190461026614</v>
       </c>
       <c r="U49">
         <v>0.2417366166625341</v>
       </c>
       <c r="V49">
-        <v>0.03703563023966227</v>
+        <v>0.03626405460966931</v>
       </c>
       <c r="W49">
-        <v>0.2327837487124335</v>
+        <v>0.2329702667947273</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1481425209586491</v>
+        <v>0.1450562184386772</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1769707231418051</v>
+        <v>0.1789300893084304</v>
       </c>
       <c r="C50">
-        <v>-263.3226040612865</v>
+        <v>-305.1993210522564</v>
       </c>
       <c r="D50">
-        <v>652.3253959387132</v>
+        <v>642.7246789477433</v>
       </c>
       <c r="E50">
-        <v>-1270.452</v>
+        <v>-1238.176</v>
       </c>
       <c r="F50">
-        <v>1549.248</v>
+        <v>1581.524</v>
       </c>
       <c r="G50">
         <v>633.6</v>
@@ -5393,37 +5393,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M50">
-        <v>374.5099698911976</v>
+        <v>382.3122609305976</v>
       </c>
       <c r="N50">
-        <v>-320.1849698911976</v>
+        <v>-327.9872609305976</v>
       </c>
       <c r="O50">
-        <v>-80.04624247279939</v>
+        <v>-81.9968152326494</v>
       </c>
       <c r="P50">
-        <v>-240.1387274183982</v>
+        <v>-245.9904456979482</v>
       </c>
       <c r="Q50">
-        <v>128.1612725816018</v>
+        <v>122.3095543020518</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1252788366929539</v>
+        <v>0.1268372452555608</v>
       </c>
       <c r="T50">
-        <v>1.549190461026614</v>
+        <v>1.579566744576155</v>
       </c>
       <c r="U50">
         <v>0.2417366166625341</v>
       </c>
       <c r="V50">
-        <v>0.03626405460966931</v>
+        <v>0.03552397186253319</v>
       </c>
       <c r="W50">
-        <v>0.2329702667947273</v>
+        <v>0.2331491718940703</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1450562184386772</v>
+        <v>0.1420958874501328</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1789300893084304</v>
+        <v>0.1808894554750558</v>
       </c>
       <c r="C51">
-        <v>-305.1993210522564</v>
+        <v>-346.7975363647456</v>
       </c>
       <c r="D51">
-        <v>642.7246789477433</v>
+        <v>633.4024636352543</v>
       </c>
       <c r="E51">
-        <v>-1238.176</v>
+        <v>-1205.9</v>
       </c>
       <c r="F51">
-        <v>1581.524</v>
+        <v>1613.8</v>
       </c>
       <c r="G51">
         <v>633.6</v>
@@ -5475,37 +5475,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M51">
-        <v>382.3122609305976</v>
+        <v>390.1145519699975</v>
       </c>
       <c r="N51">
-        <v>-327.9872609305976</v>
+        <v>-335.7895519699975</v>
       </c>
       <c r="O51">
-        <v>-81.9968152326494</v>
+        <v>-83.94738799249939</v>
       </c>
       <c r="P51">
-        <v>-245.9904456979482</v>
+        <v>-251.8421639774982</v>
       </c>
       <c r="Q51">
-        <v>122.3095543020518</v>
+        <v>116.4578360225019</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1268372452555608</v>
+        <v>0.128457990160672</v>
       </c>
       <c r="T51">
-        <v>1.579566744576155</v>
+        <v>1.611158079467678</v>
       </c>
       <c r="U51">
         <v>0.2417366166625341</v>
       </c>
       <c r="V51">
-        <v>0.03552397186253319</v>
+        <v>0.03481349242528253</v>
       </c>
       <c r="W51">
-        <v>0.2331491718940703</v>
+        <v>0.2333209207894395</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1420958874501328</v>
+        <v>0.1392539697011301</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1808894554750558</v>
+        <v>0.1828488216416811</v>
       </c>
       <c r="C52">
-        <v>-346.7975363647456</v>
+        <v>-388.129195087218</v>
       </c>
       <c r="D52">
-        <v>633.4024636352543</v>
+        <v>624.346804912782</v>
       </c>
       <c r="E52">
-        <v>-1205.9</v>
+        <v>-1173.624</v>
       </c>
       <c r="F52">
-        <v>1613.8</v>
+        <v>1646.076</v>
       </c>
       <c r="G52">
         <v>633.6</v>
@@ -5557,37 +5557,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M52">
-        <v>390.1145519699975</v>
+        <v>397.9168430093975</v>
       </c>
       <c r="N52">
-        <v>-335.7895519699975</v>
+        <v>-343.5918430093975</v>
       </c>
       <c r="O52">
-        <v>-83.94738799249939</v>
+        <v>-85.89796075234938</v>
       </c>
       <c r="P52">
-        <v>-251.8421639774982</v>
+        <v>-257.6938822570481</v>
       </c>
       <c r="Q52">
-        <v>116.4578360225019</v>
+        <v>110.6061177429519</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.128457990160672</v>
+        <v>0.1301448879190531</v>
       </c>
       <c r="T52">
-        <v>1.611158079467678</v>
+        <v>1.644038856599671</v>
       </c>
       <c r="U52">
         <v>0.2417366166625341</v>
       </c>
       <c r="V52">
-        <v>0.03481349242528253</v>
+        <v>0.03413087492674758</v>
       </c>
       <c r="W52">
-        <v>0.2333209207894395</v>
+        <v>0.23348593443401</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1392539697011301</v>
+        <v>0.1365234997069903</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1828488216416811</v>
+        <v>0.1848081878083065</v>
       </c>
       <c r="C53">
-        <v>-388.129195087218</v>
+        <v>-429.2055688283224</v>
       </c>
       <c r="D53">
-        <v>624.346804912782</v>
+        <v>615.5464311716776</v>
       </c>
       <c r="E53">
-        <v>-1173.624</v>
+        <v>-1141.348</v>
       </c>
       <c r="F53">
-        <v>1646.076</v>
+        <v>1678.352</v>
       </c>
       <c r="G53">
         <v>633.6</v>
@@ -5639,37 +5639,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M53">
-        <v>397.9168430093975</v>
+        <v>405.7191340487975</v>
       </c>
       <c r="N53">
-        <v>-343.5918430093975</v>
+        <v>-351.3941340487975</v>
       </c>
       <c r="O53">
-        <v>-85.89796075234938</v>
+        <v>-87.84853351219937</v>
       </c>
       <c r="P53">
-        <v>-257.6938822570481</v>
+        <v>-263.5456005365981</v>
       </c>
       <c r="Q53">
-        <v>110.6061177429519</v>
+        <v>104.7543994634019</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1301448879190531</v>
+        <v>0.1319020730840334</v>
       </c>
       <c r="T53">
-        <v>1.644038856599671</v>
+        <v>1.678289666112165</v>
       </c>
       <c r="U53">
         <v>0.2417366166625341</v>
       </c>
       <c r="V53">
-        <v>0.03413087492674758</v>
+        <v>0.03347451194738705</v>
       </c>
       <c r="W53">
-        <v>0.23348593443401</v>
+        <v>0.2336446013999432</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1365234997069903</v>
+        <v>0.1338980477895482</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1848081878083065</v>
+        <v>0.1867675539749318</v>
       </c>
       <c r="C54">
-        <v>-429.2055688283224</v>
+        <v>-470.0373025217598</v>
       </c>
       <c r="D54">
-        <v>615.5464311716776</v>
+        <v>606.9906974782402</v>
       </c>
       <c r="E54">
-        <v>-1141.348</v>
+        <v>-1109.072</v>
       </c>
       <c r="F54">
-        <v>1678.352</v>
+        <v>1710.628</v>
       </c>
       <c r="G54">
         <v>633.6</v>
@@ -5721,37 +5721,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M54">
-        <v>405.7191340487975</v>
+        <v>413.5214250881974</v>
       </c>
       <c r="N54">
-        <v>-351.3941340487975</v>
+        <v>-359.1964250881974</v>
       </c>
       <c r="O54">
-        <v>-87.84853351219937</v>
+        <v>-89.79910627204934</v>
       </c>
       <c r="P54">
-        <v>-263.5456005365981</v>
+        <v>-269.397318816148</v>
       </c>
       <c r="Q54">
-        <v>104.7543994634019</v>
+        <v>98.902681183852</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1319020730840334</v>
+        <v>0.1337340320858213</v>
       </c>
       <c r="T54">
-        <v>1.678289666112165</v>
+        <v>1.713997956880509</v>
       </c>
       <c r="U54">
         <v>0.2417366166625341</v>
       </c>
       <c r="V54">
-        <v>0.03347451194738705</v>
+        <v>0.03284291738234201</v>
       </c>
       <c r="W54">
-        <v>0.2336446013999432</v>
+        <v>0.2337972809331996</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1338980477895482</v>
+        <v>0.1313716695293681</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1867675539749318</v>
+        <v>0.1887269201415572</v>
       </c>
       <c r="C55">
-        <v>-470.0373025217598</v>
+        <v>-510.6344573813012</v>
       </c>
       <c r="D55">
-        <v>606.9906974782402</v>
+        <v>598.6695426186989</v>
       </c>
       <c r="E55">
-        <v>-1109.072</v>
+        <v>-1076.796</v>
       </c>
       <c r="F55">
-        <v>1710.628</v>
+        <v>1742.904</v>
       </c>
       <c r="G55">
         <v>633.6</v>
@@ -5803,37 +5803,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M55">
-        <v>413.5214250881974</v>
+        <v>421.3237161275973</v>
       </c>
       <c r="N55">
-        <v>-359.1964250881974</v>
+        <v>-366.9987161275973</v>
       </c>
       <c r="O55">
-        <v>-89.79910627204934</v>
+        <v>-91.74967903189933</v>
       </c>
       <c r="P55">
-        <v>-269.397318816148</v>
+        <v>-275.249037095698</v>
       </c>
       <c r="Q55">
-        <v>98.902681183852</v>
+        <v>93.05096290430203</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1337340320858213</v>
+        <v>0.1356456414789914</v>
       </c>
       <c r="T55">
-        <v>1.713997956880509</v>
+        <v>1.751258782030085</v>
       </c>
       <c r="U55">
         <v>0.2417366166625341</v>
       </c>
       <c r="V55">
-        <v>0.03284291738234201</v>
+        <v>0.03223471520859494</v>
       </c>
       <c r="W55">
-        <v>0.2337972809331996</v>
+        <v>0.233944305668928</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1313716695293681</v>
+        <v>0.1289388608343798</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1887269201415572</v>
+        <v>0.1906862863081825</v>
       </c>
       <c r="C56">
-        <v>-510.6344573813012</v>
+        <v>-551.0065503703993</v>
       </c>
       <c r="D56">
-        <v>598.6695426186989</v>
+        <v>590.5734496296008</v>
       </c>
       <c r="E56">
-        <v>-1076.796</v>
+        <v>-1044.52</v>
       </c>
       <c r="F56">
-        <v>1742.904</v>
+        <v>1775.18</v>
       </c>
       <c r="G56">
         <v>633.6</v>
@@ -5885,37 +5885,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M56">
-        <v>421.3237161275973</v>
+        <v>429.1260071669973</v>
       </c>
       <c r="N56">
-        <v>-366.9987161275973</v>
+        <v>-374.8010071669973</v>
       </c>
       <c r="O56">
-        <v>-91.74967903189933</v>
+        <v>-93.70025179174932</v>
       </c>
       <c r="P56">
-        <v>-275.249037095698</v>
+        <v>-281.100755375248</v>
       </c>
       <c r="Q56">
-        <v>93.05096290430203</v>
+        <v>87.19924462475205</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1356456414789914</v>
+        <v>0.1376422112896356</v>
       </c>
       <c r="T56">
-        <v>1.751258782030085</v>
+        <v>1.790175643852976</v>
       </c>
       <c r="U56">
         <v>0.2417366166625341</v>
       </c>
       <c r="V56">
-        <v>0.03223471520859494</v>
+        <v>0.03164862947752958</v>
       </c>
       <c r="W56">
-        <v>0.233944305668928</v>
+        <v>0.23408598405063</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1289388608343798</v>
+        <v>0.1265945179101183</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1906862863081825</v>
+        <v>0.1926456524748079</v>
       </c>
       <c r="C57">
-        <v>-551.0065503703993</v>
+        <v>-591.1625905119349</v>
       </c>
       <c r="D57">
-        <v>590.5734496296008</v>
+        <v>582.6934094880652</v>
       </c>
       <c r="E57">
-        <v>-1044.52</v>
+        <v>-1012.244</v>
       </c>
       <c r="F57">
-        <v>1775.18</v>
+        <v>1807.456</v>
       </c>
       <c r="G57">
         <v>633.6</v>
@@ -5967,37 +5967,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M57">
-        <v>429.1260071669973</v>
+        <v>436.9282982063972</v>
       </c>
       <c r="N57">
-        <v>-374.8010071669973</v>
+        <v>-382.6032982063973</v>
       </c>
       <c r="O57">
-        <v>-93.70025179174932</v>
+        <v>-95.65082455159931</v>
       </c>
       <c r="P57">
-        <v>-281.100755375248</v>
+        <v>-286.9524736547979</v>
       </c>
       <c r="Q57">
-        <v>87.19924462475205</v>
+        <v>81.34752634520208</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1376422112896356</v>
+        <v>0.139729534273491</v>
       </c>
       <c r="T57">
-        <v>1.790175643852976</v>
+        <v>1.830861453940543</v>
       </c>
       <c r="U57">
         <v>0.2417366166625341</v>
       </c>
       <c r="V57">
-        <v>0.03164862947752958</v>
+        <v>0.03108347537971655</v>
       </c>
       <c r="W57">
-        <v>0.23408598405063</v>
+        <v>0.2342226024901282</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1265945179101183</v>
+        <v>0.1243339015188661</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1926456524748079</v>
+        <v>0.1946050186414332</v>
       </c>
       <c r="C58">
-        <v>-591.1625905119349</v>
+        <v>-631.1111123293447</v>
       </c>
       <c r="D58">
-        <v>582.6934094880652</v>
+        <v>575.0208876706554</v>
       </c>
       <c r="E58">
-        <v>-1012.244</v>
+        <v>-979.9679999999996</v>
       </c>
       <c r="F58">
-        <v>1807.456</v>
+        <v>1839.732</v>
       </c>
       <c r="G58">
         <v>633.6</v>
@@ -6049,37 +6049,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M58">
-        <v>436.9282982063972</v>
+        <v>444.7305892457972</v>
       </c>
       <c r="N58">
-        <v>-382.6032982063973</v>
+        <v>-390.4055892457972</v>
       </c>
       <c r="O58">
-        <v>-95.65082455159931</v>
+        <v>-97.6013973114493</v>
       </c>
       <c r="P58">
-        <v>-286.9524736547979</v>
+        <v>-292.8041919343479</v>
       </c>
       <c r="Q58">
-        <v>81.34752634520208</v>
+        <v>75.49580806565211</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.139729534273491</v>
+        <v>0.1419139420472931</v>
       </c>
       <c r="T58">
-        <v>1.830861453940543</v>
+        <v>1.873439627287998</v>
       </c>
       <c r="U58">
         <v>0.2417366166625341</v>
       </c>
       <c r="V58">
-        <v>0.03108347537971655</v>
+        <v>0.03053815125024783</v>
       </c>
       <c r="W58">
-        <v>0.2342226024901282</v>
+        <v>0.2343544273001704</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1243339015188661</v>
+        <v>0.1221526050009913</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1946050186414332</v>
+        <v>0.1965643848080585</v>
       </c>
       <c r="C59">
-        <v>-631.1111123293447</v>
+        <v>-670.8602066801038</v>
       </c>
       <c r="D59">
-        <v>575.0208876706554</v>
+        <v>567.5477933198964</v>
       </c>
       <c r="E59">
-        <v>-979.9679999999996</v>
+        <v>-947.6919999999996</v>
       </c>
       <c r="F59">
-        <v>1839.732</v>
+        <v>1872.008</v>
       </c>
       <c r="G59">
         <v>633.6</v>
@@ -6131,37 +6131,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M59">
-        <v>444.7305892457972</v>
+        <v>452.5328802851972</v>
       </c>
       <c r="N59">
-        <v>-390.4055892457972</v>
+        <v>-398.2078802851972</v>
       </c>
       <c r="O59">
-        <v>-97.6013973114493</v>
+        <v>-99.55197007129931</v>
       </c>
       <c r="P59">
-        <v>-292.8041919343479</v>
+        <v>-298.6559102138979</v>
       </c>
       <c r="Q59">
-        <v>75.49580806565211</v>
+        <v>69.64408978610209</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1419139420472931</v>
+        <v>0.1442023692388953</v>
       </c>
       <c r="T59">
-        <v>1.873439627287998</v>
+        <v>1.918045332699617</v>
       </c>
       <c r="U59">
         <v>0.2417366166625341</v>
       </c>
       <c r="V59">
-        <v>0.03053815125024783</v>
+        <v>0.03001163140110562</v>
       </c>
       <c r="W59">
-        <v>0.2343544273001704</v>
+        <v>0.2344817064271078</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1221526050009913</v>
+        <v>0.1200465256044225</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1965643848080585</v>
+        <v>0.1985237509746838</v>
       </c>
       <c r="C60">
-        <v>-670.8602066801034</v>
+        <v>-710.4175492157394</v>
       </c>
       <c r="D60">
-        <v>567.5477933198964</v>
+        <v>560.2664507842603</v>
       </c>
       <c r="E60">
-        <v>-947.692</v>
+        <v>-915.4159999999999</v>
       </c>
       <c r="F60">
-        <v>1872.008</v>
+        <v>1904.284</v>
       </c>
       <c r="G60">
         <v>633.6</v>
@@ -6213,37 +6213,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M60">
-        <v>452.5328802851971</v>
+        <v>460.3351713245971</v>
       </c>
       <c r="N60">
-        <v>-398.2078802851971</v>
+        <v>-406.0101713245971</v>
       </c>
       <c r="O60">
-        <v>-99.55197007129928</v>
+        <v>-101.5025428311493</v>
       </c>
       <c r="P60">
-        <v>-298.6559102138979</v>
+        <v>-304.5076284934478</v>
       </c>
       <c r="Q60">
-        <v>69.64408978610214</v>
+        <v>63.79237150655223</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1442023692388953</v>
+        <v>0.1466024270252098</v>
       </c>
       <c r="T60">
-        <v>1.918045332699617</v>
+        <v>1.964826926180095</v>
       </c>
       <c r="U60">
         <v>0.2417366166625341</v>
       </c>
       <c r="V60">
-        <v>0.03001163140110563</v>
+        <v>0.02950295968244282</v>
       </c>
       <c r="W60">
-        <v>0.2344817064271078</v>
+        <v>0.2346046710073692</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1200465256044225</v>
+        <v>0.1180118387297713</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1985237509746838</v>
+        <v>0.2004831171413092</v>
       </c>
       <c r="C61">
-        <v>-710.4175492157394</v>
+        <v>-749.790426678838</v>
       </c>
       <c r="D61">
-        <v>560.2664507842603</v>
+        <v>553.1695733211619</v>
       </c>
       <c r="E61">
-        <v>-915.4159999999999</v>
+        <v>-883.1399999999999</v>
       </c>
       <c r="F61">
-        <v>1904.284</v>
+        <v>1936.56</v>
       </c>
       <c r="G61">
         <v>633.6</v>
@@ -6295,37 +6295,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M61">
-        <v>460.3351713245971</v>
+        <v>468.137462363997</v>
       </c>
       <c r="N61">
-        <v>-406.0101713245971</v>
+        <v>-413.812462363997</v>
       </c>
       <c r="O61">
-        <v>-101.5025428311493</v>
+        <v>-103.4531155909993</v>
       </c>
       <c r="P61">
-        <v>-304.5076284934478</v>
+        <v>-310.3593467729978</v>
       </c>
       <c r="Q61">
-        <v>63.79237150655223</v>
+        <v>57.9406532270022</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1466024270252098</v>
+        <v>0.1491224877008401</v>
       </c>
       <c r="T61">
-        <v>1.964826926180095</v>
+        <v>2.013947599334597</v>
       </c>
       <c r="U61">
         <v>0.2417366166625341</v>
       </c>
       <c r="V61">
-        <v>0.02950295968244282</v>
+        <v>0.02901124368773544</v>
       </c>
       <c r="W61">
-        <v>0.2346046710073692</v>
+        <v>0.2347235367682886</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1180118387297713</v>
+        <v>0.1160449747509418</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2004831171413092</v>
+        <v>0.2024424833079346</v>
       </c>
       <c r="C62">
-        <v>-749.790426678838</v>
+        <v>-788.9857612264229</v>
       </c>
       <c r="D62">
-        <v>553.1695733211619</v>
+        <v>546.2502387735771</v>
       </c>
       <c r="E62">
-        <v>-883.1399999999999</v>
+        <v>-850.8639999999998</v>
       </c>
       <c r="F62">
-        <v>1936.56</v>
+        <v>1968.836</v>
       </c>
       <c r="G62">
         <v>633.6</v>
@@ -6377,37 +6377,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M62">
-        <v>468.137462363997</v>
+        <v>475.939753403397</v>
       </c>
       <c r="N62">
-        <v>-413.812462363997</v>
+        <v>-421.614753403397</v>
       </c>
       <c r="O62">
-        <v>-103.4531155909993</v>
+        <v>-105.4036883508493</v>
       </c>
       <c r="P62">
-        <v>-310.3593467729978</v>
+        <v>-316.2110650525477</v>
       </c>
       <c r="Q62">
-        <v>57.9406532270022</v>
+        <v>52.08893494745229</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1491224877008401</v>
+        <v>0.1517717822572719</v>
       </c>
       <c r="T62">
-        <v>2.013947599334597</v>
+        <v>2.065587281368818</v>
       </c>
       <c r="U62">
         <v>0.2417366166625341</v>
       </c>
       <c r="V62">
-        <v>0.02901124368773544</v>
+        <v>0.02853564952892011</v>
       </c>
       <c r="W62">
-        <v>0.2347235367682886</v>
+        <v>0.2348385052911451</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1160449747509418</v>
+        <v>0.1141425981156804</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2024424833079346</v>
+        <v>0.2044018494745599</v>
       </c>
       <c r="C63">
-        <v>-788.9857612264229</v>
+        <v>-828.0101329503957</v>
       </c>
       <c r="D63">
-        <v>546.2502387735771</v>
+        <v>539.5018670496041</v>
       </c>
       <c r="E63">
-        <v>-850.8639999999998</v>
+        <v>-818.588</v>
       </c>
       <c r="F63">
-        <v>1968.836</v>
+        <v>2001.112</v>
       </c>
       <c r="G63">
         <v>633.6</v>
@@ -6459,37 +6459,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M63">
-        <v>475.939753403397</v>
+        <v>483.7420444427969</v>
       </c>
       <c r="N63">
-        <v>-421.614753403397</v>
+        <v>-429.4170444427969</v>
       </c>
       <c r="O63">
-        <v>-105.4036883508493</v>
+        <v>-107.3542611106992</v>
       </c>
       <c r="P63">
-        <v>-316.2110650525477</v>
+        <v>-322.0627833320977</v>
       </c>
       <c r="Q63">
-        <v>52.08893494745229</v>
+        <v>46.23721666790232</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1517717822572719</v>
+        <v>0.1545605133693053</v>
       </c>
       <c r="T63">
-        <v>2.065587281368818</v>
+        <v>2.11994484140484</v>
       </c>
       <c r="U63">
         <v>0.2417366166625341</v>
       </c>
       <c r="V63">
-        <v>0.02853564952892011</v>
+        <v>0.02807539711716333</v>
       </c>
       <c r="W63">
-        <v>0.2348385052911451</v>
+        <v>0.234949765151974</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1141425981156804</v>
+        <v>0.1123015884686533</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2044018494745599</v>
+        <v>0.2063612156411852</v>
       </c>
       <c r="C64">
-        <v>-828.0101329503957</v>
+        <v>-866.8698007490411</v>
       </c>
       <c r="D64">
-        <v>539.5018670496041</v>
+        <v>532.9181992509588</v>
       </c>
       <c r="E64">
-        <v>-818.588</v>
+        <v>-786.3119999999999</v>
       </c>
       <c r="F64">
-        <v>2001.112</v>
+        <v>2033.388</v>
       </c>
       <c r="G64">
         <v>633.6</v>
@@ -6541,37 +6541,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M64">
-        <v>483.7420444427969</v>
+        <v>491.5443354821969</v>
       </c>
       <c r="N64">
-        <v>-429.4170444427969</v>
+        <v>-437.2193354821969</v>
       </c>
       <c r="O64">
-        <v>-107.3542611106992</v>
+        <v>-109.3048338705492</v>
       </c>
       <c r="P64">
-        <v>-322.0627833320977</v>
+        <v>-327.9145016116477</v>
       </c>
       <c r="Q64">
-        <v>46.23721666790232</v>
+        <v>40.38549838835235</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1545605133693053</v>
+        <v>0.1574999867036109</v>
       </c>
       <c r="T64">
-        <v>2.11994484140484</v>
+        <v>2.177240647929295</v>
       </c>
       <c r="U64">
         <v>0.2417366166625341</v>
       </c>
       <c r="V64">
-        <v>0.02807539711716333</v>
+        <v>0.02762975589308138</v>
       </c>
       <c r="W64">
-        <v>0.234949765151974</v>
+        <v>0.2350574929537289</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1123015884686533</v>
+        <v>0.1105190235723255</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2063612156411852</v>
+        <v>0.2083205818078106</v>
       </c>
       <c r="C65">
-        <v>-866.8698007490411</v>
+        <v>-905.5707216887531</v>
       </c>
       <c r="D65">
-        <v>532.9181992509588</v>
+        <v>526.4932783112466</v>
       </c>
       <c r="E65">
-        <v>-786.3119999999999</v>
+        <v>-754.0360000000001</v>
       </c>
       <c r="F65">
-        <v>2033.388</v>
+        <v>2065.664</v>
       </c>
       <c r="G65">
         <v>633.6</v>
@@ -6623,37 +6623,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M65">
-        <v>491.5443354821969</v>
+        <v>499.3466265215968</v>
       </c>
       <c r="N65">
-        <v>-437.2193354821969</v>
+        <v>-445.0216265215968</v>
       </c>
       <c r="O65">
-        <v>-109.3048338705492</v>
+        <v>-111.2554066303992</v>
       </c>
       <c r="P65">
-        <v>-327.9145016116477</v>
+        <v>-333.7662198911976</v>
       </c>
       <c r="Q65">
-        <v>40.38549838835235</v>
+        <v>34.53378010880243</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1574999867036109</v>
+        <v>0.1606027641120445</v>
       </c>
       <c r="T65">
-        <v>2.177240647929295</v>
+        <v>2.23771955481622</v>
       </c>
       <c r="U65">
         <v>0.2417366166625341</v>
       </c>
       <c r="V65">
-        <v>0.02762975589308138</v>
+        <v>0.02719804095725198</v>
       </c>
       <c r="W65">
-        <v>0.2350574929537289</v>
+        <v>0.235161854261679</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1105190235723255</v>
+        <v>0.1087921638290079</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2083205818078106</v>
+        <v>0.2102799479744359</v>
       </c>
       <c r="C66">
-        <v>-905.5707216887531</v>
+        <v>-944.1185689818899</v>
       </c>
       <c r="D66">
-        <v>526.4932783112466</v>
+        <v>520.2214310181101</v>
       </c>
       <c r="E66">
-        <v>-754.0360000000001</v>
+        <v>-721.7599999999998</v>
       </c>
       <c r="F66">
-        <v>2065.664</v>
+        <v>2097.94</v>
       </c>
       <c r="G66">
         <v>633.6</v>
@@ -6705,37 +6705,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M66">
-        <v>499.3466265215968</v>
+        <v>507.1489175609968</v>
       </c>
       <c r="N66">
-        <v>-445.0216265215968</v>
+        <v>-452.8239175609968</v>
       </c>
       <c r="O66">
-        <v>-111.2554066303992</v>
+        <v>-113.2059793902492</v>
       </c>
       <c r="P66">
-        <v>-333.7662198911976</v>
+        <v>-339.6179381707476</v>
       </c>
       <c r="Q66">
-        <v>34.53378010880243</v>
+        <v>28.6820618292524</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1606027641120445</v>
+        <v>0.1638828430866743</v>
       </c>
       <c r="T66">
-        <v>2.23771955481622</v>
+        <v>2.30165439923954</v>
       </c>
       <c r="U66">
         <v>0.2417366166625341</v>
       </c>
       <c r="V66">
-        <v>0.02719804095725198</v>
+        <v>0.02677960955790964</v>
       </c>
       <c r="W66">
-        <v>0.235161854261679</v>
+        <v>0.2352630044524614</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1087921638290079</v>
+        <v>0.1071184382316386</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2102799479744359</v>
+        <v>0.2122393141410613</v>
       </c>
       <c r="C67">
-        <v>-944.1185689818899</v>
+        <v>-982.5187486947816</v>
       </c>
       <c r="D67">
-        <v>520.2214310181101</v>
+        <v>514.0972513052183</v>
       </c>
       <c r="E67">
-        <v>-721.7599999999998</v>
+        <v>-689.4839999999999</v>
       </c>
       <c r="F67">
-        <v>2097.94</v>
+        <v>2130.216</v>
       </c>
       <c r="G67">
         <v>633.6</v>
@@ -6787,37 +6787,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M67">
-        <v>507.1489175609968</v>
+        <v>514.9512086003967</v>
       </c>
       <c r="N67">
-        <v>-452.8239175609968</v>
+        <v>-460.6262086003968</v>
       </c>
       <c r="O67">
-        <v>-113.2059793902492</v>
+        <v>-115.1565521500992</v>
       </c>
       <c r="P67">
-        <v>-339.6179381707476</v>
+        <v>-345.4696564502976</v>
       </c>
       <c r="Q67">
-        <v>28.6820618292524</v>
+        <v>22.83034354970243</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1638828430866743</v>
+        <v>0.1673558678833413</v>
       </c>
       <c r="T67">
-        <v>2.30165439923954</v>
+        <v>2.369350116864233</v>
       </c>
       <c r="U67">
         <v>0.2417366166625341</v>
       </c>
       <c r="V67">
-        <v>0.02677960955790964</v>
+        <v>0.02637385789794131</v>
       </c>
       <c r="W67">
-        <v>0.2352630044524614</v>
+        <v>0.2353610894859473</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1071184382316386</v>
+        <v>0.1054954315917652</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2122393141410613</v>
+        <v>0.2141986803076866</v>
       </c>
       <c r="C68">
-        <v>-982.5187486947816</v>
+        <v>-1020.77641528933</v>
       </c>
       <c r="D68">
-        <v>514.0972513052183</v>
+        <v>508.1155847106699</v>
       </c>
       <c r="E68">
-        <v>-689.4839999999999</v>
+        <v>-657.2079999999996</v>
       </c>
       <c r="F68">
-        <v>2130.216</v>
+        <v>2162.492</v>
       </c>
       <c r="G68">
         <v>633.6</v>
@@ -6869,37 +6869,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M68">
-        <v>514.9512086003967</v>
+        <v>522.7534996397967</v>
       </c>
       <c r="N68">
-        <v>-460.6262086003968</v>
+        <v>-468.4284996397967</v>
       </c>
       <c r="O68">
-        <v>-115.1565521500992</v>
+        <v>-117.1071249099492</v>
       </c>
       <c r="P68">
-        <v>-345.4696564502976</v>
+        <v>-351.3213747298475</v>
       </c>
       <c r="Q68">
-        <v>22.83034354970243</v>
+        <v>16.97862527015246</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1673558678833413</v>
+        <v>0.1710393790313213</v>
       </c>
       <c r="T68">
-        <v>2.369350116864233</v>
+        <v>2.441148605254058</v>
       </c>
       <c r="U68">
         <v>0.2417366166625341</v>
       </c>
       <c r="V68">
-        <v>0.02637385789794131</v>
+        <v>0.02598021822782278</v>
       </c>
       <c r="W68">
-        <v>0.2353610894859473</v>
+        <v>0.2354562466079859</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1054954315917652</v>
+        <v>0.1039208729112912</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2141986803076866</v>
+        <v>0.2161580464743119</v>
       </c>
       <c r="C69">
-        <v>-1020.77641528933</v>
+        <v>-1058.896486092098</v>
       </c>
       <c r="D69">
-        <v>508.1155847106699</v>
+        <v>502.2715139079016</v>
       </c>
       <c r="E69">
-        <v>-657.2079999999996</v>
+        <v>-624.9319999999998</v>
       </c>
       <c r="F69">
-        <v>2162.492</v>
+        <v>2194.768</v>
       </c>
       <c r="G69">
         <v>633.6</v>
@@ -6951,37 +6951,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M69">
-        <v>522.7534996397967</v>
+        <v>530.5557906791967</v>
       </c>
       <c r="N69">
-        <v>-468.4284996397967</v>
+        <v>-476.2307906791967</v>
       </c>
       <c r="O69">
-        <v>-117.1071249099492</v>
+        <v>-119.0576976697992</v>
       </c>
       <c r="P69">
-        <v>-351.3213747298475</v>
+        <v>-357.1730930093975</v>
       </c>
       <c r="Q69">
-        <v>16.97862527015246</v>
+        <v>11.12690699060249</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1710393790313213</v>
+        <v>0.1749531096260501</v>
       </c>
       <c r="T69">
-        <v>2.441148605254058</v>
+        <v>2.517434499168248</v>
       </c>
       <c r="U69">
         <v>0.2417366166625341</v>
       </c>
       <c r="V69">
-        <v>0.02598021822782278</v>
+        <v>0.02559815619506068</v>
       </c>
       <c r="W69">
-        <v>0.2354562466079859</v>
+        <v>0.2355486049911411</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1039208729112912</v>
+        <v>0.1023926247802427</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2161580464743119</v>
+        <v>0.2181174126409373</v>
       </c>
       <c r="C70">
-        <v>-1058.896486092098</v>
+        <v>-1096.883654776261</v>
       </c>
       <c r="D70">
-        <v>502.2715139079016</v>
+        <v>496.560345223739</v>
       </c>
       <c r="E70">
-        <v>-624.9319999999998</v>
+        <v>-592.6559999999995</v>
       </c>
       <c r="F70">
-        <v>2194.768</v>
+        <v>2227.044</v>
       </c>
       <c r="G70">
         <v>633.6</v>
@@ -7033,37 +7033,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M70">
-        <v>530.5557906791967</v>
+        <v>538.3580817185966</v>
       </c>
       <c r="N70">
-        <v>-476.2307906791967</v>
+        <v>-484.0330817185966</v>
       </c>
       <c r="O70">
-        <v>-119.0576976697992</v>
+        <v>-121.0082704296492</v>
       </c>
       <c r="P70">
-        <v>-357.1730930093975</v>
+        <v>-363.0248112889475</v>
       </c>
       <c r="Q70">
-        <v>11.12690699060249</v>
+        <v>5.275188711052522</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1749531096260501</v>
+        <v>0.1791193389688259</v>
       </c>
       <c r="T70">
-        <v>2.517434499168248</v>
+        <v>2.598642063657546</v>
       </c>
       <c r="U70">
         <v>0.2417366166625341</v>
       </c>
       <c r="V70">
-        <v>0.02559815619506068</v>
+        <v>0.02522716842411777</v>
       </c>
       <c r="W70">
-        <v>0.2355486049911411</v>
+        <v>0.235638286319712</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1023926247802427</v>
+        <v>0.1009086736964711</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2181174126409373</v>
+        <v>0.2200767788075626</v>
       </c>
       <c r="C71">
-        <v>-1096.883654776261</v>
+        <v>-1134.742403934102</v>
       </c>
       <c r="D71">
-        <v>496.560345223739</v>
+        <v>490.977596065898</v>
       </c>
       <c r="E71">
-        <v>-592.6559999999995</v>
+        <v>-560.3799999999997</v>
       </c>
       <c r="F71">
-        <v>2227.044</v>
+        <v>2259.32</v>
       </c>
       <c r="G71">
         <v>633.6</v>
@@ -7115,37 +7115,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M71">
-        <v>538.3580817185966</v>
+        <v>546.1603727579966</v>
       </c>
       <c r="N71">
-        <v>-484.0330817185966</v>
+        <v>-491.8353727579966</v>
       </c>
       <c r="O71">
-        <v>-121.0082704296492</v>
+        <v>-122.9588431894991</v>
       </c>
       <c r="P71">
-        <v>-363.0248112889475</v>
+        <v>-368.8765295684975</v>
       </c>
       <c r="Q71">
-        <v>5.275188711052522</v>
+        <v>-0.576529568497449</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1791193389688259</v>
+        <v>0.1835633169344534</v>
       </c>
       <c r="T71">
-        <v>2.598642063657546</v>
+        <v>2.685263465779464</v>
       </c>
       <c r="U71">
         <v>0.2417366166625341</v>
       </c>
       <c r="V71">
-        <v>0.02522716842411777</v>
+        <v>0.02486678030377323</v>
       </c>
       <c r="W71">
-        <v>0.235638286319712</v>
+        <v>0.2357254053246094</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1009086736964711</v>
+        <v>0.09946712121509294</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2200767788075626</v>
+        <v>0.222036144974188</v>
       </c>
       <c r="C72">
-        <v>-1134.742403934102</v>
+        <v>-1172.477016810839</v>
       </c>
       <c r="D72">
-        <v>490.977596065898</v>
+        <v>485.5189831891611</v>
       </c>
       <c r="E72">
-        <v>-560.3799999999997</v>
+        <v>-528.1039999999998</v>
       </c>
       <c r="F72">
-        <v>2259.32</v>
+        <v>2291.596</v>
       </c>
       <c r="G72">
         <v>633.6</v>
@@ -7197,37 +7197,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M72">
-        <v>546.1603727579966</v>
+        <v>553.9626637973965</v>
       </c>
       <c r="N72">
-        <v>-491.8353727579966</v>
+        <v>-499.6376637973966</v>
       </c>
       <c r="O72">
-        <v>-122.9588431894991</v>
+        <v>-124.9094159493491</v>
       </c>
       <c r="P72">
-        <v>-368.8765295684975</v>
+        <v>-374.7282478480474</v>
       </c>
       <c r="Q72">
-        <v>-0.576529568497449</v>
+        <v>-6.42824784804742</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1835633169344534</v>
+        <v>0.1883137761390898</v>
       </c>
       <c r="T72">
-        <v>2.685263465779464</v>
+        <v>2.777858757702894</v>
       </c>
       <c r="U72">
         <v>0.2417366166625341</v>
       </c>
       <c r="V72">
-        <v>0.02486678030377323</v>
+        <v>0.02451654396146657</v>
       </c>
       <c r="W72">
-        <v>0.2357254053246094</v>
+        <v>0.2358100702730309</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.09946712121509294</v>
+        <v>0.0980661758458663</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2220361449741879</v>
+        <v>0.2239955111408133</v>
       </c>
       <c r="C73">
-        <v>-1172.477016810839</v>
+        <v>-1210.091588264322</v>
       </c>
       <c r="D73">
-        <v>485.5189831891611</v>
+        <v>480.1804117356782</v>
       </c>
       <c r="E73">
-        <v>-528.1039999999998</v>
+        <v>-495.828</v>
       </c>
       <c r="F73">
-        <v>2291.596</v>
+        <v>2323.872</v>
       </c>
       <c r="G73">
         <v>633.6</v>
@@ -7279,37 +7279,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M73">
-        <v>553.9626637973965</v>
+        <v>561.7649548367964</v>
       </c>
       <c r="N73">
-        <v>-499.6376637973966</v>
+        <v>-507.4399548367964</v>
       </c>
       <c r="O73">
-        <v>-124.9094159493491</v>
+        <v>-126.8599887091991</v>
       </c>
       <c r="P73">
-        <v>-374.7282478480474</v>
+        <v>-380.5799661275973</v>
       </c>
       <c r="Q73">
-        <v>-6.42824784804742</v>
+        <v>-12.27996612759728</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1883137761390897</v>
+        <v>0.1934035538583429</v>
       </c>
       <c r="T73">
-        <v>2.777858757702893</v>
+        <v>2.877067999049425</v>
       </c>
       <c r="U73">
         <v>0.2417366166625341</v>
       </c>
       <c r="V73">
-        <v>0.02451654396146657</v>
+        <v>0.0241760364064462</v>
       </c>
       <c r="W73">
-        <v>0.2358100702730309</v>
+        <v>0.2358923834173295</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.0980661758458663</v>
+        <v>0.09670414562578478</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2239955111408133</v>
+        <v>0.2259548773074386</v>
       </c>
       <c r="C74">
-        <v>-1210.091588264322</v>
+        <v>-1247.590035009549</v>
       </c>
       <c r="D74">
-        <v>480.1804117356782</v>
+        <v>474.9579649904505</v>
       </c>
       <c r="E74">
-        <v>-495.828</v>
+        <v>-463.5520000000001</v>
       </c>
       <c r="F74">
-        <v>2323.872</v>
+        <v>2356.148</v>
       </c>
       <c r="G74">
         <v>633.6</v>
@@ -7361,37 +7361,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M74">
-        <v>561.7649548367964</v>
+        <v>569.5672458761964</v>
       </c>
       <c r="N74">
-        <v>-507.4399548367964</v>
+        <v>-515.2422458761964</v>
       </c>
       <c r="O74">
-        <v>-126.8599887091991</v>
+        <v>-128.8105614690491</v>
       </c>
       <c r="P74">
-        <v>-380.5799661275973</v>
+        <v>-386.4316844071473</v>
       </c>
       <c r="Q74">
-        <v>-12.27996612759728</v>
+        <v>-18.1316844071473</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1934035538583429</v>
+        <v>0.1988703521493927</v>
       </c>
       <c r="T74">
-        <v>2.877067999049425</v>
+        <v>2.983626073088292</v>
       </c>
       <c r="U74">
         <v>0.2417366166625341</v>
       </c>
       <c r="V74">
-        <v>0.0241760364064462</v>
+        <v>0.02384485782553598</v>
       </c>
       <c r="W74">
-        <v>0.2358923834173295</v>
+        <v>0.2359724414069899</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.09670414562578478</v>
+        <v>0.09537943130214388</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2259548773074386</v>
+        <v>0.227914243474064</v>
       </c>
       <c r="C75">
-        <v>-1247.590035009549</v>
+        <v>-1284.976105201857</v>
       </c>
       <c r="D75">
-        <v>474.9579649904505</v>
+        <v>469.8478947981428</v>
       </c>
       <c r="E75">
-        <v>-463.5520000000001</v>
+        <v>-431.2759999999998</v>
       </c>
       <c r="F75">
-        <v>2356.148</v>
+        <v>2388.424</v>
       </c>
       <c r="G75">
         <v>633.6</v>
@@ -7443,37 +7443,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M75">
-        <v>569.5672458761964</v>
+        <v>577.3695369155963</v>
       </c>
       <c r="N75">
-        <v>-515.2422458761964</v>
+        <v>-523.0445369155964</v>
       </c>
       <c r="O75">
-        <v>-128.8105614690491</v>
+        <v>-130.7611342288991</v>
       </c>
       <c r="P75">
-        <v>-386.4316844071473</v>
+        <v>-392.2834026866973</v>
       </c>
       <c r="Q75">
-        <v>-18.1316844071473</v>
+        <v>-23.98340268669727</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1988703521493927</v>
+        <v>0.2047576733859078</v>
       </c>
       <c r="T75">
-        <v>2.983626073088292</v>
+        <v>3.098380922053227</v>
       </c>
       <c r="U75">
         <v>0.2417366166625341</v>
       </c>
       <c r="V75">
-        <v>0.02384485782553598</v>
+        <v>0.02352263001708279</v>
       </c>
       <c r="W75">
-        <v>0.2359724414069899</v>
+        <v>0.2360503356671999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.09537943130214388</v>
+        <v>0.09409052006833107</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.227914243474064</v>
+        <v>0.2298736096406893</v>
       </c>
       <c r="C76">
-        <v>-1284.976105201857</v>
+        <v>-1322.25338740806</v>
       </c>
       <c r="D76">
-        <v>469.8478947981428</v>
+        <v>464.8466125919392</v>
       </c>
       <c r="E76">
-        <v>-431.2759999999998</v>
+        <v>-399</v>
       </c>
       <c r="F76">
-        <v>2388.424</v>
+        <v>2420.7</v>
       </c>
       <c r="G76">
         <v>633.6</v>
@@ -7525,37 +7525,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M76">
-        <v>577.3695369155963</v>
+        <v>585.1718279549963</v>
       </c>
       <c r="N76">
-        <v>-523.0445369155964</v>
+        <v>-530.8468279549963</v>
       </c>
       <c r="O76">
-        <v>-130.7611342288991</v>
+        <v>-132.7117069887491</v>
       </c>
       <c r="P76">
-        <v>-392.2834026866973</v>
+        <v>-398.1351209662473</v>
       </c>
       <c r="Q76">
-        <v>-23.98340268669727</v>
+        <v>-29.83512096624725</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2047576733859078</v>
+        <v>0.2111159803213441</v>
       </c>
       <c r="T76">
-        <v>3.098380922053227</v>
+        <v>3.222316158935356</v>
       </c>
       <c r="U76">
         <v>0.2417366166625341</v>
       </c>
       <c r="V76">
-        <v>0.02352263001708279</v>
+        <v>0.02320899495018836</v>
       </c>
       <c r="W76">
-        <v>0.2360503356671999</v>
+        <v>0.2361261527471377</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09409052006833107</v>
+        <v>0.09283597980075331</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2298736096406893</v>
+        <v>0.2318329758073147</v>
       </c>
       <c r="C77">
-        <v>-1322.25338740806</v>
+        <v>-1359.425319010673</v>
       </c>
       <c r="D77">
-        <v>464.8466125919392</v>
+        <v>459.9506809893269</v>
       </c>
       <c r="E77">
-        <v>-399</v>
+        <v>-366.7239999999997</v>
       </c>
       <c r="F77">
-        <v>2420.7</v>
+        <v>2452.976</v>
       </c>
       <c r="G77">
         <v>633.6</v>
@@ -7607,37 +7607,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M77">
-        <v>585.1718279549963</v>
+        <v>592.9741189943962</v>
       </c>
       <c r="N77">
-        <v>-530.8468279549963</v>
+        <v>-538.6491189943963</v>
       </c>
       <c r="O77">
-        <v>-132.7117069887491</v>
+        <v>-134.6622797485991</v>
       </c>
       <c r="P77">
-        <v>-398.1351209662473</v>
+        <v>-403.9868392457972</v>
       </c>
       <c r="Q77">
-        <v>-29.83512096624725</v>
+        <v>-35.68683924579722</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2111159803213441</v>
+        <v>0.2180041461680668</v>
       </c>
       <c r="T77">
-        <v>3.222316158935356</v>
+        <v>3.35657933222433</v>
       </c>
       <c r="U77">
         <v>0.2417366166625341</v>
       </c>
       <c r="V77">
-        <v>0.02320899495018836</v>
+        <v>0.02290361343768588</v>
       </c>
       <c r="W77">
-        <v>0.2361261527471377</v>
+        <v>0.2361999746407614</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.09283597980075331</v>
+        <v>0.0916144537507434</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2318329758073147</v>
+        <v>0.23379234197394</v>
       </c>
       <c r="C78">
-        <v>-1359.425319010673</v>
+        <v>-1396.495194086562</v>
       </c>
       <c r="D78">
-        <v>459.9506809893269</v>
+        <v>455.1568059134383</v>
       </c>
       <c r="E78">
-        <v>-366.7239999999997</v>
+        <v>-334.4479999999999</v>
       </c>
       <c r="F78">
-        <v>2452.976</v>
+        <v>2485.252</v>
       </c>
       <c r="G78">
         <v>633.6</v>
@@ -7689,37 +7689,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M78">
-        <v>592.9741189943962</v>
+        <v>600.7764100337962</v>
       </c>
       <c r="N78">
-        <v>-538.6491189943963</v>
+        <v>-546.4514100337963</v>
       </c>
       <c r="O78">
-        <v>-134.6622797485991</v>
+        <v>-136.6128525084491</v>
       </c>
       <c r="P78">
-        <v>-403.9868392457972</v>
+        <v>-409.8385575253472</v>
       </c>
       <c r="Q78">
-        <v>-35.68683924579722</v>
+        <v>-41.53855752534719</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2180041461680668</v>
+        <v>0.2254912829579827</v>
       </c>
       <c r="T78">
-        <v>3.35657933222433</v>
+        <v>3.50251756406017</v>
       </c>
       <c r="U78">
         <v>0.2417366166625341</v>
       </c>
       <c r="V78">
-        <v>0.02290361343768588</v>
+        <v>0.02260616391252112</v>
       </c>
       <c r="W78">
-        <v>0.2361999746407614</v>
+        <v>0.2362718790826026</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.0916144537507434</v>
+        <v>0.0904246556500844</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.23379234197394</v>
+        <v>0.2357517081405654</v>
       </c>
       <c r="C79">
-        <v>-1396.495194086562</v>
+        <v>-1433.46617079799</v>
       </c>
       <c r="D79">
-        <v>455.1568059134383</v>
+        <v>450.4618292020097</v>
       </c>
       <c r="E79">
-        <v>-334.4479999999999</v>
+        <v>-302.172</v>
       </c>
       <c r="F79">
-        <v>2485.252</v>
+        <v>2517.528</v>
       </c>
       <c r="G79">
         <v>633.6</v>
@@ -7771,37 +7771,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M79">
-        <v>600.7764100337962</v>
+        <v>608.578701073196</v>
       </c>
       <c r="N79">
-        <v>-546.4514100337963</v>
+        <v>-554.253701073196</v>
       </c>
       <c r="O79">
-        <v>-136.6128525084491</v>
+        <v>-138.563425268299</v>
       </c>
       <c r="P79">
-        <v>-409.8385575253472</v>
+        <v>-415.690275804897</v>
       </c>
       <c r="Q79">
-        <v>-41.53855752534719</v>
+        <v>-47.39027580489699</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2254912829579827</v>
+        <v>0.2336590685469819</v>
       </c>
       <c r="T79">
-        <v>3.50251756406017</v>
+        <v>3.661722907881087</v>
       </c>
       <c r="U79">
         <v>0.2417366166625341</v>
       </c>
       <c r="V79">
-        <v>0.02260616391252112</v>
+        <v>0.02231634129825804</v>
       </c>
       <c r="W79">
-        <v>0.2362718790826026</v>
+        <v>0.2363419398208068</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0904246556500844</v>
+        <v>0.08926536519303219</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2357517081405654</v>
+        <v>0.2377110743071907</v>
       </c>
       <c r="C80">
-        <v>-1433.46617079799</v>
+        <v>-1470.341278330898</v>
       </c>
       <c r="D80">
-        <v>450.4618292020097</v>
+        <v>445.862721669102</v>
       </c>
       <c r="E80">
-        <v>-302.172</v>
+        <v>-269.8959999999997</v>
       </c>
       <c r="F80">
-        <v>2517.528</v>
+        <v>2549.804</v>
       </c>
       <c r="G80">
         <v>633.6</v>
@@ -7853,37 +7853,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M80">
-        <v>608.578701073196</v>
+        <v>616.3809921125961</v>
       </c>
       <c r="N80">
-        <v>-554.253701073196</v>
+        <v>-562.0559921125962</v>
       </c>
       <c r="O80">
-        <v>-138.563425268299</v>
+        <v>-140.513998028149</v>
       </c>
       <c r="P80">
-        <v>-415.690275804897</v>
+        <v>-421.5419940844471</v>
       </c>
       <c r="Q80">
-        <v>-47.39027580489699</v>
+        <v>-53.24199408444713</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2336590685469819</v>
+        <v>0.2426047384777906</v>
       </c>
       <c r="T80">
-        <v>3.661722907881087</v>
+        <v>3.836090665399234</v>
       </c>
       <c r="U80">
         <v>0.2417366166625341</v>
       </c>
       <c r="V80">
-        <v>0.02231634129825804</v>
+        <v>0.02203385596536869</v>
       </c>
       <c r="W80">
-        <v>0.2363419398208068</v>
+        <v>0.2364102268694363</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.08926536519303219</v>
+        <v>0.08813542386147466</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2377110743071907</v>
+        <v>0.239670440473816</v>
       </c>
       <c r="C81">
-        <v>-1470.341278330898</v>
+        <v>-1507.123423412442</v>
       </c>
       <c r="D81">
-        <v>445.862721669102</v>
+        <v>441.3565765875578</v>
       </c>
       <c r="E81">
-        <v>-269.8959999999997</v>
+        <v>-237.6199999999999</v>
       </c>
       <c r="F81">
-        <v>2549.804</v>
+        <v>2582.08</v>
       </c>
       <c r="G81">
         <v>633.6</v>
@@ -7935,37 +7935,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M81">
-        <v>616.3809921125961</v>
+        <v>624.1832831519961</v>
       </c>
       <c r="N81">
-        <v>-562.0559921125962</v>
+        <v>-569.8582831519961</v>
       </c>
       <c r="O81">
-        <v>-140.513998028149</v>
+        <v>-142.464570787999</v>
       </c>
       <c r="P81">
-        <v>-421.5419940844471</v>
+        <v>-427.3937123639971</v>
       </c>
       <c r="Q81">
-        <v>-53.24199408444713</v>
+        <v>-59.0937123639971</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2426047384777906</v>
+        <v>0.2524449754016801</v>
       </c>
       <c r="T81">
-        <v>3.836090665399234</v>
+        <v>4.027895198669196</v>
       </c>
       <c r="U81">
         <v>0.2417366166625341</v>
       </c>
       <c r="V81">
-        <v>0.02203385596536869</v>
+        <v>0.02175843276580158</v>
       </c>
       <c r="W81">
-        <v>0.2364102268694363</v>
+        <v>0.23647680674185</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.08813542386147466</v>
+        <v>0.08703373106320622</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.239670440473816</v>
+        <v>0.2416298066404414</v>
       </c>
       <c r="C82">
-        <v>-1507.123423412442</v>
+        <v>-1543.81539643728</v>
       </c>
       <c r="D82">
-        <v>441.3565765875578</v>
+        <v>436.9406035627206</v>
       </c>
       <c r="E82">
-        <v>-237.6199999999999</v>
+        <v>-205.3439999999996</v>
       </c>
       <c r="F82">
-        <v>2582.08</v>
+        <v>2614.356</v>
       </c>
       <c r="G82">
         <v>633.6</v>
@@ -8017,37 +8017,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M82">
-        <v>624.1832831519961</v>
+        <v>631.985574191396</v>
       </c>
       <c r="N82">
-        <v>-569.8582831519961</v>
+        <v>-577.6605741913961</v>
       </c>
       <c r="O82">
-        <v>-142.464570787999</v>
+        <v>-144.415143547849</v>
       </c>
       <c r="P82">
-        <v>-427.3937123639971</v>
+        <v>-433.2454306435471</v>
       </c>
       <c r="Q82">
-        <v>-59.0937123639971</v>
+        <v>-64.94543064354707</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2524449754016801</v>
+        <v>0.2633210267386107</v>
       </c>
       <c r="T82">
-        <v>4.027895198669196</v>
+        <v>4.239889682809681</v>
       </c>
       <c r="U82">
         <v>0.2417366166625341</v>
       </c>
       <c r="V82">
-        <v>0.02175843276580158</v>
+        <v>0.02148981013906329</v>
       </c>
       <c r="W82">
-        <v>0.23647680674185</v>
+        <v>0.2365417426667967</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.08703373106320622</v>
+        <v>0.08595924055625304</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2416298066404414</v>
+        <v>0.2435891728070667</v>
       </c>
       <c r="C83">
-        <v>-1543.81539643728</v>
+        <v>-1580.419877229708</v>
       </c>
       <c r="D83">
-        <v>436.9406035627206</v>
+        <v>432.6121227702924</v>
       </c>
       <c r="E83">
-        <v>-205.3439999999996</v>
+        <v>-173.0679999999998</v>
       </c>
       <c r="F83">
-        <v>2614.356</v>
+        <v>2646.632</v>
       </c>
       <c r="G83">
         <v>633.6</v>
@@ -8099,37 +8099,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M83">
-        <v>631.985574191396</v>
+        <v>639.787865230796</v>
       </c>
       <c r="N83">
-        <v>-577.6605741913961</v>
+        <v>-585.4628652307961</v>
       </c>
       <c r="O83">
-        <v>-144.415143547849</v>
+        <v>-146.365716307699</v>
       </c>
       <c r="P83">
-        <v>-433.2454306435471</v>
+        <v>-439.0971489230971</v>
       </c>
       <c r="Q83">
-        <v>-64.94543064354707</v>
+        <v>-70.79714892309704</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2633210267386107</v>
+        <v>0.2754055282240891</v>
       </c>
       <c r="T83">
-        <v>4.239889682809681</v>
+        <v>4.475439109632441</v>
       </c>
       <c r="U83">
         <v>0.2417366166625341</v>
       </c>
       <c r="V83">
-        <v>0.02148981013906329</v>
+        <v>0.02122773928370886</v>
       </c>
       <c r="W83">
-        <v>0.2365417426667967</v>
+        <v>0.236605094788696</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.08595924055625304</v>
+        <v>0.08491095713483532</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2435891728070667</v>
+        <v>0.2455485389736921</v>
       </c>
       <c r="C84">
-        <v>-1580.419877229708</v>
+        <v>-1616.939440466682</v>
       </c>
       <c r="D84">
-        <v>432.6121227702924</v>
+        <v>428.3685595333181</v>
       </c>
       <c r="E84">
-        <v>-173.0679999999998</v>
+        <v>-140.7919999999995</v>
       </c>
       <c r="F84">
-        <v>2646.632</v>
+        <v>2678.908</v>
       </c>
       <c r="G84">
         <v>633.6</v>
@@ -8181,37 +8181,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M84">
-        <v>639.787865230796</v>
+        <v>647.590156270196</v>
       </c>
       <c r="N84">
-        <v>-585.4628652307961</v>
+        <v>-593.265156270196</v>
       </c>
       <c r="O84">
-        <v>-146.365716307699</v>
+        <v>-148.316289067549</v>
       </c>
       <c r="P84">
-        <v>-439.0971489230971</v>
+        <v>-444.948867202647</v>
       </c>
       <c r="Q84">
-        <v>-70.79714892309704</v>
+        <v>-76.64886720264701</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2754055282240891</v>
+        <v>0.2889117357666826</v>
       </c>
       <c r="T84">
-        <v>4.475439109632441</v>
+        <v>4.738700233728466</v>
       </c>
       <c r="U84">
         <v>0.2417366166625341</v>
       </c>
       <c r="V84">
-        <v>0.02122773928370886</v>
+        <v>0.02097198338872441</v>
       </c>
       <c r="W84">
-        <v>0.236605094788696</v>
+        <v>0.236666920353441</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.08491095713483532</v>
+        <v>0.08388793355489754</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2455485389736921</v>
+        <v>0.2475079051403174</v>
       </c>
       <c r="C85">
-        <v>-1616.939440466682</v>
+        <v>-1653.376560784756</v>
       </c>
       <c r="D85">
-        <v>428.3685595333181</v>
+        <v>424.2074392152438</v>
       </c>
       <c r="E85">
-        <v>-140.7919999999995</v>
+        <v>-108.5159999999996</v>
       </c>
       <c r="F85">
-        <v>2678.908</v>
+        <v>2711.184</v>
       </c>
       <c r="G85">
         <v>633.6</v>
@@ -8263,37 +8263,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M85">
-        <v>647.590156270196</v>
+        <v>655.3924473095959</v>
       </c>
       <c r="N85">
-        <v>-593.265156270196</v>
+        <v>-601.067447309596</v>
       </c>
       <c r="O85">
-        <v>-148.316289067549</v>
+        <v>-150.266861827399</v>
       </c>
       <c r="P85">
-        <v>-444.948867202647</v>
+        <v>-450.800585482197</v>
       </c>
       <c r="Q85">
-        <v>-76.64886720264701</v>
+        <v>-82.50058548219698</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2889117357666826</v>
+        <v>0.3041062192521002</v>
       </c>
       <c r="T85">
-        <v>4.738700233728466</v>
+        <v>5.034868998336496</v>
       </c>
       <c r="U85">
         <v>0.2417366166625341</v>
       </c>
       <c r="V85">
-        <v>0.02097198338872441</v>
+        <v>0.02072231691981103</v>
       </c>
       <c r="W85">
-        <v>0.236666920353441</v>
+        <v>0.2367272738809302</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.08388793355489754</v>
+        <v>0.08288926767924398</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2475079051403174</v>
+        <v>0.2494672713069427</v>
       </c>
       <c r="C86">
-        <v>-1653.376560784756</v>
+        <v>-1689.733617592242</v>
       </c>
       <c r="D86">
-        <v>424.2074392152438</v>
+        <v>420.1263824077584</v>
       </c>
       <c r="E86">
-        <v>-108.5160000000001</v>
+        <v>-76.23999999999978</v>
       </c>
       <c r="F86">
-        <v>2711.184</v>
+        <v>2743.46</v>
       </c>
       <c r="G86">
         <v>633.6</v>
@@ -8345,37 +8345,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M86">
-        <v>655.3924473095958</v>
+        <v>663.1947383489958</v>
       </c>
       <c r="N86">
-        <v>-601.0674473095958</v>
+        <v>-608.8697383489957</v>
       </c>
       <c r="O86">
-        <v>-150.2668618273989</v>
+        <v>-152.2174345872489</v>
       </c>
       <c r="P86">
-        <v>-450.8005854821968</v>
+        <v>-456.6523037617468</v>
       </c>
       <c r="Q86">
-        <v>-82.50058548219681</v>
+        <v>-88.35230376174678</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3041062192521001</v>
+        <v>0.3213266338689068</v>
       </c>
       <c r="T86">
-        <v>5.034868998336493</v>
+        <v>5.370526931558927</v>
       </c>
       <c r="U86">
         <v>0.2417366166625341</v>
       </c>
       <c r="V86">
-        <v>0.02072231691981103</v>
+        <v>0.02047852495604855</v>
       </c>
       <c r="W86">
-        <v>0.2367272738809302</v>
+        <v>0.2367862073254197</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08288926767924421</v>
+        <v>0.08191409982419429</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2494672713069427</v>
+        <v>0.2514266374735681</v>
       </c>
       <c r="C87">
-        <v>-1689.733617592242</v>
+        <v>-1726.012899606237</v>
       </c>
       <c r="D87">
-        <v>420.1263824077584</v>
+        <v>416.1231003937625</v>
       </c>
       <c r="E87">
-        <v>-76.23999999999978</v>
+        <v>-43.96399999999994</v>
       </c>
       <c r="F87">
-        <v>2743.46</v>
+        <v>2775.736</v>
       </c>
       <c r="G87">
         <v>633.6</v>
@@ -8427,37 +8427,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M87">
-        <v>663.1947383489958</v>
+        <v>670.9970293883957</v>
       </c>
       <c r="N87">
-        <v>-608.8697383489957</v>
+        <v>-616.6720293883957</v>
       </c>
       <c r="O87">
-        <v>-152.2174345872489</v>
+        <v>-154.1680073470989</v>
       </c>
       <c r="P87">
-        <v>-456.6523037617468</v>
+        <v>-462.5040220412968</v>
       </c>
       <c r="Q87">
-        <v>-88.35230376174678</v>
+        <v>-94.20402204129675</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3213266338689068</v>
+        <v>0.3410071077166859</v>
       </c>
       <c r="T87">
-        <v>5.370526931558927</v>
+        <v>5.75413599809885</v>
       </c>
       <c r="U87">
         <v>0.2417366166625341</v>
       </c>
       <c r="V87">
-        <v>0.02047852495604855</v>
+        <v>0.02024040257283868</v>
       </c>
       <c r="W87">
-        <v>0.2367862073254197</v>
+        <v>0.2368437702246884</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08191409982419429</v>
+        <v>0.08096161029135485</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2514266374735681</v>
+        <v>0.2533860036401934</v>
       </c>
       <c r="C88">
-        <v>-1726.012899606237</v>
+        <v>-1762.216609132724</v>
       </c>
       <c r="D88">
-        <v>416.1231003937625</v>
+        <v>412.1953908672762</v>
       </c>
       <c r="E88">
-        <v>-43.96399999999994</v>
+        <v>-11.6880000000001</v>
       </c>
       <c r="F88">
-        <v>2775.736</v>
+        <v>2808.012</v>
       </c>
       <c r="G88">
         <v>633.6</v>
@@ -8509,37 +8509,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M88">
-        <v>670.9970293883957</v>
+        <v>678.7993204277956</v>
       </c>
       <c r="N88">
-        <v>-616.6720293883957</v>
+        <v>-624.4743204277956</v>
       </c>
       <c r="O88">
-        <v>-154.1680073470989</v>
+        <v>-156.1185801069489</v>
       </c>
       <c r="P88">
-        <v>-462.5040220412968</v>
+        <v>-468.3557403208467</v>
       </c>
       <c r="Q88">
-        <v>-94.20402204129675</v>
+        <v>-100.0557403208467</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3410071077166859</v>
+        <v>0.3637153467718155</v>
       </c>
       <c r="T88">
-        <v>5.75413599809885</v>
+        <v>6.196761844106454</v>
       </c>
       <c r="U88">
         <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.02024040257283868</v>
+        <v>0.02000775426740376</v>
       </c>
       <c r="W88">
-        <v>0.2368437702246884</v>
+        <v>0.2369000098389165</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.08096161029135485</v>
+        <v>0.08003101706961491</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2533860036401934</v>
+        <v>0.2553453698068188</v>
       </c>
       <c r="C89">
-        <v>-1762.216609132724</v>
+        <v>-1798.346866106518</v>
       </c>
       <c r="D89">
-        <v>412.1953908672762</v>
+        <v>408.3411338934819</v>
       </c>
       <c r="E89">
-        <v>-11.6880000000001</v>
+        <v>20.58800000000019</v>
       </c>
       <c r="F89">
-        <v>2808.012</v>
+        <v>2840.288</v>
       </c>
       <c r="G89">
         <v>633.6</v>
@@ -8591,37 +8591,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M89">
-        <v>678.7993204277956</v>
+        <v>686.6016114671957</v>
       </c>
       <c r="N89">
-        <v>-624.4743204277956</v>
+        <v>-632.2766114671956</v>
       </c>
       <c r="O89">
-        <v>-156.1185801069489</v>
+        <v>-158.0691528667989</v>
       </c>
       <c r="P89">
-        <v>-468.3557403208467</v>
+        <v>-474.2074586003967</v>
       </c>
       <c r="Q89">
-        <v>-100.0557403208467</v>
+        <v>-105.9074586003967</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3637153467718155</v>
+        <v>0.3902082923361335</v>
       </c>
       <c r="T89">
-        <v>6.196761844106454</v>
+        <v>6.71315866444866</v>
       </c>
       <c r="U89">
         <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.02000775426740376</v>
+        <v>0.01978039342345598</v>
       </c>
       <c r="W89">
-        <v>0.2369000098389165</v>
+        <v>0.236954971280094</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08003101706961491</v>
+        <v>0.079121573693824</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2553453698068188</v>
+        <v>0.2573047359734441</v>
       </c>
       <c r="C90">
-        <v>-1798.346866106518</v>
+        <v>-1834.405711906684</v>
       </c>
       <c r="D90">
-        <v>408.3411338934819</v>
+        <v>404.5582880933159</v>
       </c>
       <c r="E90">
-        <v>20.58800000000019</v>
+        <v>52.86400000000003</v>
       </c>
       <c r="F90">
-        <v>2840.288</v>
+        <v>2872.564</v>
       </c>
       <c r="G90">
         <v>633.6</v>
@@ -8673,37 +8673,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M90">
-        <v>686.6016114671957</v>
+        <v>694.4039025065956</v>
       </c>
       <c r="N90">
-        <v>-632.2766114671956</v>
+        <v>-640.0789025065956</v>
       </c>
       <c r="O90">
-        <v>-158.0691528667989</v>
+        <v>-160.0197256266489</v>
       </c>
       <c r="P90">
-        <v>-474.2074586003967</v>
+        <v>-480.0591768799467</v>
       </c>
       <c r="Q90">
-        <v>-105.9074586003967</v>
+        <v>-111.7591768799467</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3902082923361335</v>
+        <v>0.4215181370939639</v>
       </c>
       <c r="T90">
-        <v>6.71315866444866</v>
+        <v>7.323445815762174</v>
       </c>
       <c r="U90">
         <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.01978039342345598</v>
+        <v>0.01955814181195648</v>
       </c>
       <c r="W90">
-        <v>0.236954971280094</v>
+        <v>0.2370086976327057</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.079121573693824</v>
+        <v>0.07823256724782601</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2573047359734441</v>
+        <v>0.2592641021400694</v>
       </c>
       <c r="C91">
-        <v>-1834.405711906684</v>
+        <v>-1870.395112961807</v>
       </c>
       <c r="D91">
-        <v>404.5582880933159</v>
+        <v>400.8448870381927</v>
       </c>
       <c r="E91">
-        <v>52.86400000000003</v>
+        <v>85.14000000000033</v>
       </c>
       <c r="F91">
-        <v>2872.564</v>
+        <v>2904.84</v>
       </c>
       <c r="G91">
         <v>633.6</v>
@@ -8755,37 +8755,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M91">
-        <v>694.4039025065956</v>
+        <v>702.2061935459956</v>
       </c>
       <c r="N91">
-        <v>-640.0789025065956</v>
+        <v>-647.8811935459955</v>
       </c>
       <c r="O91">
-        <v>-160.0197256266489</v>
+        <v>-161.9702983864989</v>
       </c>
       <c r="P91">
-        <v>-480.0591768799467</v>
+        <v>-485.9108951594966</v>
       </c>
       <c r="Q91">
-        <v>-111.7591768799467</v>
+        <v>-117.6108951594966</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4215181370939639</v>
+        <v>0.4590899508033602</v>
       </c>
       <c r="T91">
-        <v>7.323445815762174</v>
+        <v>8.055790397338392</v>
       </c>
       <c r="U91">
         <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.01955814181195648</v>
+        <v>0.01934082912515696</v>
       </c>
       <c r="W91">
-        <v>0.2370086976327057</v>
+        <v>0.2370612300663704</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.07823256724782601</v>
+        <v>0.07736331650062789</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2592641021400694</v>
+        <v>0.2612234683066948</v>
       </c>
       <c r="C92">
-        <v>-1870.395112961807</v>
+        <v>-1906.316964158527</v>
       </c>
       <c r="D92">
-        <v>400.8448870381927</v>
+        <v>397.1990358414733</v>
       </c>
       <c r="E92">
-        <v>85.14000000000033</v>
+        <v>117.4160000000002</v>
       </c>
       <c r="F92">
-        <v>2904.84</v>
+        <v>2937.116</v>
       </c>
       <c r="G92">
         <v>633.6</v>
@@ -8837,37 +8837,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M92">
-        <v>702.2061935459956</v>
+        <v>710.0084845853955</v>
       </c>
       <c r="N92">
-        <v>-647.8811935459955</v>
+        <v>-655.6834845853955</v>
       </c>
       <c r="O92">
-        <v>-161.9702983864989</v>
+        <v>-163.9208711463489</v>
       </c>
       <c r="P92">
-        <v>-485.9108951594966</v>
+        <v>-491.7626134390466</v>
       </c>
       <c r="Q92">
-        <v>-117.6108951594966</v>
+        <v>-123.4626134390466</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4590899508033602</v>
+        <v>0.5050110564481781</v>
       </c>
       <c r="T92">
-        <v>8.055790397338392</v>
+        <v>8.950878219264881</v>
       </c>
       <c r="U92">
         <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.01934082912515696</v>
+        <v>0.01912829254136403</v>
       </c>
       <c r="W92">
-        <v>0.2370612300663704</v>
+        <v>0.2371126079410536</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.07736331650062789</v>
+        <v>0.07651317016545622</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2612234683066948</v>
+        <v>0.2631828344733201</v>
       </c>
       <c r="C93">
-        <v>-1906.316964158527</v>
+        <v>-1942.173092065726</v>
       </c>
       <c r="D93">
-        <v>397.1990358414733</v>
+        <v>393.6189079342742</v>
       </c>
       <c r="E93">
-        <v>117.4160000000002</v>
+        <v>149.692</v>
       </c>
       <c r="F93">
-        <v>2937.116</v>
+        <v>2969.392</v>
       </c>
       <c r="G93">
         <v>633.6</v>
@@ -8919,37 +8919,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M93">
-        <v>710.0084845853955</v>
+        <v>717.8107756247954</v>
       </c>
       <c r="N93">
-        <v>-655.6834845853955</v>
+        <v>-663.4857756247955</v>
       </c>
       <c r="O93">
-        <v>-163.9208711463489</v>
+        <v>-165.8714439061989</v>
       </c>
       <c r="P93">
-        <v>-491.7626134390466</v>
+        <v>-497.6143317185966</v>
       </c>
       <c r="Q93">
-        <v>-123.4626134390466</v>
+        <v>-129.3143317185966</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5050110564481781</v>
+        <v>0.5624124385042005</v>
       </c>
       <c r="T93">
-        <v>8.950878219264881</v>
+        <v>10.06973799667299</v>
       </c>
       <c r="U93">
         <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.01912829254136403</v>
+        <v>0.01892037631808833</v>
       </c>
       <c r="W93">
-        <v>0.2371126079410536</v>
+        <v>0.2371628689054175</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.07651317016545622</v>
+        <v>0.07568150527235329</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2631828344733201</v>
+        <v>0.2651422006399455</v>
       </c>
       <c r="C94">
-        <v>-1942.173092065726</v>
+        <v>-1977.96525798592</v>
       </c>
       <c r="D94">
-        <v>393.6189079342742</v>
+        <v>390.1027420140805</v>
       </c>
       <c r="E94">
-        <v>149.692</v>
+        <v>181.9680000000003</v>
       </c>
       <c r="F94">
-        <v>2969.392</v>
+        <v>3001.668</v>
       </c>
       <c r="G94">
         <v>633.6</v>
@@ -9001,37 +9001,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M94">
-        <v>717.8107756247954</v>
+        <v>725.6130666641955</v>
       </c>
       <c r="N94">
-        <v>-663.4857756247955</v>
+        <v>-671.2880666641954</v>
       </c>
       <c r="O94">
-        <v>-165.8714439061989</v>
+        <v>-167.8220166660489</v>
       </c>
       <c r="P94">
-        <v>-497.6143317185966</v>
+        <v>-503.4660499981466</v>
       </c>
       <c r="Q94">
-        <v>-129.3143317185966</v>
+        <v>-135.1660499981465</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5624124385042005</v>
+        <v>0.6362142154333721</v>
       </c>
       <c r="T94">
-        <v>10.06973799667299</v>
+        <v>11.50827199619771</v>
       </c>
       <c r="U94">
         <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.01892037631808833</v>
+        <v>0.01871693141144222</v>
       </c>
       <c r="W94">
-        <v>0.2371628689054175</v>
+        <v>0.2372120489888273</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.07568150527235329</v>
+        <v>0.07486772564576893</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2651422006399455</v>
+        <v>0.2671015668065708</v>
       </c>
       <c r="C95">
-        <v>-1977.96525798592</v>
+        <v>-2013.695160844539</v>
       </c>
       <c r="D95">
-        <v>390.1027420140805</v>
+        <v>386.6488391554611</v>
       </c>
       <c r="E95">
-        <v>181.9680000000003</v>
+        <v>214.2440000000001</v>
       </c>
       <c r="F95">
-        <v>3001.668</v>
+        <v>3033.944</v>
       </c>
       <c r="G95">
         <v>633.6</v>
@@ -9083,37 +9083,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M95">
-        <v>725.6130666641955</v>
+        <v>733.4153577035953</v>
       </c>
       <c r="N95">
-        <v>-671.2880666641954</v>
+        <v>-679.0903577035954</v>
       </c>
       <c r="O95">
-        <v>-167.8220166660489</v>
+        <v>-169.7725894258988</v>
       </c>
       <c r="P95">
-        <v>-503.4660499981466</v>
+        <v>-509.3177682776965</v>
       </c>
       <c r="Q95">
-        <v>-135.1660499981465</v>
+        <v>-141.0177682776965</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6362142154333721</v>
+        <v>0.7346165846722675</v>
       </c>
       <c r="T95">
-        <v>11.50827199619771</v>
+        <v>13.42631732889733</v>
       </c>
       <c r="U95">
         <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.01871693141144222</v>
+        <v>0.01851781511983113</v>
       </c>
       <c r="W95">
-        <v>0.2372120489888273</v>
+        <v>0.2372601826874838</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07486772564576893</v>
+        <v>0.07407126047932444</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2671015668065708</v>
+        <v>0.2690609329731962</v>
       </c>
       <c r="C96">
-        <v>-2013.695160844539</v>
+        <v>-2049.364439927079</v>
       </c>
       <c r="D96">
-        <v>386.6488391554611</v>
+        <v>383.2555600729216</v>
       </c>
       <c r="E96">
-        <v>214.2440000000001</v>
+        <v>246.5200000000004</v>
       </c>
       <c r="F96">
-        <v>3033.944</v>
+        <v>3066.22</v>
       </c>
       <c r="G96">
         <v>633.6</v>
@@ -9165,37 +9165,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M96">
-        <v>733.4153577035953</v>
+        <v>741.2176487429954</v>
       </c>
       <c r="N96">
-        <v>-679.0903577035954</v>
+        <v>-686.8926487429953</v>
       </c>
       <c r="O96">
-        <v>-169.7725894258988</v>
+        <v>-171.7231621857488</v>
       </c>
       <c r="P96">
-        <v>-509.3177682776965</v>
+        <v>-515.1694865572465</v>
       </c>
       <c r="Q96">
-        <v>-141.0177682776965</v>
+        <v>-146.8694865572465</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7346165846722675</v>
+        <v>0.8723799016067215</v>
       </c>
       <c r="T96">
-        <v>13.42631732889733</v>
+        <v>16.1115807946768</v>
       </c>
       <c r="U96">
         <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.01851781511983113</v>
+        <v>0.0183228907501487</v>
       </c>
       <c r="W96">
-        <v>0.2372601826874838</v>
+        <v>0.2373073030451159</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07407126047932444</v>
+        <v>0.07329156300059492</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2690609329731962</v>
+        <v>0.2710202991398215</v>
       </c>
       <c r="C97">
-        <v>-2049.364439927079</v>
+        <v>-2084.974677473365</v>
       </c>
       <c r="D97">
-        <v>383.2555600729216</v>
+        <v>379.921322526635</v>
       </c>
       <c r="E97">
-        <v>246.5200000000004</v>
+        <v>278.7960000000003</v>
       </c>
       <c r="F97">
-        <v>3066.22</v>
+        <v>3098.496</v>
       </c>
       <c r="G97">
         <v>633.6</v>
@@ -9247,37 +9247,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M97">
-        <v>741.2176487429954</v>
+        <v>749.0199397823952</v>
       </c>
       <c r="N97">
-        <v>-686.8926487429953</v>
+        <v>-694.6949397823953</v>
       </c>
       <c r="O97">
-        <v>-171.7231621857488</v>
+        <v>-173.6737349455988</v>
       </c>
       <c r="P97">
-        <v>-515.1694865572465</v>
+        <v>-521.0212048367964</v>
       </c>
       <c r="Q97">
-        <v>-146.8694865572465</v>
+        <v>-152.7212048367964</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8723799016067215</v>
+        <v>1.079024877008403</v>
       </c>
       <c r="T97">
-        <v>16.1115807946768</v>
+        <v>20.13947599334601</v>
       </c>
       <c r="U97">
         <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.0183228907501487</v>
+        <v>0.01813202730483465</v>
       </c>
       <c r="W97">
-        <v>0.2373073030451159</v>
+        <v>0.2373534417286307</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07329156300059492</v>
+        <v>0.0725281092193385</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2710202991398215</v>
+        <v>0.2729796653064468</v>
       </c>
       <c r="C98">
-        <v>-2084.974677473365</v>
+        <v>-2120.52740113758</v>
       </c>
       <c r="D98">
-        <v>379.921322526635</v>
+        <v>376.6445988624192</v>
       </c>
       <c r="E98">
-        <v>278.7959999999998</v>
+        <v>311.0720000000001</v>
       </c>
       <c r="F98">
-        <v>3098.496</v>
+        <v>3130.772</v>
       </c>
       <c r="G98">
         <v>633.6</v>
@@ -9329,37 +9329,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M98">
-        <v>749.0199397823951</v>
+        <v>756.8222308217952</v>
       </c>
       <c r="N98">
-        <v>-694.6949397823951</v>
+        <v>-702.4972308217953</v>
       </c>
       <c r="O98">
-        <v>-173.6737349455988</v>
+        <v>-175.6243077054488</v>
       </c>
       <c r="P98">
-        <v>-521.0212048367963</v>
+        <v>-526.8729231163464</v>
       </c>
       <c r="Q98">
-        <v>-152.7212048367963</v>
+        <v>-158.5729231163464</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.0790248770084</v>
+        <v>1.423433169344533</v>
       </c>
       <c r="T98">
-        <v>20.13947599334596</v>
+        <v>26.85263465779461</v>
       </c>
       <c r="U98">
         <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.01813202730483466</v>
+        <v>0.01794509918828997</v>
       </c>
       <c r="W98">
-        <v>0.2373534417286307</v>
+        <v>0.2373986290990833</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07252810921933872</v>
+        <v>0.07178039675315984</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2729796653064468</v>
+        <v>0.2749390314730722</v>
       </c>
       <c r="C99">
-        <v>-2120.52740113758</v>
+        <v>-2156.024086322068</v>
       </c>
       <c r="D99">
-        <v>376.6445988624192</v>
+        <v>373.4239136779316</v>
       </c>
       <c r="E99">
-        <v>311.0720000000001</v>
+        <v>343.348</v>
       </c>
       <c r="F99">
-        <v>3130.772</v>
+        <v>3163.048</v>
       </c>
       <c r="G99">
         <v>633.6</v>
@@ -9411,37 +9411,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M99">
-        <v>756.8222308217952</v>
+        <v>764.6245218611951</v>
       </c>
       <c r="N99">
-        <v>-702.4972308217953</v>
+        <v>-710.2995218611952</v>
       </c>
       <c r="O99">
-        <v>-175.6243077054488</v>
+        <v>-177.5748804652988</v>
       </c>
       <c r="P99">
-        <v>-526.8729231163464</v>
+        <v>-532.7246413958965</v>
       </c>
       <c r="Q99">
-        <v>-158.5729231163464</v>
+        <v>-164.4246413958965</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.423433169344533</v>
+        <v>2.112249754016799</v>
       </c>
       <c r="T99">
-        <v>26.85263465779461</v>
+        <v>40.27895198669192</v>
       </c>
       <c r="U99">
         <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.01794509918828997</v>
+        <v>0.0177619859312666</v>
       </c>
       <c r="W99">
-        <v>0.2373986290990833</v>
+        <v>0.2374428942783022</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07178039675315984</v>
+        <v>0.07104794372506629</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2749390314730722</v>
+        <v>0.2768983976396975</v>
       </c>
       <c r="C100">
-        <v>-2156.024086322068</v>
+        <v>-2191.466158392417</v>
       </c>
       <c r="D100">
-        <v>373.4239136779316</v>
+        <v>370.2578416075831</v>
       </c>
       <c r="E100">
-        <v>343.348</v>
+        <v>375.6240000000003</v>
       </c>
       <c r="F100">
-        <v>3163.048</v>
+        <v>3195.324</v>
       </c>
       <c r="G100">
         <v>633.6</v>
@@ -9493,37 +9493,37 @@
         <v>54.32499999999999</v>
       </c>
       <c r="M100">
-        <v>764.6245218611951</v>
+        <v>772.4268129005951</v>
       </c>
       <c r="N100">
-        <v>-710.2995218611952</v>
+        <v>-718.1018129005952</v>
       </c>
       <c r="O100">
-        <v>-177.5748804652988</v>
+        <v>-179.5254532251488</v>
       </c>
       <c r="P100">
-        <v>-532.7246413958965</v>
+        <v>-538.5763596754464</v>
       </c>
       <c r="Q100">
-        <v>-164.4246413958965</v>
+        <v>-170.2763596754464</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.112249754016799</v>
+        <v>4.178699508033599</v>
       </c>
       <c r="T100">
-        <v>40.27895198669192</v>
+        <v>80.55790397338384</v>
       </c>
       <c r="U100">
         <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.0177619859312666</v>
+        <v>0.01758257193196087</v>
       </c>
       <c r="W100">
-        <v>0.2374428942783022</v>
+        <v>0.2374862652114762</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07104794372506629</v>
+        <v>0.07033028772784344</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2768983976396975</v>
-      </c>
-      <c r="C101">
-        <v>-2191.466158392417</v>
-      </c>
-      <c r="D101">
-        <v>370.2578416075831</v>
-      </c>
-      <c r="E101">
-        <v>375.6240000000003</v>
-      </c>
-      <c r="F101">
-        <v>3195.324</v>
-      </c>
-      <c r="G101">
-        <v>633.6</v>
-      </c>
-      <c r="H101">
-        <v>407.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>422.625</v>
-      </c>
-      <c r="K101">
-        <v>368.3</v>
-      </c>
-      <c r="L101">
-        <v>54.32499999999999</v>
-      </c>
-      <c r="M101">
-        <v>772.4268129005951</v>
-      </c>
-      <c r="N101">
-        <v>-718.1018129005952</v>
-      </c>
-      <c r="O101">
-        <v>-179.5254532251488</v>
-      </c>
-      <c r="P101">
-        <v>-538.5763596754464</v>
-      </c>
-      <c r="Q101">
-        <v>-170.2763596754464</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.178699508033599</v>
-      </c>
-      <c r="T101">
-        <v>80.55790397338384</v>
-      </c>
-      <c r="U101">
-        <v>0.2417366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.01758257193196087</v>
-      </c>
-      <c r="W101">
-        <v>0.2374862652114762</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07033028772784344</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
